--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 04-Sep-2026  14:44:21    |    Closing Price Date: 04-Sep-2026</t>
+          <t>Scan Run: 07-Sep-2026  16:15:16    |    Closing Price Date: 07-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>04-Sep-2026  14:44:21</t>
+          <t>07-Sep-2026  16:15:16</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 14.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 7 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 12 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 20 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1322</v>
+        <v>1309.5</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1306</v>
+        <v>1306.33</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1308.93</v>
+        <v>1308.95</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1355.96</v>
+        <v>1355.53</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>712.1</v>
+        <v>710.5</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>722.27</v>
+        <v>721.15</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>742.02</v>
+        <v>740.78</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>810.4400000000001</v>
+        <v>809.61</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -849,29 +849,29 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2304</v>
+        <v>2270</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2325.53</v>
+        <v>2320.24</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2302.4</v>
+        <v>2301.13</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2494.58</v>
+        <v>2490.49</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>176.4</v>
+        <v>172.8</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>179.87</v>
+        <v>179.19</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>181.04</v>
+        <v>180.72</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>198.92</v>
+        <v>198.67</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -937,24 +937,24 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1423.2</v>
+        <v>1427.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1426.58</v>
+        <v>1426.67</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1406.37</v>
+        <v>1407.2</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1364.32</v>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1364.82</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1016.1</v>
+        <v>1005.9</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1042.13</v>
+        <v>1038.68</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1039.99</v>
+        <v>1038.66</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1005.73</v>
+        <v>1006.42</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -1006,9 +1006,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J7" s="14" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1840</v>
+        <v>1854</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1897.43</v>
+        <v>1893.29</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1899.73</v>
+        <v>1897.94</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1893.55</v>
+        <v>1893.07</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1130</v>
+        <v>1087.5</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1135.4</v>
+        <v>1130.84</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1130.34</v>
+        <v>1128.66</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1237.49</v>
+        <v>1236.14</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3170</v>
+        <v>3160</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3309.43</v>
+        <v>3295.2</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3279.59</v>
+        <v>3274.9</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3250.04</v>
+        <v>3250.28</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3964.1</v>
+        <v>3999</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4017.99</v>
+        <v>4016.18</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4003.11</v>
+        <v>4002.95</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3928.44</v>
+        <v>3930.47</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1256.46</v>
+        <v>1257.37</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1266.07</v>
+        <v>1266.06</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1268.77</v>
+        <v>1268.73</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
@@ -1245,34 +1245,34 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>188.79</v>
+        <v>185.61</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>186.02</v>
+        <v>185.98</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>188.28</v>
+        <v>188.17</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.6</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>187.49</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="14" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>322.75</v>
+        <v>320.8</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>321.57</v>
+        <v>321.5</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>305.51</v>
+        <v>306.11</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>280.35</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>281.45</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1899</v>
+        <v>1895</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1923.37</v>
+        <v>1920.67</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1912.04</v>
+        <v>1911.37</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1815.24</v>
+        <v>1816.34</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>984.8</v>
+        <v>992</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1017.23</v>
+        <v>1014.83</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1039.52</v>
+        <v>1037.66</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1058.1</v>
+        <v>1057.56</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>424.5</v>
+        <v>422.1</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>409.72</v>
+        <v>410.9</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>399.64</v>
+        <v>400.52</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.26</v>
+        <v>398.41</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>332.8</v>
+        <v>332.73</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>340.67</v>
+        <v>340.33</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>349.66</v>
+        <v>349.19</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1060.5</v>
+        <v>1060</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1073.3</v>
+        <v>1072.04</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1053.06</v>
+        <v>1053.33</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>987.4400000000001</v>
+        <v>987.74</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1023.44</v>
+        <v>1021.78</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1014.07</v>
+        <v>1013.76</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>951.9</v>
+        <v>951.6799999999999</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2938</v>
+        <v>2950</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2994.55</v>
+        <v>2990.3</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2989.23</v>
+        <v>2987.7</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2685.05</v>
+        <v>2687.83</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>405.35</v>
+        <v>404</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>408.11</v>
+        <v>407.72</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>408.56</v>
+        <v>408.38</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>413.07</v>
+        <v>412.86</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12694</v>
+        <v>12760</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13391.04</v>
+        <v>13330.94</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13531.64</v>
+        <v>13501.38</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13758.74</v>
+        <v>13747.13</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>415.35</v>
+        <v>418.85</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>404.9</v>
+        <v>406.23</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>411.73</v>
+        <v>412.01</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>412.96</v>
+        <v>413.08</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1707.3</v>
+        <v>1694.3</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1691.24</v>
+        <v>1691.54</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1716.89</v>
+        <v>1716</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1631.47</v>
+        <v>1634.4</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1817,29 +1817,29 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8650</v>
+        <v>8760</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8773.18</v>
+        <v>8771.93</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8716.83</v>
+        <v>8718.530000000001</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8122.48</v>
+        <v>8127.18</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>264.1</v>
+        <v>263.5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>269.95</v>
+        <v>269.34</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>277.06</v>
+        <v>276.52</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>306.74</v>
+        <v>306.27</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1086.13</v>
+        <v>1081.45</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1067.68</v>
+        <v>1066.48</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>968.22</v>
+        <v>968.38</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -1949,29 +1949,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1596.9</v>
+        <v>1564</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1605.82</v>
+        <v>1601.84</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1567.61</v>
+        <v>1567.47</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1494.28</v>
+        <v>1493.76</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4977</v>
+        <v>5001</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5151.14</v>
+        <v>5136.84</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>5131.94</v>
+        <v>5126.81</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5018.62</v>
+        <v>5018.56</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1973.4</v>
+        <v>1960</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2020.88</v>
+        <v>2015.09</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2072.7</v>
+        <v>2068.28</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2190.89</v>
+        <v>2188.98</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2527.3</v>
+        <v>2500.9</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2625.4</v>
+        <v>2613.54</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2651.48</v>
+        <v>2645.58</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2572.35</v>
+        <v>2570.19</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11408</v>
+        <v>11175</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11554.12</v>
+        <v>11518.01</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11555.72</v>
+        <v>11540.79</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11533.76</v>
+        <v>11528.47</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>239.5</v>
+        <v>234.4</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>242.43</v>
+        <v>241.66</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>243.27</v>
+        <v>242.92</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>254.85</v>
+        <v>254.49</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>311.5</v>
+        <v>307</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>320.63</v>
+        <v>319.33</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>331.95</v>
+        <v>330.97</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>382.27</v>
+        <v>381.27</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7630.5</v>
+        <v>7672</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7894.98</v>
+        <v>7873.75</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7752.86</v>
+        <v>7749.69</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7242.55</v>
+        <v>7248.19</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>5020</v>
+        <v>4995</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>5038.44</v>
+        <v>5034.3</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4855.84</v>
+        <v>4861.3</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4366.9</v>
+        <v>4371.14</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2853</v>
+        <v>2814.5</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2910.18</v>
+        <v>2901.06</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2937.32</v>
+        <v>2932.5</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3229.42</v>
+        <v>3227.78</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>266</v>
+        <v>266.45</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>268.71</v>
+        <v>268.49</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>275.77</v>
+        <v>275.41</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>283.7</v>
+        <v>283.61</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3322</v>
+        <v>3302.4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3282.18</v>
+        <v>3284.11</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3213.02</v>
+        <v>3216.52</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2991.07</v>
+        <v>2992</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>234.65</v>
+        <v>233.7</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>235.65</v>
+        <v>235.47</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>241.11</v>
+        <v>240.82</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>249.94</v>
+        <v>249.61</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1293.4</v>
+        <v>1282.8</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1315.15</v>
+        <v>1312.07</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1282.12</v>
+        <v>1282.14</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1321.34</v>
+        <v>1319.95</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1410.5</v>
+        <v>1398</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1458.43</v>
+        <v>1452.67</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1455.81</v>
+        <v>1453.55</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1366.54</v>
+        <v>1366.6</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2609,24 +2609,24 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1325</v>
+        <v>1302</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1305.31</v>
+        <v>1305</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1285.09</v>
+        <v>1285.75</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1222.96</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1222.84</v>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -2653,24 +2653,24 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>546.4</v>
+        <v>533.2</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>544.05</v>
+        <v>543.01</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>553.9400000000001</v>
+        <v>553.12</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>622.09</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>620.29</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>11919</v>
+        <v>11800</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>11800.05</v>
+        <v>11800.04</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>11311.27</v>
+        <v>11330.43</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10149.47</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>10152.69</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -2741,29 +2741,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1970</v>
+        <v>1938.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1995.53</v>
+        <v>1990.11</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1951.12</v>
+        <v>1950.63</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1910.93</v>
+        <v>1911.48</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1151</v>
+        <v>1144.2</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1174.43</v>
+        <v>1171.55</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1201.05</v>
+        <v>1198.82</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1239.92</v>
+        <v>1239.17</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1422.6</v>
+        <v>1419.97</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1423.85</v>
+        <v>1422.72</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1404.96</v>
+        <v>1404.93</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1048.77</v>
+        <v>1045.56</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1075.36</v>
+        <v>1073</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1108.53</v>
+        <v>1107.9</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>04-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1775</v>
+        <v>1732</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1775.26</v>
+        <v>1771.14</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1802.76</v>
+        <v>1799.98</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1855.55</v>
+        <v>1854.11</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -160,13 +160,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 07-Sep-2026  16:15:16    |    Closing Price Date: 07-Sep-2026</t>
+          <t>Scan Run: 08-Sep-2026  14:51:28    |    Closing Price Date: 08-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>07-Sep-2026  16:15:16</t>
+          <t>08-Sep-2026  14:51:28</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 14.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 7 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 9 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 12 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 10 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 20 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 21 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,37 +761,37 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1309.5</v>
+        <v>1294.9</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1306.33</v>
+        <v>1305.24</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1308.95</v>
+        <v>1308.4</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1355.53</v>
+        <v>1354.93</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -805,37 +805,37 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>710.5</v>
+        <v>703</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>721.15</v>
+        <v>719.42</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>740.78</v>
+        <v>739.3</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>809.61</v>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="14" t="inlineStr">
+        <v>808.55</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -849,37 +849,37 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2270</v>
+        <v>2255.5</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2320.24</v>
+        <v>2314.07</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2301.13</v>
+        <v>2299.34</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2490.49</v>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
+        <v>2488.15</v>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -893,37 +893,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>172.8</v>
+        <v>171.5</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>179.19</v>
+        <v>178.46</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>180.72</v>
+        <v>180.36</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>198.67</v>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
+        <v>198.4</v>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
@@ -937,37 +937,37 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1427.5</v>
+        <v>1399.4</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1426.67</v>
+        <v>1424.07</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1407.2</v>
+        <v>1406.9</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1364.82</v>
+        <v>1365.17</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -981,37 +981,37 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1005.9</v>
+        <v>1008</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1038.68</v>
+        <v>1035.76</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1038.66</v>
+        <v>1037.45</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1006.42</v>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
+        <v>1006.44</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1854</v>
+        <v>1844</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1893.29</v>
+        <v>1888.6</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1897.94</v>
+        <v>1895.83</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1893.07</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
+        <v>1892.59</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1087.5</v>
+        <v>1082</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1130.84</v>
+        <v>1126.19</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1128.66</v>
+        <v>1126.83</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1236.14</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
+        <v>1234.61</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1113,37 +1113,37 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
         <v>3160</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3295.2</v>
+        <v>3282.32</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3274.9</v>
+        <v>3270.39</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3250.28</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
+        <v>3249.38</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1157,37 +1157,37 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3999</v>
+        <v>3946.1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4016.18</v>
+        <v>4009.51</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4002.95</v>
+        <v>4000.72</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3930.47</v>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
+        <v>3930.63</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -1201,37 +1201,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1266</v>
+        <v>1244.9</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1257.37</v>
+        <v>1255.36</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1266.06</v>
+        <v>1265.24</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1268.73</v>
+        <v>1268.52</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -1245,37 +1245,37 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>185.61</v>
+        <v>184.15</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>185.98</v>
+        <v>185.81</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>188.17</v>
+        <v>188.02</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.49</v>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
+        <v>187.46</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -1289,37 +1289,37 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>320.8</v>
+        <v>321.6</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>321.5</v>
+        <v>321.58</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>306.11</v>
+        <v>306.14</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>281.45</v>
       </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1333,37 +1333,37 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1895</v>
+        <v>1885.9</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1920.67</v>
+        <v>1917.36</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1911.37</v>
+        <v>1910.37</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1816.34</v>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
+        <v>1817.04</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -1377,37 +1377,37 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1014.83</v>
+        <v>1014.92</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1037.66</v>
+        <v>1037.7</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1057.56</v>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
+        <v>1057.57</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
@@ -1421,37 +1421,37 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>422.1</v>
+        <v>419.25</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>410.9</v>
+        <v>411.7</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>400.52</v>
+        <v>401.25</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.41</v>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
+        <v>398.62</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -1465,37 +1465,37 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>332</v>
+        <v>330.8</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>332.73</v>
+        <v>332.54</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>340.33</v>
+        <v>339.95</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>349.19</v>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
+        <v>349.01</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1060</v>
+        <v>1054.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1072.04</v>
+        <v>1070.33</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1053.33</v>
+        <v>1053.36</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>987.74</v>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
+        <v>988.4</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1553,37 +1553,37 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1021.78</v>
+        <v>1022.07</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1013.76</v>
+        <v>1013.87</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>951.6799999999999</v>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
+        <v>951.71</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2950</v>
+        <v>2953.1</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2990.3</v>
+        <v>2986.76</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2987.7</v>
+        <v>2986.34</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2687.83</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
+        <v>2690.47</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -1641,37 +1641,37 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>404</v>
+        <v>410.55</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>407.72</v>
+        <v>407.99</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>408.38</v>
+        <v>408.47</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>412.86</v>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J22" s="14" t="inlineStr">
+        <v>412.84</v>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1685,37 +1685,37 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12760</v>
+        <v>12641</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13330.94</v>
+        <v>13265.23</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13501.38</v>
+        <v>13467.64</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13747.13</v>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
+        <v>13736.12</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -1729,37 +1729,37 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>418.85</v>
+        <v>420.25</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>406.23</v>
+        <v>407.56</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>412.01</v>
+        <v>412.33</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>413.08</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
+        <v>413.15</v>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1773,37 +1773,37 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1694.3</v>
+        <v>1710</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1691.54</v>
+        <v>1693.03</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1716</v>
+        <v>1716.62</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1634.4</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
+        <v>1634.55</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -1817,37 +1817,37 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8760</v>
+        <v>8837.5</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8771.93</v>
+        <v>8779.309999999999</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8718.530000000001</v>
+        <v>8721.57</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8127.18</v>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
+        <v>8127.96</v>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -1861,37 +1861,37 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
         <v>263.5</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>269.34</v>
+        <v>268.78</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>276.52</v>
+        <v>276.01</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>306.27</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
+        <v>305.85</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1905,37 +1905,37 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1081.45</v>
+        <v>1076.45</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1066.48</v>
+        <v>1065.01</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>968.38</v>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
+        <v>968.98</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1601.84</v>
+        <v>1597.76</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1567.47</v>
+        <v>1567.14</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1493.76</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
+        <v>1494.41</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -1993,37 +1993,37 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>5001</v>
+        <v>5000</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5136.84</v>
+        <v>5136.74</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>5126.81</v>
+        <v>5126.77</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5018.56</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J30" s="14" t="inlineStr">
+        <v>5018.55</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
@@ -2037,37 +2037,37 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1960</v>
+        <v>1980</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2015.09</v>
+        <v>2016.99</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2068.28</v>
+        <v>2069.07</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2188.98</v>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="inlineStr">
+        <v>2189.18</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -2081,37 +2081,37 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2500.9</v>
+        <v>2481.6</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2613.54</v>
+        <v>2600.98</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2645.58</v>
+        <v>2639.15</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2570.19</v>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
+        <v>2569.31</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -2125,37 +2125,37 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11175</v>
+        <v>11009</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11518.01</v>
+        <v>11469.54</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11540.79</v>
+        <v>11519.94</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11528.47</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
+        <v>11523.3</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2169,37 +2169,37 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>234.4</v>
+        <v>233.15</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>241.66</v>
+        <v>241.54</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>242.92</v>
+        <v>242.87</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>254.49</v>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="14" t="inlineStr">
+        <v>254.48</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
@@ -2213,37 +2213,37 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>307</v>
+        <v>306.45</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>319.33</v>
+        <v>318.1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>330.97</v>
+        <v>330.01</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>381.27</v>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
+        <v>380.52</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2257,37 +2257,37 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7672</v>
+        <v>7747.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7873.75</v>
+        <v>7880.94</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7749.69</v>
+        <v>7752.65</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7248.19</v>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
+        <v>7248.94</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -2301,37 +2301,37 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4995</v>
+        <v>4987</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>5034.3</v>
+        <v>5029.8</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4861.3</v>
+        <v>4866.23</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4371.14</v>
-      </c>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J37" s="14" t="inlineStr">
+        <v>4377.27</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2345,37 +2345,37 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2814.5</v>
+        <v>2793.6</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2901.06</v>
+        <v>2890.83</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2932.5</v>
+        <v>2927.05</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3227.78</v>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="14" t="inlineStr">
+        <v>3223.46</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2389,37 +2389,37 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>266.45</v>
+        <v>265.75</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>268.49</v>
+        <v>268.42</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>275.41</v>
+        <v>275.38</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>283.61</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
+        <v>283.6</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2433,37 +2433,37 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3302.4</v>
+        <v>3306.8</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3284.11</v>
+        <v>3284.53</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3216.52</v>
+        <v>3216.69</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2992</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J40" s="14" t="inlineStr">
+        <v>2992.04</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -2477,37 +2477,37 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>233.7</v>
+        <v>236</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>235.47</v>
+        <v>235.52</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>240.82</v>
+        <v>240.63</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>249.61</v>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="14" t="inlineStr">
+        <v>249.48</v>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2521,37 +2521,37 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1282.8</v>
+        <v>1277</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1312.07</v>
+        <v>1308.73</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1282.14</v>
+        <v>1281.94</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1319.95</v>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
+        <v>1319.52</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J42" s="14" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -2565,37 +2565,37 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1398</v>
+        <v>1400.5</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1452.67</v>
+        <v>1447.71</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1453.55</v>
+        <v>1451.47</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1366.6</v>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
+        <v>1366.93</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2609,37 +2609,37 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1302</v>
+        <v>1297.3</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1305</v>
+        <v>1304.26</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1285.75</v>
+        <v>1286.21</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1222.84</v>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J44" s="14" t="inlineStr">
+        <v>1223.58</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -2653,37 +2653,37 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>533.2</v>
+        <v>533.8</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>543.01</v>
+        <v>542.14</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>553.12</v>
+        <v>552.36</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>620.29</v>
-      </c>
-      <c r="G45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="inlineStr">
+        <v>619.4299999999999</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>11800</v>
+        <v>11880</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>11800.04</v>
+        <v>11807.66</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>11330.43</v>
+        <v>11351.98</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10152.69</v>
-      </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J46" s="14" t="inlineStr">
+        <v>10169.88</v>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -2741,37 +2741,37 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1938.6</v>
+        <v>1938.1</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1990.11</v>
+        <v>1985.16</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1950.63</v>
+        <v>1950.14</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1911.48</v>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J47" s="14" t="inlineStr">
+        <v>1911.75</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2785,37 +2785,37 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1144.2</v>
+        <v>1151</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1171.55</v>
+        <v>1169.6</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1198.82</v>
+        <v>1196.94</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1239.17</v>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J48" s="14" t="inlineStr">
+        <v>1238.29</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -2829,37 +2829,37 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1395</v>
+        <v>1384</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1419.97</v>
+        <v>1418.93</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1422.72</v>
+        <v>1422.29</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1404.93</v>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J49" s="14" t="inlineStr">
+        <v>1404.82</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -2873,37 +2873,37 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1015</v>
+        <v>1014.1</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1045.56</v>
+        <v>1042.56</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1073</v>
+        <v>1070.69</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1107.9</v>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="14" t="inlineStr">
+        <v>1106.97</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2917,37 +2917,37 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1732</v>
+        <v>1696.6</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1771.14</v>
+        <v>1764.04</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1799.98</v>
+        <v>1795.93</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1854.11</v>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
+        <v>1852.54</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Sep-2026  14:51:28    |    Closing Price Date: 08-Sep-2026</t>
+          <t>Scan Run: 09-Sep-2026  14:59:46    |    Closing Price Date: 09-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Sep-2026  14:51:28</t>
+          <t>09-Sep-2026  14:59:46</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 9 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 12 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 21 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 20 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1294.9</v>
+        <v>1279</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1305.24</v>
+        <v>1302.74</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1308.4</v>
+        <v>1307.25</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1354.93</v>
+        <v>1354.17</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>703</v>
+        <v>687.1</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>719.42</v>
+        <v>716.34</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>739.3</v>
+        <v>737.25</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>808.55</v>
+        <v>807.34</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2255.5</v>
+        <v>2208</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2314.07</v>
+        <v>2303.97</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2299.34</v>
+        <v>2295.76</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2488.15</v>
+        <v>2485.36</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>171.5</v>
+        <v>167</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>178.46</v>
+        <v>177.37</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>180.36</v>
+        <v>179.83</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>198.4</v>
+        <v>198.09</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1399.4</v>
+        <v>1389.1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1424.07</v>
+        <v>1420.74</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1406.9</v>
+        <v>1406.2</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1365.17</v>
+        <v>1365.4</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1008</v>
+        <v>1000.5</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1035.76</v>
+        <v>1032.4</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1037.45</v>
+        <v>1036</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1006.44</v>
+        <v>1006.38</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1006,9 +1006,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1844</v>
+        <v>1814.7</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1888.6</v>
+        <v>1881.56</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1895.83</v>
+        <v>1892.64</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1892.59</v>
+        <v>1891.81</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1082</v>
+        <v>1035</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1126.19</v>
+        <v>1117.5</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1126.83</v>
+        <v>1123.23</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1234.61</v>
+        <v>1232.62</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3160</v>
+        <v>3150</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3282.32</v>
+        <v>3269.72</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3270.39</v>
+        <v>3265.67</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3249.38</v>
+        <v>3248.4</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3946.1</v>
+        <v>3922.6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4009.51</v>
+        <v>4001.23</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4000.72</v>
+        <v>3997.65</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3930.63</v>
+        <v>3930.55</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1182,9 +1182,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr">
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1244.9</v>
+        <v>1238.5</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1255.36</v>
+        <v>1253.76</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1265.24</v>
+        <v>1264.19</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1268.52</v>
+        <v>1268.22</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,34 +1245,34 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>184.15</v>
+        <v>188.75</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>185.81</v>
+        <v>186.09</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>188.02</v>
+        <v>188.05</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.46</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>187.47</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>321.6</v>
+        <v>320.6</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>321.58</v>
+        <v>321.48</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>306.14</v>
+        <v>306.71</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>281.45</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>281.84</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1885.9</v>
+        <v>1864.9</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1917.36</v>
+        <v>1912.36</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1910.37</v>
+        <v>1908.59</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1817.04</v>
+        <v>1817.51</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,24 +1377,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>993</v>
+        <v>1037.5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1014.92</v>
+        <v>1017.07</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1037.7</v>
+        <v>1037.69</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1057.57</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1057.37</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>419.25</v>
+        <v>414</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>411.7</v>
+        <v>411.92</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>401.25</v>
+        <v>401.75</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.62</v>
+        <v>398.77</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,24 +1465,24 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>330.8</v>
+        <v>334.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>332.54</v>
+        <v>332.73</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>339.95</v>
+        <v>339.74</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>349.01</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>348.86</v>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1509,29 +1509,29 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1054.1</v>
+        <v>1039.3</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1070.33</v>
+        <v>1067.37</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1053.36</v>
+        <v>1052.81</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>988.4</v>
+        <v>988.91</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -1553,29 +1553,29 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1009</v>
+        <v>1026.9</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1022.07</v>
+        <v>1022.53</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1013.87</v>
+        <v>1014.38</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>951.71</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>952.46</v>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -1597,29 +1597,29 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2953.1</v>
+        <v>3104.7</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2986.76</v>
+        <v>2997.99</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2986.34</v>
+        <v>2990.98</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2690.47</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2694.59</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>410.55</v>
+        <v>406</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>407.99</v>
+        <v>407.8</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>408.47</v>
+        <v>408.37</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>412.84</v>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>412.77</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12641</v>
+        <v>12618</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13265.23</v>
+        <v>13203.59</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13467.64</v>
+        <v>13434.32</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13736.12</v>
+        <v>13724.99</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>420.25</v>
+        <v>431</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>407.56</v>
+        <v>409.79</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>412.33</v>
+        <v>413.07</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>413.15</v>
+        <v>413.33</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,29 +1773,29 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1710</v>
+        <v>1775</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1693.03</v>
+        <v>1700.84</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1716.62</v>
+        <v>1718.91</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1634.55</v>
+        <v>1635.95</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8837.5</v>
+        <v>8967</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8779.309999999999</v>
+        <v>8797.190000000001</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8721.57</v>
+        <v>8731.190000000001</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8127.96</v>
+        <v>8136.3</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>263.5</v>
+        <v>260.8</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>268.78</v>
+        <v>268.02</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>276.01</v>
+        <v>275.42</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>305.85</v>
+        <v>305.4</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
         <v>1029</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1076.45</v>
+        <v>1071.93</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1065.01</v>
+        <v>1063.6</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>968.98</v>
+        <v>969.58</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1559</v>
+        <v>1508</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1597.76</v>
+        <v>1589.21</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1567.14</v>
+        <v>1564.82</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1494.41</v>
+        <v>1494.54</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>5000</v>
+        <v>4975</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5136.74</v>
+        <v>5121.34</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>5126.77</v>
+        <v>5120.82</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5018.55</v>
+        <v>5018.11</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1980</v>
+        <v>1945</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2016.99</v>
+        <v>2010.13</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2069.07</v>
+        <v>2064.2</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2189.18</v>
+        <v>2186.75</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2481.6</v>
+        <v>2489</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2600.98</v>
+        <v>2590.31</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2639.15</v>
+        <v>2633.26</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2569.31</v>
+        <v>2568.51</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11009</v>
+        <v>10900</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11469.54</v>
+        <v>11415.29</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11519.94</v>
+        <v>11495.62</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11523.3</v>
+        <v>11517.1</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>233.15</v>
+        <v>231</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>241.54</v>
+        <v>240.54</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>242.87</v>
+        <v>242.41</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>254.48</v>
+        <v>254.24</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>306.45</v>
+        <v>303</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>318.1</v>
+        <v>316.67</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>330.01</v>
+        <v>328.95</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>380.52</v>
+        <v>379.75</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7747.5</v>
+        <v>7734.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7880.94</v>
+        <v>7866.99</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7752.65</v>
+        <v>7751.94</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7248.94</v>
+        <v>7253.77</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4987</v>
+        <v>5005</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>5029.8</v>
+        <v>5027.44</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4866.23</v>
+        <v>4871.67</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4377.27</v>
+        <v>4383.52</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2793.6</v>
+        <v>2820</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2890.83</v>
+        <v>2884.08</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2927.05</v>
+        <v>2922.86</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3223.46</v>
+        <v>3219.45</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>265.75</v>
+        <v>265.85</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>268.42</v>
+        <v>268.18</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>275.38</v>
+        <v>275.01</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>283.6</v>
+        <v>283.42</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3306.8</v>
+        <v>3300</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3284.53</v>
+        <v>3286</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3216.69</v>
+        <v>3219.96</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2992.04</v>
+        <v>2995.1</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,24 +2477,24 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>236</v>
+        <v>234.02</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>235.52</v>
+        <v>235.37</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>240.63</v>
+        <v>240.37</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>249.48</v>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>249.32</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1277</v>
+        <v>1229.8</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1308.73</v>
+        <v>1301.21</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1281.94</v>
+        <v>1279.9</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1319.52</v>
+        <v>1318.63</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1400.5</v>
+        <v>1393</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1447.71</v>
+        <v>1442.5</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1451.47</v>
+        <v>1449.17</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1366.93</v>
+        <v>1367.19</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,24 +2609,24 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1297.3</v>
+        <v>1310</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1304.26</v>
+        <v>1304.81</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1286.21</v>
+        <v>1287.14</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1223.58</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1224.44</v>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>533.8</v>
+        <v>514</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>542.14</v>
+        <v>539.46</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>552.36</v>
+        <v>550.86</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>619.4299999999999</v>
+        <v>618.38</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>11880</v>
+        <v>11790</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>11807.66</v>
+        <v>11805.98</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>11351.98</v>
+        <v>11369.16</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10169.88</v>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>10186</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1938.1</v>
+        <v>1927</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1985.16</v>
+        <v>1979.62</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1950.14</v>
+        <v>1949.23</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1911.75</v>
+        <v>1911.9</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1169.6</v>
+        <v>1167.25</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1196.94</v>
+        <v>1194.91</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1238.29</v>
+        <v>1237.37</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1384</v>
+        <v>1363.1</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1418.93</v>
+        <v>1413.61</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1422.29</v>
+        <v>1419.97</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1404.82</v>
+        <v>1404.4</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1014.1</v>
+        <v>1001</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1042.56</v>
+        <v>1038.6</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1070.69</v>
+        <v>1067.95</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1106.97</v>
+        <v>1105.91</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1696.6</v>
+        <v>1684</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1764.04</v>
+        <v>1756.42</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1795.93</v>
+        <v>1791.54</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1852.54</v>
+        <v>1850.87</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Sep-2026  14:59:46    |    Closing Price Date: 09-Sep-2026</t>
+          <t>Scan Run: 10-Sep-2026  14:45:29    |    Closing Price Date: 10-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>24</v>
-      </c>
       <c r="D5" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Sep-2026  14:59:46</t>
+          <t>10-Sep-2026  14:45:29</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 12 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 12 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 11 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 20 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 21 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1302.74</v>
+        <v>1300.01</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1307.25</v>
+        <v>1305.95</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1354.17</v>
+        <v>1353.04</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>687.1</v>
+        <v>693.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>716.34</v>
+        <v>714.2</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>737.25</v>
+        <v>735.55</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>807.34</v>
+        <v>806.0599999999999</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2208</v>
+        <v>2204.1</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2303.97</v>
+        <v>2294.46</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2295.76</v>
+        <v>2292.17</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2485.36</v>
+        <v>2480.86</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>167</v>
+        <v>166.3</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>177.37</v>
+        <v>176.31</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>179.83</v>
+        <v>179.3</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>198.09</v>
+        <v>197.71</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1389.1</v>
+        <v>1384.5</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1420.74</v>
+        <v>1417.29</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1406.2</v>
+        <v>1405.35</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1365.4</v>
+        <v>1365.09</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1000.5</v>
+        <v>1009.7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1032.4</v>
+        <v>1030.24</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1036</v>
+        <v>1034.97</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1006.38</v>
+        <v>1006.26</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1006,9 +1006,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1814.7</v>
+        <v>1839</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1881.56</v>
+        <v>1877.5</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1892.64</v>
+        <v>1890.54</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1891.81</v>
+        <v>1890.78</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1035</v>
+        <v>1036.5</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1117.5</v>
+        <v>1109.79</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1123.23</v>
+        <v>1119.83</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1232.62</v>
+        <v>1230.25</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3150</v>
+        <v>3123.8</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3269.72</v>
+        <v>3255.82</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3265.67</v>
+        <v>3260.11</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3248.4</v>
+        <v>3247.97</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3922.6</v>
+        <v>3955</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>4001.23</v>
+        <v>3996.83</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3997.65</v>
+        <v>3995.98</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3930.55</v>
+        <v>3930.76</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1182,9 +1182,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr">
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1238.5</v>
+        <v>1246</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1253.76</v>
+        <v>1253.02</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1264.19</v>
+        <v>1263.47</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1268.22</v>
+        <v>1267.47</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,34 +1245,34 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>188.75</v>
+        <v>186.78</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>186.09</v>
+        <v>186.16</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>188.05</v>
+        <v>188</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.47</v>
+        <v>187.4</v>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>320.6</v>
+        <v>322.1</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>321.48</v>
+        <v>321.54</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>306.71</v>
+        <v>307.31</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>281.84</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>282.1</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1864.9</v>
+        <v>1861</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1912.36</v>
+        <v>1907.47</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1908.59</v>
+        <v>1906.72</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1817.51</v>
+        <v>1817.66</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,29 +1377,29 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1037.5</v>
+        <v>1038.6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1017.07</v>
+        <v>1019.12</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1037.69</v>
+        <v>1037.73</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1057.37</v>
+        <v>1056.67</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>414</v>
+        <v>416.55</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>411.92</v>
+        <v>412.36</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>401.75</v>
+        <v>402.33</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.77</v>
+        <v>398.79</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>334.5</v>
+        <v>335</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>332.73</v>
+        <v>332.94</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>339.74</v>
+        <v>339.55</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>348.86</v>
+        <v>348.56</v>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1039.3</v>
+        <v>1043.5</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1067.37</v>
+        <v>1065.1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1052.81</v>
+        <v>1052.45</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>988.91</v>
+        <v>988.89</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,29 +1553,29 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1026.9</v>
+        <v>1014</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1022.53</v>
+        <v>1021.72</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1014.38</v>
+        <v>1014.37</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>952.46</v>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>953.1</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3104.7</v>
+        <v>3077.2</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2997.99</v>
+        <v>3005.54</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2990.98</v>
+        <v>2994.36</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2694.59</v>
+        <v>2696.47</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>407.8</v>
+        <v>407.53</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>408.37</v>
+        <v>408.24</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>412.77</v>
+        <v>412.64</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12618</v>
+        <v>12590</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13203.59</v>
+        <v>13145.15</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13434.32</v>
+        <v>13401.21</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13724.99</v>
+        <v>13707.3</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>409.79</v>
+        <v>411.91</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>413.07</v>
+        <v>413.81</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>413.33</v>
+        <v>413.26</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1775</v>
+        <v>1768</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1700.84</v>
+        <v>1707.23</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1718.91</v>
+        <v>1720.83</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1635.95</v>
+        <v>1635.82</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8967</v>
+        <v>8900</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8797.190000000001</v>
+        <v>8806.98</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8731.190000000001</v>
+        <v>8737.809999999999</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8136.3</v>
+        <v>8139.72</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>260.8</v>
+        <v>259.3</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>268.02</v>
+        <v>267.19</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>275.42</v>
+        <v>274.78</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>305.4</v>
+        <v>304.85</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1071.93</v>
+        <v>1068.7</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1063.6</v>
+        <v>1062.59</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>969.58</v>
+        <v>970.48</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1508</v>
+        <v>1525.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1589.21</v>
+        <v>1583.17</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1564.82</v>
+        <v>1563.29</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1494.54</v>
+        <v>1494.65</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4975</v>
+        <v>4945</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5121.34</v>
+        <v>5104.54</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>5120.82</v>
+        <v>5113.92</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5018.11</v>
+        <v>5019.46</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1945</v>
+        <v>1942.3</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2010.13</v>
+        <v>2003.67</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2064.2</v>
+        <v>2059.42</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2186.75</v>
+        <v>2183.55</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2489</v>
+        <v>2498.1</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2590.31</v>
+        <v>2581.53</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2633.26</v>
+        <v>2627.96</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2568.51</v>
+        <v>2567.37</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10900</v>
+        <v>10979</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11415.29</v>
+        <v>11373.74</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11495.62</v>
+        <v>11475.36</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11517.1</v>
+        <v>11505.45</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>231</v>
+        <v>230.25</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>240.54</v>
+        <v>239.56</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>242.41</v>
+        <v>241.93</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>254.24</v>
+        <v>253.9</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>303</v>
+        <v>300.5</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>316.67</v>
+        <v>315.13</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>328.95</v>
+        <v>327.83</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>379.75</v>
+        <v>378.65</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7734.5</v>
+        <v>7697</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7866.99</v>
+        <v>7850.8</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7751.94</v>
+        <v>7749.78</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7253.77</v>
+        <v>7257.9</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>5005</v>
+        <v>5021</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>5027.44</v>
+        <v>5026.82</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4871.67</v>
+        <v>4877.53</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4383.52</v>
+        <v>4389.63</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2820</v>
+        <v>2818.7</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2884.08</v>
+        <v>2877.86</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2922.86</v>
+        <v>2918.77</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3219.45</v>
+        <v>3214.19</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,24 +2389,24 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>265.85</v>
+        <v>271.75</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>268.18</v>
+        <v>268.52</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>275.01</v>
+        <v>274.88</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>283.42</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>283.12</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3300</v>
+        <v>3319</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3286</v>
+        <v>3289.14</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3219.96</v>
+        <v>3223.84</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2995.1</v>
+        <v>2999.47</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
@@ -2477,24 +2477,24 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>234.02</v>
+        <v>237.27</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>235.37</v>
+        <v>235.56</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>240.37</v>
+        <v>240.25</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>249.32</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>249.16</v>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1229.8</v>
+        <v>1207</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1301.21</v>
+        <v>1292.24</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1279.9</v>
+        <v>1277.04</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1318.63</v>
+        <v>1317.48</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1393</v>
+        <v>1386.2</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1442.5</v>
+        <v>1437.13</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1449.17</v>
+        <v>1446.7</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1367.19</v>
+        <v>1367.09</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,24 +2609,24 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1304.81</v>
+        <v>1304.73</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1287.14</v>
+        <v>1287.8</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1224.44</v>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1225.03</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>514</v>
+        <v>526.15</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>539.46</v>
+        <v>538.1900000000001</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>550.86</v>
+        <v>549.89</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>618.38</v>
+        <v>617.11</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>11790</v>
+        <v>11768</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>11805.98</v>
+        <v>11802.36</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>11369.16</v>
+        <v>11384.8</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10186</v>
+        <v>10203.66</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1927</v>
+        <v>1940.5</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1979.62</v>
+        <v>1975.89</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1949.23</v>
+        <v>1948.89</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1911.9</v>
+        <v>1910.69</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1167.25</v>
+        <v>1164.94</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1194.91</v>
+        <v>1192.87</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1237.37</v>
+        <v>1236.45</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1363.1</v>
+        <v>1373.3</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1413.61</v>
+        <v>1409.77</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1419.97</v>
+        <v>1418.14</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1404.4</v>
+        <v>1404.21</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1001</v>
+        <v>999.6</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1038.6</v>
+        <v>1034.89</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1067.95</v>
+        <v>1065.27</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1105.91</v>
+        <v>1104.62</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>09-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1684</v>
+        <v>1700.6</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1756.42</v>
+        <v>1751.11</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1791.54</v>
+        <v>1787.97</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1850.87</v>
+        <v>1848.27</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 10-Sep-2026  14:45:29    |    Closing Price Date: 10-Sep-2026</t>
+          <t>Scan Run: 11-Sep-2026  14:49:16    |    Closing Price Date: 11-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>10-Sep-2026  14:45:29</t>
+          <t>11-Sep-2026  14:49:16</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 12 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 11 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 9 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 21 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 20 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1274</v>
+        <v>1257.5</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1300.01</v>
+        <v>1295.96</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1305.95</v>
+        <v>1304.05</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1353.04</v>
+        <v>1352.81</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>693.8</v>
+        <v>708.25</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>714.2</v>
+        <v>713.63</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>735.55</v>
+        <v>734.48</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>806.0599999999999</v>
+        <v>805.42</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2204.1</v>
+        <v>2200.8</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2294.46</v>
+        <v>2285.54</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2292.17</v>
+        <v>2288.58</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2480.86</v>
+        <v>2478.29</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>166.3</v>
+        <v>167.4</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>176.31</v>
+        <v>175.47</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>179.3</v>
+        <v>178.84</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>197.71</v>
+        <v>197.44</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1384.5</v>
+        <v>1379.3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1417.29</v>
+        <v>1413.67</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1405.35</v>
+        <v>1404.33</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1365.09</v>
+        <v>1364.96</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1009.7</v>
+        <v>995.7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1030.24</v>
+        <v>1026.95</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1034.97</v>
+        <v>1033.43</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1006.26</v>
+        <v>1006.02</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -1006,9 +1006,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1839</v>
+        <v>1831.1</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1877.5</v>
+        <v>1873.08</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1890.54</v>
+        <v>1888.21</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1890.78</v>
+        <v>1891.53</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1036.5</v>
+        <v>1037.7</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1109.79</v>
+        <v>1102.92</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1119.83</v>
+        <v>1116.61</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1230.25</v>
+        <v>1228.65</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>3123.8</v>
+        <v>3107</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>3255.82</v>
+        <v>3241.65</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3260.11</v>
+        <v>3254.1</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3247.97</v>
+        <v>3246.84</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3955</v>
+        <v>3930.7</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3996.83</v>
+        <v>3990.53</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3995.98</v>
+        <v>3993.42</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3930.76</v>
+        <v>3930.03</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
         <v>1246</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1253.02</v>
+        <v>1252.35</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1263.47</v>
+        <v>1262.79</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1267.47</v>
+        <v>1266.83</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,24 +1245,24 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>186.78</v>
+        <v>183</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>186.16</v>
+        <v>185.86</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>188</v>
+        <v>187.8</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>187.4</v>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>187.38</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>322.1</v>
+        <v>323.5</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>321.54</v>
+        <v>321.73</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>307.31</v>
+        <v>307.95</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>282.1</v>
+        <v>282.84</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1861</v>
+        <v>1840</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1907.47</v>
+        <v>1901.04</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1906.72</v>
+        <v>1904.1</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1817.66</v>
+        <v>1817.78</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,29 +1377,29 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1038.6</v>
+        <v>1037.7</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1019.12</v>
+        <v>1020.89</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>1037.73</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1056.67</v>
+        <v>1056.88</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>416.55</v>
+        <v>419</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>412.36</v>
+        <v>412.99</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>402.33</v>
+        <v>402.98</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>398.79</v>
+        <v>399.01</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>335</v>
+        <v>333.4</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>332.94</v>
+        <v>332.99</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>339.55</v>
+        <v>339.31</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>348.56</v>
+        <v>348.45</v>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1043.5</v>
+        <v>1034.5</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1065.1</v>
+        <v>1062.18</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1052.45</v>
+        <v>1051.74</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>988.89</v>
+        <v>989.38</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1014</v>
+        <v>981.5</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>1021.72</v>
+        <v>1017.89</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1014.37</v>
+        <v>1013.08</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>953.1</v>
+        <v>953.54</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3077.2</v>
+        <v>3060</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>3005.54</v>
+        <v>3010.72</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2994.36</v>
+        <v>2996.94</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2696.47</v>
+        <v>2700.83</v>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>405</v>
+        <v>404.35</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>407.53</v>
+        <v>407.23</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>408.24</v>
+        <v>408.09</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>412.64</v>
+        <v>412.74</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12590</v>
+        <v>12400</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>13145.15</v>
+        <v>13074.19</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>13401.21</v>
+        <v>13361.94</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13707.3</v>
+        <v>13695.67</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>432</v>
+        <v>426.4</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>411.91</v>
+        <v>413.29</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>413.81</v>
+        <v>414.3</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>413.26</v>
+        <v>413.46</v>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1768</v>
+        <v>1764.6</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1707.23</v>
+        <v>1712.7</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1720.83</v>
+        <v>1722.55</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1635.82</v>
+        <v>1637.26</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8900</v>
+        <v>8836</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8806.98</v>
+        <v>8809.74</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8737.809999999999</v>
+        <v>8741.66</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8139.72</v>
+        <v>8148.37</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>259.3</v>
+        <v>259.85</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>267.19</v>
+        <v>266.49</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>274.78</v>
+        <v>274.2</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>304.85</v>
+        <v>304.4</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1038</v>
+        <v>1028.6</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>1068.7</v>
+        <v>1064.88</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1062.59</v>
+        <v>1061.26</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>970.48</v>
+        <v>970.78</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1525.8</v>
+        <v>1541</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1583.17</v>
+        <v>1579.15</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1563.29</v>
+        <v>1562.42</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1494.65</v>
+        <v>1495.6</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4945</v>
+        <v>4973</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>5104.54</v>
+        <v>5092.02</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>5113.92</v>
+        <v>5108.4</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5019.46</v>
+        <v>5020.34</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1942.3</v>
+        <v>1927</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2003.67</v>
+        <v>1996.37</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2059.42</v>
+        <v>2054.23</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2183.55</v>
+        <v>2181.48</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2498.1</v>
+        <v>2472.5</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2581.53</v>
+        <v>2571.15</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2627.96</v>
+        <v>2621.86</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2567.37</v>
+        <v>2566.16</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10979</v>
+        <v>11000</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>11373.74</v>
+        <v>11338.15</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11475.36</v>
+        <v>11456.72</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11505.45</v>
+        <v>11500.35</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>230.25</v>
+        <v>229.9</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>239.56</v>
+        <v>238.64</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>241.93</v>
+        <v>241.46</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>253.9</v>
+        <v>253.92</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>300.5</v>
+        <v>301.1</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>315.13</v>
+        <v>313.79</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>327.83</v>
+        <v>326.79</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>378.65</v>
+        <v>378.33</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7697</v>
+        <v>7530</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7850.8</v>
+        <v>7820.25</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7749.78</v>
+        <v>7741.17</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7257.9</v>
+        <v>7259.23</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>5021</v>
+        <v>5009.5</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>5026.82</v>
+        <v>5025.17</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4877.53</v>
+        <v>4882.7</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4389.63</v>
+        <v>4395</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2818.7</v>
+        <v>2802.4</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2877.86</v>
+        <v>2870.67</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2918.77</v>
+        <v>2914.21</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3214.19</v>
+        <v>3206.73</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>271.75</v>
+        <v>269.1</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>268.52</v>
+        <v>268.57</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>274.88</v>
+        <v>274.65</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>283.12</v>
+        <v>282.99</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>3319</v>
+        <v>3281.9</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3289.14</v>
+        <v>3288.45</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3223.84</v>
+        <v>3226.12</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2999.47</v>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>3002.17</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
@@ -2477,24 +2477,24 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>237.27</v>
+        <v>232.5</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>235.56</v>
+        <v>235.26</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>240.25</v>
+        <v>239.95</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>249.16</v>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>249.03</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1207</v>
+        <v>1206.1</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1292.24</v>
+        <v>1284.04</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1277.04</v>
+        <v>1274.26</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1317.48</v>
+        <v>1316.2</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1386.2</v>
+        <v>1383.3</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1437.13</v>
+        <v>1432.01</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1446.7</v>
+        <v>1444.22</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1367.09</v>
+        <v>1367.37</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,29 +2609,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1304</v>
+        <v>1265</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1304.73</v>
+        <v>1300.95</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1287.8</v>
+        <v>1286.91</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1225.03</v>
+        <v>1225.22</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>526.15</v>
+        <v>530</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>538.1900000000001</v>
+        <v>537.41</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>549.89</v>
+        <v>549.11</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>617.11</v>
+        <v>616.27</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>11768</v>
+        <v>11678</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>11802.36</v>
+        <v>11790.52</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>11384.8</v>
+        <v>11396.3</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10203.66</v>
+        <v>10218.35</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1940.5</v>
+        <v>1913.5</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1975.89</v>
+        <v>1969.95</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1948.89</v>
+        <v>1947.5</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1910.69</v>
+        <v>1909.27</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,24 +2785,24 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1143</v>
+        <v>1165.5</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1164.94</v>
+        <v>1165</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1192.87</v>
+        <v>1191.8</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1236.45</v>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1235.89</v>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1373.3</v>
+        <v>1366</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1409.77</v>
+        <v>1405.6</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1418.14</v>
+        <v>1416.09</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1404.21</v>
+        <v>1403.78</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>999.6</v>
+        <v>991</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>1034.89</v>
+        <v>1030.71</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1065.27</v>
+        <v>1062.36</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1104.62</v>
+        <v>1103.88</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1700.6</v>
+        <v>1684.7</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1751.11</v>
+        <v>1744.78</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1787.97</v>
+        <v>1783.92</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1848.27</v>
+        <v>1846.67</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -70,7 +70,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -90,11 +90,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -129,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -144,9 +139,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,7 +158,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 11-Sep-2026  14:49:16    |    Closing Price Date: 11-Sep-2026</t>
+          <t>Scan Run: 14-Sep-2026  16:45:16    |    Closing Price Date: 11-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -603,71 +595,71 @@
       <c r="C5" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>40</v>
+      <c r="D5" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>11-Sep-2026  14:49:16</t>
+          <t>14-Sep-2026  16:45:16</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Market Breadth Interpretation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Medium-Term (50 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 38.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Counts</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  Above 50 EMA : 9 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Above 200 EMA: 20 of 50 stocks</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Above 200 EMA: 19 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -754,2200 +746,2200 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n">
         <v>1257.5</v>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="10" t="n">
         <v>1295.96</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="10" t="n">
         <v>1304.05</v>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>1352.81</v>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="F2" s="10" t="n">
+        <v>1353.84</v>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>708.25</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="10" t="n">
         <v>713.63</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="10" t="n">
         <v>734.48</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>805.42</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="F3" s="10" t="n">
+        <v>806.17</v>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
         <v>2200.8</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="10" t="n">
         <v>2285.54</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="10" t="n">
         <v>2288.58</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>2478.29</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="F4" s="10" t="n">
+        <v>2479.92</v>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>167.4</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="10" t="n">
         <v>175.47</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <v>178.84</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>197.44</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="F5" s="10" t="n">
+        <v>197.61</v>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>1379.3</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>1413.67</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>1404.33</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>1364.96</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="F6" s="10" t="n">
+        <v>1365.1</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
         <v>995.7</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="10" t="n">
         <v>1026.95</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="10" t="n">
         <v>1033.43</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>1006.02</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="F7" s="10" t="n">
+        <v>1006.57</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
         <v>1831.1</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
         <v>1873.08</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>1888.21</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>1891.53</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="F8" s="10" t="n">
+        <v>1891.12</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>1037.7</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>1102.92</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <v>1116.61</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>1228.65</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="F9" s="10" t="n">
+        <v>1229.51</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
         <v>3107</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="10" t="n">
         <v>3241.65</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>3254.1</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>3246.84</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="F10" s="10" t="n">
+        <v>3248.21</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="n">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>3930.7</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>3990.53</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <v>3993.42</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>3930.03</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="F11" s="10" t="n">
+        <v>3932.17</v>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
         <v>1246</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="10" t="n">
         <v>1252.35</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="10" t="n">
         <v>1262.79</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>1266.83</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="F12" s="10" t="n">
+        <v>1268.88</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
         <v>183</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>185.86</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="10" t="n">
         <v>187.8</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>187.38</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="F13" s="10" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>323.5</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="10" t="n">
         <v>321.73</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="10" t="n">
         <v>307.95</v>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>282.84</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="F14" s="10" t="n">
+        <v>283.3</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="n">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
         <v>1840</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="10" t="n">
         <v>1901.04</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="10" t="n">
         <v>1904.1</v>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>1817.78</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
+      <c r="F15" s="10" t="n">
+        <v>1818.98</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
         <v>1037.7</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="10" t="n">
         <v>1020.89</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="10" t="n">
         <v>1037.73</v>
       </c>
-      <c r="F16" s="11" t="n">
-        <v>1056.88</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="F16" s="10" t="n">
+        <v>1058.8</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="n">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
         <v>419</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="10" t="n">
         <v>412.99</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="10" t="n">
         <v>402.98</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>399.01</v>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="F17" s="10" t="n">
+        <v>399.77</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
         <v>333.4</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="10" t="n">
         <v>332.99</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="10" t="n">
         <v>339.31</v>
       </c>
-      <c r="F18" s="11" t="n">
-        <v>348.45</v>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="F18" s="10" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
         <v>1034.5</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="10" t="n">
         <v>1062.18</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="10" t="n">
         <v>1051.74</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>989.38</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="F19" s="10" t="n">
+        <v>991.9299999999999</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="n">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
         <v>981.5</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="10" t="n">
         <v>1017.89</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="10" t="n">
         <v>1013.08</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>953.54</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="F20" s="10" t="n">
+        <v>954.16</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
         <v>3060</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="10" t="n">
         <v>3010.72</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="10" t="n">
         <v>2996.94</v>
       </c>
-      <c r="F21" s="11" t="n">
-        <v>2700.83</v>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="F21" s="10" t="n">
+        <v>2704.66</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
         <v>404.35</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="10" t="n">
         <v>407.23</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="10" t="n">
         <v>408.09</v>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>412.74</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="F22" s="10" t="n">
+        <v>412.81</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
         <v>12400</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="10" t="n">
         <v>13074.19</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="10" t="n">
         <v>13361.94</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>13695.67</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+      <c r="F23" s="10" t="n">
+        <v>13714.87</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="n">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
         <v>426.4</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="10" t="n">
         <v>413.29</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="10" t="n">
         <v>414.3</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>413.46</v>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="F24" s="10" t="n">
+        <v>413.7</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
         <v>1764.6</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="10" t="n">
         <v>1712.7</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="10" t="n">
         <v>1722.55</v>
       </c>
-      <c r="F25" s="11" t="n">
-        <v>1637.26</v>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="F25" s="10" t="n">
+        <v>1638.52</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
         <v>8836</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="10" t="n">
         <v>8809.74</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="10" t="n">
         <v>8741.66</v>
       </c>
-      <c r="F26" s="11" t="n">
-        <v>8148.37</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="F26" s="10" t="n">
+        <v>8151.55</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n">
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
         <v>259.85</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="10" t="n">
         <v>266.49</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="10" t="n">
         <v>274.2</v>
       </c>
-      <c r="F27" s="11" t="n">
-        <v>304.4</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="F27" s="10" t="n">
+        <v>304.64</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="n">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
         <v>1028.6</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="10" t="n">
         <v>1064.88</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="10" t="n">
         <v>1061.26</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>970.78</v>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="F28" s="10" t="n">
+        <v>973.08</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
         <v>1541</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="10" t="n">
         <v>1579.15</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="10" t="n">
         <v>1562.42</v>
       </c>
-      <c r="F29" s="11" t="n">
-        <v>1495.6</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="F29" s="10" t="n">
+        <v>1496.48</v>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
         <v>4973</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="10" t="n">
         <v>5092.02</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="10" t="n">
         <v>5108.4</v>
       </c>
-      <c r="F30" s="11" t="n">
-        <v>5020.34</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="F30" s="10" t="n">
+        <v>5032.1</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="n">
         <v>1927</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="10" t="n">
         <v>1996.37</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="10" t="n">
         <v>2054.23</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>2181.48</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
+      <c r="F31" s="10" t="n">
+        <v>2182.64</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
         <v>2472.5</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="10" t="n">
         <v>2571.15</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="10" t="n">
         <v>2621.86</v>
       </c>
-      <c r="F32" s="11" t="n">
-        <v>2566.16</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="F32" s="10" t="n">
+        <v>2566.12</v>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n">
         <v>11000</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="10" t="n">
         <v>11338.15</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="10" t="n">
         <v>11456.72</v>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>11500.35</v>
-      </c>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
+      <c r="F33" s="10" t="n">
+        <v>11509.4</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="n">
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
         <v>229.9</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="10" t="n">
         <v>238.64</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="10" t="n">
         <v>241.46</v>
       </c>
-      <c r="F34" s="11" t="n">
-        <v>253.92</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
+      <c r="F34" s="10" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="n">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="n">
         <v>301.1</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="10" t="n">
         <v>313.79</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="10" t="n">
         <v>326.79</v>
       </c>
-      <c r="F35" s="11" t="n">
-        <v>378.33</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+      <c r="F35" s="10" t="n">
+        <v>378.69</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="n">
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
         <v>7530</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="10" t="n">
         <v>7820.25</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="10" t="n">
         <v>7741.17</v>
       </c>
-      <c r="F36" s="11" t="n">
-        <v>7259.23</v>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
+      <c r="F36" s="10" t="n">
+        <v>7262.14</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="n">
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n">
         <v>5009.5</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="10" t="n">
         <v>5025.17</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="10" t="n">
         <v>4882.7</v>
       </c>
-      <c r="F37" s="11" t="n">
-        <v>4395</v>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
+      <c r="F37" s="10" t="n">
+        <v>4396.38</v>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="n">
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n">
         <v>2802.4</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="10" t="n">
         <v>2870.67</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="10" t="n">
         <v>2914.21</v>
       </c>
-      <c r="F38" s="11" t="n">
-        <v>3206.73</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
+      <c r="F38" s="10" t="n">
+        <v>3223.44</v>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="n">
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
         <v>269.1</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="10" t="n">
         <v>268.57</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="10" t="n">
         <v>274.65</v>
       </c>
-      <c r="F39" s="11" t="n">
-        <v>282.99</v>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
+      <c r="F39" s="10" t="n">
+        <v>283.47</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="n">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n">
         <v>3281.9</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="10" t="n">
         <v>3288.45</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="10" t="n">
         <v>3226.12</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>3002.17</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
+      <c r="F40" s="10" t="n">
+        <v>3004.61</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="n">
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n">
         <v>232.5</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="10" t="n">
         <v>235.26</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="10" t="n">
         <v>239.95</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>249.03</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
+      <c r="F41" s="10" t="n">
+        <v>249.21</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="n">
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n">
         <v>1206.1</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="10" t="n">
         <v>1284.04</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="10" t="n">
         <v>1274.26</v>
       </c>
-      <c r="F42" s="11" t="n">
-        <v>1316.2</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
+      <c r="F42" s="10" t="n">
+        <v>1317.07</v>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="n">
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="n">
         <v>1383.3</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="10" t="n">
         <v>1432.01</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="10" t="n">
         <v>1444.22</v>
       </c>
-      <c r="F43" s="11" t="n">
-        <v>1367.37</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+      <c r="F43" s="10" t="n">
+        <v>1367.73</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="n">
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="n">
         <v>1265</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D44" s="10" t="n">
         <v>1300.95</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="10" t="n">
         <v>1286.91</v>
       </c>
-      <c r="F44" s="11" t="n">
-        <v>1225.22</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
+      <c r="F44" s="10" t="n">
+        <v>1226.83</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="n">
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="n">
         <v>530</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="10" t="n">
         <v>537.41</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="10" t="n">
         <v>549.11</v>
       </c>
-      <c r="F45" s="11" t="n">
-        <v>616.27</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
+      <c r="F45" s="10" t="n">
+        <v>616.34</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="n">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="n">
         <v>11678</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="10" t="n">
         <v>11790.52</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="10" t="n">
         <v>11396.3</v>
       </c>
-      <c r="F46" s="11" t="n">
-        <v>10218.35</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
+      <c r="F46" s="10" t="n">
+        <v>10221.42</v>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="n">
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="n">
         <v>1913.5</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="10" t="n">
         <v>1969.95</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E47" s="10" t="n">
         <v>1947.5</v>
       </c>
-      <c r="F47" s="11" t="n">
-        <v>1909.27</v>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
+      <c r="F47" s="10" t="n">
+        <v>1911.81</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="n">
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="n">
         <v>1165.5</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="10" t="n">
         <v>1165</v>
       </c>
-      <c r="E48" s="11" t="n">
+      <c r="E48" s="10" t="n">
         <v>1191.8</v>
       </c>
-      <c r="F48" s="11" t="n">
-        <v>1235.89</v>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
+      <c r="F48" s="10" t="n">
+        <v>1238.6</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="n">
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="n">
         <v>1366</v>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="10" t="n">
         <v>1405.6</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E49" s="10" t="n">
         <v>1416.09</v>
       </c>
-      <c r="F49" s="11" t="n">
-        <v>1403.78</v>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
+      <c r="F49" s="10" t="n">
+        <v>1405.19</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="n">
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="n">
         <v>991</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="10" t="n">
         <v>1030.71</v>
       </c>
-      <c r="E50" s="11" t="n">
+      <c r="E50" s="10" t="n">
         <v>1062.36</v>
       </c>
-      <c r="F50" s="11" t="n">
-        <v>1103.88</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
+      <c r="F50" s="10" t="n">
+        <v>1103.76</v>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>11-Sep-2026</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="n">
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n">
         <v>1684.7</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="10" t="n">
         <v>1744.78</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E51" s="10" t="n">
         <v>1783.92</v>
       </c>
-      <c r="F51" s="11" t="n">
-        <v>1846.67</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
+      <c r="F51" s="10" t="n">
+        <v>1847.29</v>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 14-Sep-2026  16:45:16    |    Closing Price Date: 11-Sep-2026</t>
+          <t>Scan Run: 15-Sep-2026  15:25:31    |    Closing Price Date: 15-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>14-Sep-2026  16:45:16</t>
+          <t>15-Sep-2026  15:25:31</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 38.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 5 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 9 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 5 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 19 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 16 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1257.5</v>
+        <v>1235.3</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1295.96</v>
+        <v>1290.18</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1304.05</v>
+        <v>1301.35</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1353.84</v>
+        <v>1352.66</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,24 +797,24 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>708.25</v>
+        <v>716.55</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>713.63</v>
+        <v>713.91</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>734.48</v>
+        <v>733.78</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>806.17</v>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>805.28</v>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2200.8</v>
+        <v>2251</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2285.54</v>
+        <v>2282.25</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2288.58</v>
+        <v>2287.11</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2479.92</v>
+        <v>2477.65</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>167.4</v>
+        <v>170</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>175.47</v>
+        <v>174.94</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>178.84</v>
+        <v>178.49</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>197.61</v>
+        <v>197.33</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1379.3</v>
+        <v>1350.4</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1413.67</v>
+        <v>1407.65</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1404.33</v>
+        <v>1402.21</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1365.1</v>
+        <v>1364.95</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -954,9 +954,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>995.7</v>
+        <v>968</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1026.95</v>
+        <v>1021.34</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1033.43</v>
+        <v>1030.87</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1006.57</v>
+        <v>1006.19</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1831.1</v>
+        <v>1830.4</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1873.08</v>
+        <v>1869.02</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1888.21</v>
+        <v>1885.94</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1891.12</v>
+        <v>1890.51</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1037.7</v>
+        <v>1077</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1102.92</v>
+        <v>1100.45</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1116.61</v>
+        <v>1115.06</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1229.51</v>
+        <v>1228</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3107</v>
+        <v>3029.5</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3241.65</v>
+        <v>3221.44</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3254.1</v>
+        <v>3245.29</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3248.21</v>
+        <v>3246.04</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3930.7</v>
+        <v>3850.7</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3990.53</v>
+        <v>3977.21</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3993.42</v>
+        <v>3987.82</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3932.17</v>
+        <v>3931.36</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1246</v>
+        <v>1222.9</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1252.35</v>
+        <v>1249.54</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1262.79</v>
+        <v>1261.22</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1268.88</v>
+        <v>1268.42</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>183</v>
+        <v>183.65</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>185.86</v>
+        <v>185.65</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.8</v>
+        <v>187.64</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.5</v>
+        <v>187.46</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,24 +1281,24 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>323.5</v>
+        <v>315.25</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>321.73</v>
+        <v>321.11</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>307.95</v>
+        <v>308.23</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>283.3</v>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>283.61</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1901.04</v>
+        <v>1894.75</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1904.1</v>
+        <v>1901.39</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1818.98</v>
+        <v>1819.14</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1037.7</v>
+        <v>1030</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1020.89</v>
+        <v>1021.76</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1037.73</v>
+        <v>1037.42</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1058.8</v>
+        <v>1058.51</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1413,24 +1413,24 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>419</v>
+        <v>409.8</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>412.99</v>
+        <v>412.69</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>402.98</v>
+        <v>403.25</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>399.77</v>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>399.87</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1457,24 +1457,24 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>333.4</v>
+        <v>329.5</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>332.99</v>
+        <v>332.66</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>339.31</v>
+        <v>338.93</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>348.76</v>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>348.57</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1034.5</v>
+        <v>1009.2</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1062.18</v>
+        <v>1057.14</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1051.74</v>
+        <v>1050.07</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>991.9299999999999</v>
+        <v>992.1</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>981.5</v>
+        <v>958.7</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1017.89</v>
+        <v>1012.25</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1013.08</v>
+        <v>1010.95</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>954.16</v>
+        <v>954.2</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,29 +1589,29 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>3060</v>
+        <v>2928.6</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>3010.72</v>
+        <v>3002.9</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2996.94</v>
+        <v>2994.26</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2704.66</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2706.88</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>404.35</v>
+        <v>382.9</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>407.23</v>
+        <v>404.91</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>408.09</v>
+        <v>407.1</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>412.81</v>
+        <v>412.51</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12400</v>
+        <v>12231</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>13074.19</v>
+        <v>12993.88</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13361.94</v>
+        <v>13317.59</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13714.87</v>
+        <v>13700.11</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>426.4</v>
+        <v>419.25</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>413.29</v>
+        <v>413.86</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>414.3</v>
+        <v>414.5</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.7</v>
+        <v>413.75</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1765,29 +1765,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1764.6</v>
+        <v>1713.8</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1712.7</v>
+        <v>1712.8</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1722.55</v>
+        <v>1722.21</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1638.52</v>
+        <v>1639.27</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1809,29 +1809,29 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8836</v>
+        <v>8714</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8809.74</v>
+        <v>8800.620000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8741.66</v>
+        <v>8740.58</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8151.55</v>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>8157.15</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>259.85</v>
+        <v>258</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>266.49</v>
+        <v>265.68</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>274.2</v>
+        <v>273.56</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>304.64</v>
+        <v>304.18</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1028.6</v>
+        <v>979.8</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1064.88</v>
+        <v>1056.78</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1061.26</v>
+        <v>1058.06</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>973.08</v>
+        <v>973.15</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,29 +1941,29 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1541</v>
+        <v>1575.9</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1579.15</v>
+        <v>1578.84</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1562.42</v>
+        <v>1562.95</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1496.48</v>
+        <v>1497.27</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4973</v>
+        <v>4776</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>5092.02</v>
+        <v>5061.92</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5108.4</v>
+        <v>5095.36</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5032.1</v>
+        <v>5029.55</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1927</v>
+        <v>1938.1</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1996.37</v>
+        <v>1990.82</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2054.23</v>
+        <v>2049.67</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2182.64</v>
+        <v>2180.2</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2472.5</v>
+        <v>2402.8</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2571.15</v>
+        <v>2555.11</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2621.86</v>
+        <v>2613.27</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2566.12</v>
+        <v>2564.5</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11000</v>
+        <v>10697</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11338.15</v>
+        <v>11277.09</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11456.72</v>
+        <v>11426.93</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11509.4</v>
+        <v>11501.32</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>229.9</v>
+        <v>225.6</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>238.64</v>
+        <v>237.4</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>241.46</v>
+        <v>240.84</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>254.5</v>
+        <v>254.22</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>301.1</v>
+        <v>303.6</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>313.79</v>
+        <v>312.82</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>326.79</v>
+        <v>325.88</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>378.69</v>
+        <v>377.94</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7530</v>
+        <v>7452.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7820.25</v>
+        <v>7785.22</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7741.17</v>
+        <v>7729.85</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7262.14</v>
+        <v>7264.04</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,29 +2293,29 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>5009.5</v>
+        <v>4856</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>5025.17</v>
+        <v>5009.06</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4882.7</v>
+        <v>4881.65</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4396.38</v>
+        <v>4400.95</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2802.4</v>
+        <v>2730</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2870.67</v>
+        <v>2857.27</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2914.21</v>
+        <v>2906.99</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3223.44</v>
+        <v>3218.53</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,24 +2381,24 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>269.1</v>
+        <v>262.8</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>268.57</v>
+        <v>268.02</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>274.65</v>
+        <v>274.19</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>283.47</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>283.27</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -2425,29 +2425,29 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3281.9</v>
+        <v>3171</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3288.45</v>
+        <v>3277.27</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3226.12</v>
+        <v>3223.96</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3004.61</v>
+        <v>3006.27</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
@@ -2469,24 +2469,24 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>232.5</v>
+        <v>235.95</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>235.26</v>
+        <v>235.33</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>239.95</v>
+        <v>239.79</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>249.21</v>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>249.08</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1206.1</v>
+        <v>1253.7</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1284.04</v>
+        <v>1281.15</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1274.26</v>
+        <v>1273.45</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1317.07</v>
+        <v>1316.44</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1383.3</v>
+        <v>1362</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1432.01</v>
+        <v>1425.34</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1444.22</v>
+        <v>1440.99</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1367.73</v>
+        <v>1367.67</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2582,9 +2582,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1265</v>
+        <v>1229.2</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1300.95</v>
+        <v>1294.11</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1286.91</v>
+        <v>1284.64</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1226.83</v>
+        <v>1226.86</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>530</v>
+        <v>516.1</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>537.41</v>
+        <v>535.38</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>549.11</v>
+        <v>547.8200000000001</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>616.34</v>
+        <v>615.34</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11678</v>
+        <v>11424</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11790.52</v>
+        <v>11755.61</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11396.3</v>
+        <v>11397.39</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10221.42</v>
+        <v>10233.39</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1913.5</v>
+        <v>1855.5</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1969.95</v>
+        <v>1959.05</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1947.5</v>
+        <v>1943.89</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1911.81</v>
+        <v>1911.25</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2758,9 +2758,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1165.5</v>
+        <v>1145</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1165</v>
+        <v>1163.09</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1191.8</v>
+        <v>1189.96</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1238.6</v>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1237.67</v>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1366</v>
+        <v>1351</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1405.6</v>
+        <v>1400.4</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1416.09</v>
+        <v>1413.54</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1405.19</v>
+        <v>1404.65</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>991</v>
+        <v>986.1</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1030.71</v>
+        <v>1026.46</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1062.36</v>
+        <v>1059.37</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1103.76</v>
+        <v>1102.59</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1684.7</v>
+        <v>1654.1</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1744.78</v>
+        <v>1736.14</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1783.92</v>
+        <v>1778.83</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1847.29</v>
+        <v>1845.37</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 15-Sep-2026  15:25:31    |    Closing Price Date: 15-Sep-2026</t>
+          <t>Scan Run: 16-Sep-2026  15:18:35    |    Closing Price Date: 16-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>15-Sep-2026  15:25:31</t>
+          <t>16-Sep-2026  15:18:35</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 12.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 12.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 5 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 6 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 5 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 6 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 16 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 17 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1235.3</v>
+        <v>1240</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1290.18</v>
+        <v>1282.4</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1301.35</v>
+        <v>1297.26</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1352.66</v>
+        <v>1350.6</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>716.55</v>
+        <v>721.5</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>713.91</v>
+        <v>714.21</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>733.78</v>
+        <v>732.34</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>805.28</v>
+        <v>803.49</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2251</v>
+        <v>2188.8</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2282.25</v>
+        <v>2266.74</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2287.11</v>
+        <v>2280.08</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2477.65</v>
+        <v>2472.05</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>170</v>
+        <v>166.89</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>174.94</v>
+        <v>173.55</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>178.49</v>
+        <v>177.62</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>197.33</v>
+        <v>196.74</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1350.4</v>
+        <v>1358.8</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1407.65</v>
+        <v>1400.32</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1402.21</v>
+        <v>1399.6</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1364.95</v>
+        <v>1365.03</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>968</v>
+        <v>991.4</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1021.34</v>
+        <v>1016.05</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1030.87</v>
+        <v>1027.95</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1006.19</v>
+        <v>1005.94</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1830.4</v>
+        <v>1835</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1869.02</v>
+        <v>1862.51</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1885.94</v>
+        <v>1881.88</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1890.51</v>
+        <v>1889.37</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1077</v>
+        <v>1060</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1100.45</v>
+        <v>1091.52</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1115.06</v>
+        <v>1110.04</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1228</v>
+        <v>1224.45</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3029.5</v>
+        <v>3070</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3221.44</v>
+        <v>3196.52</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3245.29</v>
+        <v>3233.09</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3246.04</v>
+        <v>3242.91</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3850.7</v>
+        <v>3807.7</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3977.21</v>
+        <v>3956.4</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3987.82</v>
+        <v>3978.49</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3931.36</v>
+        <v>3930.11</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1222.9</v>
+        <v>1241</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1249.54</v>
+        <v>1248.24</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1261.22</v>
+        <v>1259.82</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1268.42</v>
+        <v>1267.93</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>183.65</v>
+        <v>183</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>185.65</v>
+        <v>185.17</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.64</v>
+        <v>187.28</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.46</v>
+        <v>187.37</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>315.25</v>
+        <v>317</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>321.11</v>
+        <v>320.86</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>308.23</v>
+        <v>309.14</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>283.61</v>
+        <v>284.34</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1835</v>
+        <v>1853.5</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1894.75</v>
+        <v>1886.07</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1901.39</v>
+        <v>1897.19</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1819.14</v>
+        <v>1819.69</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1021.76</v>
+        <v>1022.07</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1037.42</v>
+        <v>1036.94</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1058.51</v>
+        <v>1058.18</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1413,24 +1413,24 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>409.8</v>
+        <v>415</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>412.69</v>
+        <v>413.38</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>403.25</v>
+        <v>404.29</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>399.87</v>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>400.21</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>329.5</v>
+        <v>327</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>332.66</v>
+        <v>332.15</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>338.93</v>
+        <v>338.24</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>348.57</v>
+        <v>348.2</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1009.2</v>
+        <v>1006.2</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1057.14</v>
+        <v>1050.13</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1050.07</v>
+        <v>1047.73</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>992.1</v>
+        <v>992.65</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>958.7</v>
+        <v>972.7</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1012.25</v>
+        <v>1005.65</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1010.95</v>
+        <v>1008.3</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>954.2</v>
+        <v>954.65</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2928.6</v>
+        <v>2920</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>3002.9</v>
+        <v>2998.85</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2994.26</v>
+        <v>2993.63</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2706.88</v>
+        <v>2712.47</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>382.9</v>
+        <v>385.75</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>404.91</v>
+        <v>402.86</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>407.1</v>
+        <v>406.13</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>412.51</v>
+        <v>412.17</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12231</v>
+        <v>12166</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12993.88</v>
+        <v>12862.48</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13317.59</v>
+        <v>13237.61</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13700.11</v>
+        <v>13672.02</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>419.25</v>
+        <v>422.25</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>413.86</v>
+        <v>415.68</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>414.5</v>
+        <v>415.24</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.75</v>
+        <v>413.96</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1765,29 +1765,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1713.8</v>
+        <v>1723.8</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1712.8</v>
+        <v>1717.9</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1722.21</v>
+        <v>1723.79</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1639.27</v>
+        <v>1641.34</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8714</v>
+        <v>8696.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8800.620000000001</v>
+        <v>8792.75</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8740.58</v>
+        <v>8742.26</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8157.15</v>
+        <v>8169.19</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>258</v>
+        <v>264.15</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>265.68</v>
+        <v>265.02</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>273.56</v>
+        <v>272.68</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>304.18</v>
+        <v>303.34</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>979.8</v>
+        <v>979</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1056.78</v>
+        <v>1046.54</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1058.06</v>
+        <v>1053.78</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>973.15</v>
+        <v>973.75</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,29 +1941,29 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1575.9</v>
+        <v>1558</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1578.84</v>
+        <v>1576.86</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1562.95</v>
+        <v>1562.75</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1497.27</v>
+        <v>1497.87</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4776</v>
+        <v>4733.5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>5061.92</v>
+        <v>5021.36</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5095.36</v>
+        <v>5076.27</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5029.55</v>
+        <v>5026.03</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1938.1</v>
+        <v>1962</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1990.82</v>
+        <v>1982.67</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2049.67</v>
+        <v>2041.63</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2180.2</v>
+        <v>2175.54</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2402.8</v>
+        <v>2416.6</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2555.11</v>
+        <v>2534.23</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2613.27</v>
+        <v>2600.15</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2564.5</v>
+        <v>2562.11</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10697</v>
+        <v>10700</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11277.09</v>
+        <v>11195.76</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11426.93</v>
+        <v>11381.89</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11501.32</v>
+        <v>11488.37</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>225.6</v>
+        <v>224.84</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>237.4</v>
+        <v>235.52</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>240.84</v>
+        <v>239.79</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>254.22</v>
+        <v>253.68</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>303.6</v>
+        <v>301</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>312.82</v>
+        <v>310.7</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>325.88</v>
+        <v>323.97</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>377.94</v>
+        <v>376.42</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7452.5</v>
+        <v>7500</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7785.22</v>
+        <v>7758.06</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7729.85</v>
+        <v>7720.83</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7264.04</v>
+        <v>7266.38</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,29 +2293,29 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4856</v>
+        <v>4908.5</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>5009.06</v>
+        <v>4998.26</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4881.65</v>
+        <v>4887.3</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4400.95</v>
+        <v>4411.98</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2730</v>
+        <v>2769.7</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2857.27</v>
+        <v>2843.61</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2906.99</v>
+        <v>2897.55</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3218.53</v>
+        <v>3209.96</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
         <v>262.8</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>268.02</v>
+        <v>267.57</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>274.19</v>
+        <v>273.54</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>283.27</v>
+        <v>282.92</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3171</v>
+        <v>3187</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3277.27</v>
+        <v>3268.16</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3223.96</v>
+        <v>3224.53</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3006.27</v>
+        <v>3010.77</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>235.95</v>
+        <v>236.8</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>235.33</v>
+        <v>235.25</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>239.79</v>
+        <v>239.4</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>249.08</v>
+        <v>248.8</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1253.7</v>
+        <v>1253</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1281.15</v>
+        <v>1272.39</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1273.45</v>
+        <v>1270.18</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1316.44</v>
+        <v>1314.73</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1362</v>
+        <v>1384.5</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1425.34</v>
+        <v>1417.65</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1440.99</v>
+        <v>1436.57</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1367.67</v>
+        <v>1367.99</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2582,9 +2582,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1229.2</v>
+        <v>1248.9</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1294.11</v>
+        <v>1287.01</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1284.64</v>
+        <v>1282.45</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1226.86</v>
+        <v>1227.45</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>516.1</v>
+        <v>530.2</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>535.38</v>
+        <v>534.3099999999999</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>547.8200000000001</v>
+        <v>546.4299999999999</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>615.34</v>
+        <v>613.65</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11424</v>
+        <v>11593</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11755.61</v>
+        <v>11731.35</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11397.39</v>
+        <v>11415.26</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10233.39</v>
+        <v>10261.12</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1855.5</v>
+        <v>1837</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1959.05</v>
+        <v>1947.43</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1943.89</v>
+        <v>1939.7</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1911.25</v>
+        <v>1910.51</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1163.09</v>
+        <v>1160.93</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1189.96</v>
+        <v>1187.05</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1237.67</v>
+        <v>1235.99</v>
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1400.4</v>
+        <v>1393.28</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1413.54</v>
+        <v>1409.55</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1404.65</v>
+        <v>1403.81</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>986.1</v>
+        <v>1000.1</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1026.46</v>
+        <v>1020.85</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1059.37</v>
+        <v>1054.46</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1102.59</v>
+        <v>1100.47</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>16-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1654.1</v>
+        <v>1697.9</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1736.14</v>
+        <v>1727.82</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1778.83</v>
+        <v>1772.07</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1845.37</v>
+        <v>1842.31</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 16-Sep-2026  15:18:35    |    Closing Price Date: 16-Sep-2026</t>
+          <t>Scan Run: 17-Sep-2026  15:24:47    |    Closing Price Date: 17-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>34</v>
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>16-Sep-2026  15:18:35</t>
+          <t>17-Sep-2026  15:24:47</t>
         </is>
       </c>
     </row>
@@ -617,14 +617,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 12.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 12.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,14 +645,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 6 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 6 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 9 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1240</v>
+        <v>1243.9</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1282.4</v>
+        <v>1278.74</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1297.26</v>
+        <v>1295.17</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1350.6</v>
+        <v>1349.13</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,24 +797,24 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>721.5</v>
+        <v>713</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>714.21</v>
+        <v>714.1</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>732.34</v>
+        <v>731.59</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>803.49</v>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>802.3200000000001</v>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2188.8</v>
+        <v>2190</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2266.74</v>
+        <v>2259.43</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2280.08</v>
+        <v>2276.54</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2472.05</v>
+        <v>2470.83</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>166.89</v>
+        <v>166.4</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>173.55</v>
+        <v>172.87</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>177.62</v>
+        <v>177.18</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>196.74</v>
+        <v>196.57</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1358.8</v>
+        <v>1347.6</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1400.32</v>
+        <v>1395.29</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1399.6</v>
+        <v>1397.56</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1365.03</v>
+        <v>1364.38</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>991.4</v>
+        <v>988.7</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1016.05</v>
+        <v>1013.44</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1027.95</v>
+        <v>1026.41</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1005.94</v>
+        <v>1005.65</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1862.51</v>
+        <v>1859.98</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1881.88</v>
+        <v>1880.08</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1889.37</v>
+        <v>1888.53</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1060</v>
+        <v>1058.6</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1091.52</v>
+        <v>1088.38</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1110.04</v>
+        <v>1108.02</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1224.45</v>
+        <v>1223.7</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3070</v>
+        <v>3076.5</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3196.52</v>
+        <v>3185.09</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3233.09</v>
+        <v>3226.95</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3242.91</v>
+        <v>3240.46</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3807.7</v>
+        <v>3836.2</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3956.4</v>
+        <v>3944.96</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3978.49</v>
+        <v>3972.91</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3930.11</v>
+        <v>3929.21</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1248.24</v>
+        <v>1247.45</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1259.82</v>
+        <v>1259.05</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1267.93</v>
+        <v>1268.17</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,29 +1237,29 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>183</v>
+        <v>187.29</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>185.17</v>
+        <v>185.37</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>187.28</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.37</v>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>187.3</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1281,24 +1281,24 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>317</v>
+        <v>322.35</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>320.86</v>
+        <v>321</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>309.14</v>
+        <v>309.66</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>284.34</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>284.67</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1853.5</v>
+        <v>1867.3</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1886.07</v>
+        <v>1884.28</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1897.19</v>
+        <v>1896.02</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1819.69</v>
+        <v>1819.94</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1025</v>
+        <v>1037</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1022.07</v>
+        <v>1023.49</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>1036.94</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1058.18</v>
+        <v>1057.47</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>415</v>
+        <v>416.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>413.38</v>
+        <v>413.67</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>404.29</v>
+        <v>404.77</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>400.21</v>
+        <v>400.47</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>327</v>
+        <v>329.6</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>332.15</v>
+        <v>331.91</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>338.24</v>
+        <v>337.91</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>348.2</v>
+        <v>348.1</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1006.2</v>
+        <v>1015</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1050.13</v>
+        <v>1046.78</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1047.73</v>
+        <v>1046.45</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>992.65</v>
+        <v>992.4400000000001</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>972.7</v>
+        <v>980.5</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1005.65</v>
+        <v>1003.25</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1008.3</v>
+        <v>1007.21</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>954.65</v>
+        <v>955.21</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2920</v>
+        <v>2923.2</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2998.85</v>
+        <v>2991.64</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2993.63</v>
+        <v>2990.87</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2712.47</v>
+        <v>2715.82</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>385.75</v>
+        <v>395.45</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>402.86</v>
+        <v>402.16</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>406.13</v>
+        <v>405.71</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>412.17</v>
+        <v>412.2</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12166</v>
+        <v>12338</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12862.48</v>
+        <v>12812.53</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13237.61</v>
+        <v>13202.33</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13672.02</v>
+        <v>13654.12</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>422.25</v>
+        <v>418</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>415.68</v>
+        <v>415.9</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>415.24</v>
+        <v>415.35</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.96</v>
+        <v>413.95</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1723.8</v>
+        <v>1738.3</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1717.9</v>
+        <v>1719.84</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1723.79</v>
+        <v>1724.36</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1641.34</v>
+        <v>1642.58</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,29 +1809,29 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8696.5</v>
+        <v>8768.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8792.75</v>
+        <v>8790.440000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8742.26</v>
+        <v>8743.290000000001</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8169.19</v>
+        <v>8174.61</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>264.15</v>
+        <v>266.2</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>265.02</v>
+        <v>265.13</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>272.68</v>
+        <v>272.42</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>303.34</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>303.13</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1046.54</v>
+        <v>1041.63</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1053.78</v>
+        <v>1051.48</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>973.75</v>
+        <v>974.0599999999999</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1576.86</v>
+        <v>1575.35</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1562.75</v>
+        <v>1562.68</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1497.87</v>
+        <v>1499.73</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4733.5</v>
+        <v>4845</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>5021.36</v>
+        <v>5004.57</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5076.27</v>
+        <v>5067.2</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5026.03</v>
+        <v>5020.28</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1962</v>
+        <v>1942.2</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1982.67</v>
+        <v>1978.81</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2041.63</v>
+        <v>2037.73</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2175.54</v>
+        <v>2173.3</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2416.6</v>
+        <v>2454</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2534.23</v>
+        <v>2526.59</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2600.15</v>
+        <v>2594.42</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2562.11</v>
+        <v>2560.7</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10700</v>
+        <v>10764</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11195.76</v>
+        <v>11154.64</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11381.89</v>
+        <v>11357.66</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11488.37</v>
+        <v>11486.32</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>224.84</v>
+        <v>229.3</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>235.52</v>
+        <v>234.93</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>239.79</v>
+        <v>239.38</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>253.68</v>
+        <v>253.38</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,24 +2205,24 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>301</v>
+        <v>314.5</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>310.7</v>
+        <v>311.07</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>323.97</v>
+        <v>323.6</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>376.42</v>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>376.38</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7500</v>
+        <v>7493.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7758.06</v>
+        <v>7732.86</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7720.83</v>
+        <v>7711.92</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7266.38</v>
+        <v>7268.1</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,29 +2293,29 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4908.5</v>
+        <v>4841</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4998.26</v>
+        <v>4983.29</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4887.3</v>
+        <v>4885.48</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4411.98</v>
+        <v>4415.86</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2769.7</v>
+        <v>2789</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2843.61</v>
+        <v>2838.41</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2897.55</v>
+        <v>2893.3</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3209.96</v>
+        <v>3201.76</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>262.8</v>
+        <v>263.75</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>267.57</v>
+        <v>267.2</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>273.54</v>
+        <v>273.16</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>282.92</v>
+        <v>282.75</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3187</v>
+        <v>3173.1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3268.16</v>
+        <v>3259.11</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3224.53</v>
+        <v>3222.51</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3010.77</v>
+        <v>3016.42</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,24 +2469,24 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>236.8</v>
+        <v>232.43</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>235.25</v>
+        <v>234.99</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>239.4</v>
+        <v>239.13</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>248.8</v>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>248.7</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1253</v>
+        <v>1258.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1272.39</v>
+        <v>1271.05</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1270.18</v>
+        <v>1269.71</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1314.73</v>
+        <v>1314.93</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1384.5</v>
+        <v>1370.6</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1417.65</v>
+        <v>1413.17</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1436.57</v>
+        <v>1433.99</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1367.99</v>
+        <v>1368.34</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1248.9</v>
+        <v>1253.4</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1287.01</v>
+        <v>1283.81</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1282.45</v>
+        <v>1281.31</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1227.45</v>
+        <v>1227.51</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,29 +2645,29 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>530.2</v>
+        <v>557</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>534.3099999999999</v>
+        <v>536.47</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>546.4299999999999</v>
+        <v>546.85</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>613.65</v>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>613.17</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11593</v>
+        <v>11500</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11731.35</v>
+        <v>11709.32</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11415.26</v>
+        <v>11418.58</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10261.12</v>
+        <v>10272.87</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1837</v>
+        <v>1859.2</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1947.43</v>
+        <v>1935.04</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1939.7</v>
+        <v>1935.36</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1910.51</v>
+        <v>1909.24</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,24 +2777,24 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1140</v>
+        <v>1175</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1160.93</v>
+        <v>1162.27</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1187.05</v>
+        <v>1186.58</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1235.99</v>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1236.56</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1358</v>
+        <v>1376.3</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1393.28</v>
+        <v>1391.66</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1409.55</v>
+        <v>1408.25</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1403.81</v>
+        <v>1403.7</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1000.1</v>
+        <v>1013.7</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1020.85</v>
+        <v>1020.17</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1054.46</v>
+        <v>1052.86</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1100.47</v>
+        <v>1099.36</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,24 +2909,24 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>16-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1697.9</v>
+        <v>1766.9</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1727.82</v>
+        <v>1731.54</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1772.07</v>
+        <v>1771.86</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1842.31</v>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1841.35</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 17-Sep-2026  15:24:47    |    Closing Price Date: 17-Sep-2026</t>
+          <t>Scan Run: 18-Sep-2026  14:45:26    |    Closing Price Date: 18-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>34</v>
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>17-Sep-2026  15:24:47</t>
+          <t>18-Sep-2026  14:45:26</t>
         </is>
       </c>
     </row>
@@ -617,14 +617,14 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 16.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,14 +645,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 13 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 9 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 8 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1243.9</v>
+        <v>1226.4</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1278.74</v>
+        <v>1273.75</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1295.17</v>
+        <v>1292.47</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1349.13</v>
+        <v>1348.32</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,24 +797,24 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>714.1</v>
+        <v>715.71</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>731.59</v>
+        <v>731.5599999999999</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>802.3200000000001</v>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>801.3200000000001</v>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2190</v>
+        <v>2105</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2259.43</v>
+        <v>2244.73</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2276.54</v>
+        <v>2269.82</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2470.83</v>
+        <v>2467.53</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>166.4</v>
+        <v>166.83</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>172.87</v>
+        <v>172.29</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>177.18</v>
+        <v>176.78</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>196.57</v>
+        <v>196.43</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1347.6</v>
+        <v>1338.9</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1395.29</v>
+        <v>1389.92</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1397.56</v>
+        <v>1395.26</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1364.38</v>
+        <v>1364.45</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>988.7</v>
+        <v>996.2</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1013.44</v>
+        <v>1011.8</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1026.41</v>
+        <v>1025.23</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1005.65</v>
+        <v>1005.47</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,34 +1017,34 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1836</v>
+        <v>1893.3</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1859.98</v>
+        <v>1863.16</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1880.08</v>
+        <v>1880.6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1888.53</v>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1888.7</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1058.6</v>
+        <v>1051.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1088.38</v>
+        <v>1084.86</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1108.02</v>
+        <v>1105.8</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1223.7</v>
+        <v>1223.35</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3076.5</v>
+        <v>3052</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3185.09</v>
+        <v>3172.42</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3226.95</v>
+        <v>3220.09</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3240.46</v>
+        <v>3239.11</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3836.2</v>
+        <v>3885</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3944.96</v>
+        <v>3939.25</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3972.91</v>
+        <v>3969.46</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3929.21</v>
+        <v>3928.97</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,24 +1193,24 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1240</v>
+        <v>1257</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1247.45</v>
+        <v>1248.73</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1259.05</v>
+        <v>1258.96</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1268.17</v>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1267.96</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -1237,29 +1237,29 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>187.29</v>
+        <v>185.54</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>185.37</v>
+        <v>185.39</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.28</v>
+        <v>187.21</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.3</v>
+        <v>187.31</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>322.35</v>
+        <v>326.85</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>321</v>
+        <v>321.53</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>309.66</v>
+        <v>310.75</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>284.67</v>
+        <v>285.5</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1867.3</v>
+        <v>1837.3</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1884.28</v>
+        <v>1879.8</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1896.02</v>
+        <v>1893.72</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1819.94</v>
+        <v>1820.18</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1037</v>
+        <v>1049.3</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1023.49</v>
+        <v>1026.05</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1036.94</v>
+        <v>1036.12</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1057.47</v>
+        <v>1056.76</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1413,24 +1413,24 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>413.67</v>
+        <v>413.56</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>404.77</v>
+        <v>405.07</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>400.47</v>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>400.55</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>329.6</v>
+        <v>323.65</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>331.91</v>
+        <v>331.12</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>337.91</v>
+        <v>337.35</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>348.1</v>
+        <v>347.81</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1015</v>
+        <v>1040.3</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1046.78</v>
+        <v>1049.19</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1046.45</v>
+        <v>1047.44</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>992.4400000000001</v>
+        <v>992.39</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>980.5</v>
+        <v>986.5</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1003.25</v>
+        <v>1003.08</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1007.21</v>
+        <v>1007.22</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>955.21</v>
+        <v>955.64</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,29 +1589,29 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2923.2</v>
+        <v>3020</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2991.64</v>
+        <v>2994.34</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2990.87</v>
+        <v>2992.01</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2715.82</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2717.56</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>395.45</v>
+        <v>393.3</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>402.16</v>
+        <v>401.31</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>405.71</v>
+        <v>405.22</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>412.2</v>
+        <v>411.83</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12338</v>
+        <v>12103</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12812.53</v>
+        <v>12744.95</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13202.33</v>
+        <v>13159.22</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13654.12</v>
+        <v>13636</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,34 +1721,34 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>418</v>
+        <v>409.9</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>415.9</v>
+        <v>415.33</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>415.35</v>
+        <v>415.13</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.95</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>414</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1738.3</v>
+        <v>1824</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1719.84</v>
+        <v>1729.88</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1724.36</v>
+        <v>1727.65</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1642.58</v>
+        <v>1644.24</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,24 +1809,24 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8768.5</v>
+        <v>8944.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8790.440000000001</v>
+        <v>8804.610000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8743.290000000001</v>
+        <v>8752.360000000001</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8174.61</v>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>8188.44</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>266.2</v>
+        <v>262.3</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>265.13</v>
+        <v>264.86</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>272.42</v>
+        <v>272.02</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>303.13</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>302.69</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1041.63</v>
+        <v>1038.62</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1051.48</v>
+        <v>1049.85</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.0599999999999</v>
+        <v>973.84</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1561</v>
+        <v>1537.1</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1575.35</v>
+        <v>1573.07</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1562.68</v>
+        <v>1561.75</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1499.73</v>
+        <v>1500.53</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4845</v>
+        <v>4920</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>5004.57</v>
+        <v>4990.7</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5067.2</v>
+        <v>5057.85</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5020.28</v>
+        <v>5020.32</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1942.2</v>
+        <v>1932</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1978.81</v>
+        <v>1972</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2037.73</v>
+        <v>2030.5</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2173.3</v>
+        <v>2168.05</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2454</v>
+        <v>2451.3</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2526.59</v>
+        <v>2519.42</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2594.42</v>
+        <v>2588.81</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2560.7</v>
+        <v>2559.21</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10764</v>
+        <v>11014</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11154.64</v>
+        <v>11141.25</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11357.66</v>
+        <v>11344.18</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11486.32</v>
+        <v>11484.48</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>229.3</v>
+        <v>229.89</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>234.93</v>
+        <v>234.14</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>239.38</v>
+        <v>238.76</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>253.38</v>
+        <v>252.95</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,24 +2205,24 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>314.5</v>
+        <v>303.8</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>311.07</v>
+        <v>310.37</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>323.6</v>
+        <v>322.82</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>376.38</v>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>375.83</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7493.5</v>
+        <v>7516</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7732.86</v>
+        <v>7685.06</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7711.92</v>
+        <v>7694.96</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7268.1</v>
+        <v>7276.01</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4841</v>
+        <v>4798.5</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4983.29</v>
+        <v>4965.69</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4885.48</v>
+        <v>4882.07</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4415.86</v>
+        <v>4420.37</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2789</v>
+        <v>2824</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2838.41</v>
+        <v>2837.04</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2893.3</v>
+        <v>2890.58</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3201.76</v>
+        <v>3196.5</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,24 +2381,24 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>263.75</v>
+        <v>270.3</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>267.2</v>
+        <v>267.73</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>273.16</v>
+        <v>273.15</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>282.75</v>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>282.43</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3173.1</v>
+        <v>3209.2</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3259.11</v>
+        <v>3263.41</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3222.51</v>
+        <v>3226.47</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3016.42</v>
+        <v>3020.16</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>232.43</v>
+        <v>232.8</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>234.99</v>
+        <v>234.78</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>239.13</v>
+        <v>238.88</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>248.7</v>
+        <v>248.65</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1258.3</v>
+        <v>1249.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1271.05</v>
+        <v>1268.98</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1269.71</v>
+        <v>1268.91</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1314.93</v>
+        <v>1316.33</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1370.6</v>
+        <v>1372.4</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1413.17</v>
+        <v>1413.34</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1433.99</v>
+        <v>1434.06</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1368.34</v>
+        <v>1368.11</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1253.4</v>
+        <v>1275.6</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1283.81</v>
+        <v>1285.92</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1281.31</v>
+        <v>1282.18</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1227.51</v>
+        <v>1227.89</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>557</v>
+        <v>550.95</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>536.47</v>
+        <v>537.85</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>546.85</v>
+        <v>547.01</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>613.17</v>
+        <v>612.62</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -2689,29 +2689,29 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11500</v>
+        <v>11414</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11709.32</v>
+        <v>11701.13</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11418.58</v>
+        <v>11415.21</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10272.87</v>
+        <v>10275.66</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1859.2</v>
+        <v>1852.5</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1935.04</v>
+        <v>1934.4</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1935.36</v>
+        <v>1935.1</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1909.24</v>
+        <v>1909.77</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1162.27</v>
+        <v>1163.22</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1186.58</v>
+        <v>1186.97</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1236.56</v>
+        <v>1236.76</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,24 +2821,24 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1376.3</v>
+        <v>1394.5</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1391.66</v>
+        <v>1392.21</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1408.25</v>
+        <v>1408.14</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1403.7</v>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1404.21</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1013.7</v>
+        <v>996</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1020.17</v>
+        <v>1017.87</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1052.86</v>
+        <v>1050.63</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1099.36</v>
+        <v>1097.9</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,24 +2909,24 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>18-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1766.9</v>
+        <v>1731</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1731.54</v>
+        <v>1731.49</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1771.86</v>
+        <v>1770.26</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1841.35</v>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1840.81</v>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 18-Sep-2026  14:45:26    |    Closing Price Date: 18-Sep-2026</t>
+          <t>Scan Run: 21-Sep-2026  16:45:27    |    Closing Price Date: 21-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>26</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>18-Sep-2026  14:45:26</t>
+          <t>21-Sep-2026  16:45:27</t>
         </is>
       </c>
     </row>
@@ -624,14 +624,14 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 16.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -652,14 +652,14 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 8 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 10 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 17 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 18 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1226.4</v>
+        <v>1247.4</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1273.75</v>
+        <v>1271.24</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1292.47</v>
+        <v>1290.7</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1348.32</v>
+        <v>1346.88</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,29 +797,29 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>731</v>
+        <v>739.5</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>715.71</v>
+        <v>717.97</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>731.5599999999999</v>
+        <v>731.87</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>801.3200000000001</v>
+        <v>800.41</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2105</v>
+        <v>2128.7</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2244.73</v>
+        <v>2233.68</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2269.82</v>
+        <v>2264.28</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2467.53</v>
+        <v>2465.15</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>166.83</v>
+        <v>164.55</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>172.29</v>
+        <v>171.56</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>176.78</v>
+        <v>176.3</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>196.43</v>
+        <v>196.27</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1338.9</v>
+        <v>1345</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1389.92</v>
+        <v>1385.65</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1395.26</v>
+        <v>1393.29</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1364.45</v>
+        <v>1364.1</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>996.2</v>
+        <v>996</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1011.8</v>
+        <v>1010.3</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1025.23</v>
+        <v>1024.08</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1005.47</v>
+        <v>1004.48</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,34 +1017,34 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1893.3</v>
+        <v>1830.2</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1863.16</v>
+        <v>1860.02</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1880.6</v>
+        <v>1878.62</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1888.7</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1888.17</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1051.4</v>
+        <v>1038.5</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1084.86</v>
+        <v>1080.44</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1105.8</v>
+        <v>1103.16</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1223.35</v>
+        <v>1221.25</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3052</v>
+        <v>3055.3</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3172.42</v>
+        <v>3161.26</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3220.09</v>
+        <v>3213.63</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3239.11</v>
+        <v>3235.03</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3885</v>
+        <v>3904.8</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3939.25</v>
+        <v>3935.96</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3969.46</v>
+        <v>3966.93</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3928.97</v>
+        <v>3926.52</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1248.73</v>
+        <v>1248.85</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1258.96</v>
+        <v>1258.61</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1267.96</v>
+        <v>1267.15</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1237,24 +1237,24 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>185.54</v>
+        <v>183.4</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>185.39</v>
+        <v>185.2</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.21</v>
+        <v>187.06</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.31</v>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>187.19</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>326.85</v>
+        <v>335.9</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>321.53</v>
+        <v>322.9</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>310.75</v>
+        <v>311.74</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>285.5</v>
+        <v>285.8</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1837.3</v>
+        <v>1868.9</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1879.8</v>
+        <v>1878.77</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1893.72</v>
+        <v>1892.75</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1820.18</v>
+        <v>1820.45</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1049.3</v>
+        <v>1066.6</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1026.05</v>
+        <v>1029.91</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1036.12</v>
+        <v>1037.32</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1056.76</v>
+        <v>1059.29</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1394,9 +1394,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
@@ -1413,24 +1413,24 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>412.5</v>
+        <v>414.8</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>413.56</v>
+        <v>413.68</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>405.07</v>
+        <v>405.46</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>400.55</v>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>400.64</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>323.65</v>
+        <v>326.4</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>331.12</v>
+        <v>330.67</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>337.35</v>
+        <v>336.92</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>347.81</v>
+        <v>347.43</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1040.3</v>
+        <v>1021.3</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1049.19</v>
+        <v>1043.8</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1047.44</v>
+        <v>1045.23</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>992.39</v>
+        <v>992.73</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>986.5</v>
+        <v>981.2</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1003.08</v>
+        <v>999.1</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1007.22</v>
+        <v>1005.2</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>955.64</v>
+        <v>955.92</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,29 +1589,29 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>3020</v>
+        <v>2975</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2994.34</v>
+        <v>2992.5</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2992.01</v>
+        <v>2991.34</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2717.56</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2718.69</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>393.3</v>
+        <v>398.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>401.31</v>
+        <v>401.05</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>405.22</v>
+        <v>404.96</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>411.83</v>
+        <v>412.15</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12103</v>
+        <v>12153</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12744.95</v>
+        <v>12688.58</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13159.22</v>
+        <v>13119.76</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13636</v>
+        <v>13624.43</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>409.9</v>
+        <v>414.7</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>415.33</v>
+        <v>415.27</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>415.13</v>
+        <v>415.12</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414</v>
+        <v>413.72</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1746,9 +1746,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1824</v>
+        <v>1787.1</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1729.88</v>
+        <v>1735.33</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1727.65</v>
+        <v>1729.98</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1644.24</v>
+        <v>1643.68</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8944.5</v>
+        <v>8912</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8804.610000000001</v>
+        <v>8814.83</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8752.360000000001</v>
+        <v>8758.620000000001</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8188.44</v>
+        <v>8203.23</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>262.3</v>
+        <v>267</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>264.86</v>
+        <v>265.07</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>272.02</v>
+        <v>271.83</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>302.69</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>302.03</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1897,17 +1897,17 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1010</v>
+        <v>1011.8</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1038.62</v>
+        <v>1036.07</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1049.85</v>
+        <v>1048.36</v>
       </c>
       <c r="F28" s="10" t="n">
         <v>973.84</v>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1537.1</v>
+        <v>1558.5</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1573.07</v>
+        <v>1568.25</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1561.75</v>
+        <v>1560.87</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1500.53</v>
+        <v>1504.29</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4920</v>
+        <v>4941</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4990.7</v>
+        <v>4985.97</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5057.85</v>
+        <v>5053.26</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5020.32</v>
+        <v>5009.43</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1932</v>
+        <v>1947</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1972</v>
+        <v>1969.62</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2030.5</v>
+        <v>2027.23</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2168.05</v>
+        <v>2163.93</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2451.3</v>
+        <v>2440.3</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2519.42</v>
+        <v>2511.88</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2588.81</v>
+        <v>2582.98</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2559.21</v>
+        <v>2559.48</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11014</v>
+        <v>11100</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11141.25</v>
+        <v>11137.32</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11344.18</v>
+        <v>11334.61</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11484.48</v>
+        <v>11482.05</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>229.89</v>
+        <v>229.97</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>234.14</v>
+        <v>233.74</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>238.76</v>
+        <v>238.42</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>252.95</v>
+        <v>252.38</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>303.8</v>
+        <v>301.65</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>310.37</v>
+        <v>309.54</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>322.82</v>
+        <v>321.99</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>375.83</v>
+        <v>373.07</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7516</v>
+        <v>7512.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7685.06</v>
+        <v>7668.63</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7694.96</v>
+        <v>7687.81</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7276.01</v>
+        <v>7278.92</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4798.5</v>
+        <v>4875</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4965.69</v>
+        <v>4957.05</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4882.07</v>
+        <v>4881.79</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4420.37</v>
+        <v>4420.74</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2824</v>
+        <v>2815.5</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2837.04</v>
+        <v>2834.99</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2890.58</v>
+        <v>2887.63</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3196.5</v>
+        <v>3188.99</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,24 +2381,24 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>270.3</v>
+        <v>266.1</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>267.73</v>
+        <v>267.29</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>273.15</v>
+        <v>272.53</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>282.43</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>281.82</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3209.2</v>
+        <v>3166</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3263.41</v>
+        <v>3246.65</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3226.47</v>
+        <v>3222.14</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3020.16</v>
+        <v>3022.45</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,24 +2469,24 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>232.8</v>
+        <v>235.63</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>234.78</v>
+        <v>234.86</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>238.88</v>
+        <v>238.75</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>248.65</v>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>248.88</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -2513,29 +2513,29 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1249.3</v>
+        <v>1281</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1268.98</v>
+        <v>1270.12</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1268.91</v>
+        <v>1269.39</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1316.33</v>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H42" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1316.04</v>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1372.4</v>
+        <v>1385</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1413.34</v>
+        <v>1406.98</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1434.06</v>
+        <v>1429.74</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1368.11</v>
+        <v>1367.72</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1275.6</v>
+        <v>1268.6</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1285.92</v>
+        <v>1281.65</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1282.18</v>
+        <v>1280.6</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1227.89</v>
+        <v>1228.43</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>550.95</v>
+        <v>559.4</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>537.85</v>
+        <v>539.9</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>547.01</v>
+        <v>547.49</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>612.62</v>
+        <v>612.36</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -2689,29 +2689,29 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11414</v>
+        <v>11460</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11701.13</v>
+        <v>11660.13</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11415.21</v>
+        <v>11420.03</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10275.66</v>
+        <v>10292.15</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1852.5</v>
+        <v>1849.8</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1934.4</v>
+        <v>1919.81</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1935.1</v>
+        <v>1928.88</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1909.77</v>
+        <v>1909.3</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,29 +2777,29 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1185</v>
+        <v>1198.3</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1163.22</v>
+        <v>1167.66</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1186.97</v>
+        <v>1186.98</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1236.76</v>
+        <v>1235.58</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -2821,24 +2821,24 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1394.5</v>
+        <v>1386.1</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1392.21</v>
+        <v>1390.41</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1408.14</v>
+        <v>1406.1</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1404.21</v>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1403.98</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>996</v>
+        <v>1000.6</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1017.87</v>
+        <v>1016.23</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1050.63</v>
+        <v>1048.67</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1097.9</v>
+        <v>1096.1</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,24 +2909,24 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>18-Sep-2026</t>
+          <t>21-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1731</v>
+        <v>1756</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1731.49</v>
+        <v>1733.82</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1770.26</v>
+        <v>1769.7</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1840.81</v>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1839.93</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 21-Sep-2026  16:45:27    |    Closing Price Date: 21-Sep-2026</t>
+          <t>Scan Run: 22-Sep-2026  15:23:12    |    Closing Price Date: 22-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2026  16:45:27</t>
+          <t>22-Sep-2026  15:23:12</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 13 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 14 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 12 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 18 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 17 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1247.4</v>
+        <v>1240.4</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1271.24</v>
+        <v>1268.31</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1290.7</v>
+        <v>1288.73</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1346.88</v>
+        <v>1345.82</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>739.5</v>
+        <v>738.6</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>717.97</v>
+        <v>719.9400000000001</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>731.87</v>
+        <v>732.14</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>800.41</v>
+        <v>799.8</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2128.7</v>
+        <v>2105</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2233.68</v>
+        <v>2221.42</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2264.28</v>
+        <v>2258.04</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2465.15</v>
+        <v>2461.56</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>164.55</v>
+        <v>166</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>171.56</v>
+        <v>171.03</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>176.3</v>
+        <v>175.89</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>196.27</v>
+        <v>195.97</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1345</v>
+        <v>1339.6</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1385.65</v>
+        <v>1381.26</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1393.29</v>
+        <v>1391.19</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1364.1</v>
+        <v>1363.85</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1010.3</v>
+        <v>1008.08</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1024.08</v>
+        <v>1022.63</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1004.48</v>
+        <v>1004.31</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1830.2</v>
+        <v>1817.2</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1860.02</v>
+        <v>1855.94</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1878.62</v>
+        <v>1876.21</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1888.17</v>
+        <v>1887.47</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1038.5</v>
+        <v>1029.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1080.44</v>
+        <v>1075.58</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1103.16</v>
+        <v>1100.27</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1221.25</v>
+        <v>1219.34</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3055.3</v>
+        <v>3044.5</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3161.26</v>
+        <v>3150.14</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3213.63</v>
+        <v>3207</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3235.03</v>
+        <v>3233.13</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3904.8</v>
+        <v>3866.4</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3935.96</v>
+        <v>3929.34</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3966.93</v>
+        <v>3962.98</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3926.52</v>
+        <v>3925.92</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,24 +1193,24 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1250</v>
+        <v>1242.7</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1248.85</v>
+        <v>1248.27</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1258.61</v>
+        <v>1257.99</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1267.15</v>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1266.9</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>183.4</v>
+        <v>184.97</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>185.2</v>
+        <v>185.18</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.06</v>
+        <v>186.98</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.19</v>
+        <v>187.17</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>335.9</v>
+        <v>342</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>322.9</v>
+        <v>324.72</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>311.74</v>
+        <v>312.92</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>285.8</v>
+        <v>286.36</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1868.9</v>
+        <v>1846.4</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1878.77</v>
+        <v>1875.68</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1892.75</v>
+        <v>1890.93</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1820.45</v>
+        <v>1820.71</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1066.6</v>
+        <v>1056.5</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1029.91</v>
+        <v>1032.44</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1037.32</v>
+        <v>1038.07</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1059.29</v>
+        <v>1059.26</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1394,9 +1394,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
@@ -1413,24 +1413,24 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>414.8</v>
+        <v>412.65</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>413.68</v>
+        <v>413.58</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>405.46</v>
+        <v>405.74</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>400.64</v>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>400.76</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>326.4</v>
+        <v>327.8</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>330.67</v>
+        <v>330.4</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>336.92</v>
+        <v>336.56</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>347.43</v>
+        <v>347.24</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1021.3</v>
+        <v>1008.8</v>
       </c>
       <c r="D19" s="10" t="n">
+        <v>1040.46</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>1043.8</v>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>1045.23</v>
-      </c>
       <c r="F19" s="10" t="n">
-        <v>992.73</v>
+        <v>992.89</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>981.2</v>
+        <v>973</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>999.1</v>
+        <v>996.61</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1005.2</v>
+        <v>1003.94</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>955.92</v>
+        <v>956.09</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,29 +1589,29 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2975</v>
+        <v>2997</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2992.5</v>
+        <v>2992.93</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2991.34</v>
+        <v>2991.56</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2718.69</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2721.45</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>398.5</v>
+        <v>397.9</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>401.05</v>
+        <v>400.75</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>404.96</v>
+        <v>404.68</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>412.15</v>
+        <v>412</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12153</v>
+        <v>12190</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12688.58</v>
+        <v>12641.09</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13119.76</v>
+        <v>13083.3</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13624.43</v>
+        <v>13610.16</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,29 +1721,29 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>414.7</v>
+        <v>428</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>415.27</v>
+        <v>416.48</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>415.12</v>
+        <v>415.62</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.72</v>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>413.87</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I24" s="13" t="inlineStr">
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1787.1</v>
+        <v>1795</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1735.33</v>
+        <v>1741.01</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1729.98</v>
+        <v>1732.53</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1643.68</v>
+        <v>1645.19</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8912</v>
+        <v>8835.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8814.83</v>
+        <v>8816.799999999999</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8758.620000000001</v>
+        <v>8761.639999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8203.23</v>
+        <v>8209.52</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>267</v>
+        <v>265.8</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>265.07</v>
+        <v>265.14</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>271.83</v>
+        <v>271.59</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>302.03</v>
+        <v>301.67</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1011.8</v>
+        <v>1006</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1036.07</v>
+        <v>1033.2</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1048.36</v>
+        <v>1046.7</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>973.84</v>
+        <v>974.16</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1558.5</v>
+        <v>1551.6</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1568.25</v>
+        <v>1566.66</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1560.87</v>
+        <v>1560.5</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1504.29</v>
+        <v>1504.76</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,24 +1985,24 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4941</v>
+        <v>5030</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4985.97</v>
+        <v>4990.16</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5053.26</v>
+        <v>5052.35</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5009.43</v>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5009.63</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -2010,9 +2010,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1947</v>
+        <v>1933.8</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1969.62</v>
+        <v>1966.21</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2027.23</v>
+        <v>2023.56</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2163.93</v>
+        <v>2161.64</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2440.3</v>
+        <v>2448.5</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2511.88</v>
+        <v>2505.85</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2582.98</v>
+        <v>2577.71</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2559.48</v>
+        <v>2558.38</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11137.32</v>
+        <v>11124.24</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11334.61</v>
+        <v>11321.48</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11482.05</v>
+        <v>11477.26</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>229.97</v>
+        <v>230.7</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>233.74</v>
+        <v>233.45</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>238.42</v>
+        <v>238.12</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>252.38</v>
+        <v>252.17</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>301.65</v>
+        <v>300.05</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>309.54</v>
+        <v>308.64</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>321.99</v>
+        <v>321.13</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>373.07</v>
+        <v>372.35</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7512.5</v>
+        <v>7427</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7668.63</v>
+        <v>7645.61</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7687.81</v>
+        <v>7677.58</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7278.92</v>
+        <v>7280.39</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,29 +2293,29 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4875</v>
+        <v>4928.5</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4957.05</v>
+        <v>4954.33</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4881.79</v>
+        <v>4883.63</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4420.74</v>
+        <v>4425.8</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2815.5</v>
+        <v>2782.9</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2834.99</v>
+        <v>2830.03</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2887.63</v>
+        <v>2883.53</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3188.99</v>
+        <v>3184.95</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>266.1</v>
+        <v>265.95</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>267.29</v>
+        <v>267.16</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>272.53</v>
+        <v>272.27</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>281.82</v>
+        <v>281.67</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3166</v>
+        <v>3128.2</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3246.65</v>
+        <v>3235.37</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3222.14</v>
+        <v>3218.46</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3022.45</v>
+        <v>3023.5</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>235.63</v>
+        <v>236.13</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>234.86</v>
+        <v>234.98</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>238.75</v>
+        <v>238.65</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>248.88</v>
+        <v>248.76</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1281</v>
+        <v>1270.4</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1270.12</v>
+        <v>1270.15</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1269.39</v>
+        <v>1269.43</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1316.04</v>
+        <v>1315.59</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1385</v>
+        <v>1363.9</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1406.98</v>
+        <v>1402.87</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1429.74</v>
+        <v>1427.16</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1367.72</v>
+        <v>1367.68</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2582,9 +2582,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1268.6</v>
+        <v>1267</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1281.65</v>
+        <v>1280.26</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1280.6</v>
+        <v>1280.06</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1228.43</v>
+        <v>1228.81</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>559.4</v>
+        <v>559.2</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>539.9</v>
+        <v>541.74</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>547.49</v>
+        <v>547.95</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>612.36</v>
+        <v>611.83</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -2689,29 +2689,29 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11460</v>
+        <v>11363</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11660.13</v>
+        <v>11631.83</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11420.03</v>
+        <v>11417.79</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10292.15</v>
+        <v>10302.81</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1849.8</v>
+        <v>1823.4</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1919.81</v>
+        <v>1910.63</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1928.88</v>
+        <v>1924.75</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1909.3</v>
+        <v>1908.45</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1198.3</v>
+        <v>1211</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1167.66</v>
+        <v>1171.79</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1186.98</v>
+        <v>1187.92</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1235.58</v>
+        <v>1235.34</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1386.1</v>
+        <v>1384.1</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1390.41</v>
+        <v>1389.81</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1406.1</v>
+        <v>1405.24</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1403.98</v>
+        <v>1403.78</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>1000.6</v>
+        <v>984.1</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1016.23</v>
+        <v>1013.17</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1048.67</v>
+        <v>1046.14</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1096.1</v>
+        <v>1094.98</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>21-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1756</v>
+        <v>1756.3</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1733.82</v>
+        <v>1735.96</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1769.7</v>
+        <v>1769.18</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1839.93</v>
+        <v>1839.1</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 24-Sep-2026  15:41:10    |    Closing Price Date: 24-Sep-2026</t>
+          <t>Scan Run: 25-Sep-2026  15:42:52    |    Closing Price Date: 25-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>24-Sep-2026  15:41:10</t>
+          <t>25-Sep-2026  15:42:52</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 12 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 13 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 16 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 17 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1219.2</v>
+        <v>1226</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1261.88</v>
+        <v>1258.46</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1284.47</v>
+        <v>1282.18</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1343.33</v>
+        <v>1342.12</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,29 +797,29 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>728.9</v>
+        <v>735.6</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>722.28</v>
+        <v>723.55</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>732.2</v>
+        <v>732.34</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>798.36</v>
+        <v>797.8200000000001</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2197.26</v>
+        <v>2186.28</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2244.98</v>
+        <v>2238.59</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2454.91</v>
+        <v>2448.73</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>163.64</v>
+        <v>164.02</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>169.8</v>
+        <v>169.25</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>175</v>
+        <v>174.57</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>195.34</v>
+        <v>194.98</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1334.5</v>
+        <v>1326.8</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1373.25</v>
+        <v>1368.83</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1387.04</v>
+        <v>1384.67</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1363.18</v>
+        <v>1362.4</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>978.5</v>
+        <v>983</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1004.06</v>
+        <v>1002.05</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1019.82</v>
+        <v>1018.38</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1003.94</v>
+        <v>1003.72</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1795.8</v>
+        <v>1785.4</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1848.25</v>
+        <v>1842.27</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1871.44</v>
+        <v>1868.06</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1885.76</v>
+        <v>1885.2</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1014.5</v>
+        <v>1000.2</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1065.02</v>
+        <v>1058.85</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1093.9</v>
+        <v>1090.23</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1215.97</v>
+        <v>1213.55</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2982.7</v>
+        <v>3035</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3124.27</v>
+        <v>3115.77</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3191.72</v>
+        <v>3185.58</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3228.04</v>
+        <v>3227.46</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3858.4</v>
+        <v>3876.2</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3922.63</v>
+        <v>3918.21</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3957.64</v>
+        <v>3954.44</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3925.03</v>
+        <v>3923.71</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1186.5</v>
+        <v>1222.4</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1241.95</v>
+        <v>1240.08</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1254.63</v>
+        <v>1253.36</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1265.86</v>
+        <v>1265.66</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>188.02</v>
+        <v>187.97</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>185.93</v>
+        <v>186.13</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.17</v>
+        <v>187.2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.15</v>
+        <v>187.14</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>335.5</v>
+        <v>335</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>327.29</v>
+        <v>328.02</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>314.93</v>
+        <v>315.72</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>287.21</v>
+        <v>287.73</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1849.9</v>
+        <v>1852.2</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1872.31</v>
+        <v>1870.39</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1888.34</v>
+        <v>1886.93</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1820.04</v>
+        <v>1820.27</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1046</v>
+        <v>1014</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1036.1</v>
+        <v>1033.99</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1039.2</v>
+        <v>1038.21</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1058.33</v>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1056.07</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>412.74</v>
+        <v>411.9</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>405.99</v>
+        <v>405.91</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>400.91</v>
+        <v>400.9</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
         <v>326.6</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>329.66</v>
+        <v>329.37</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>335.77</v>
+        <v>335.41</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>346.88</v>
+        <v>346.57</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>982</v>
+        <v>996.9</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1035.13</v>
+        <v>1031.49</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1041.35</v>
+        <v>1039.61</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>992.67</v>
+        <v>992.5599999999999</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1526,9 +1526,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>995.84</v>
+        <v>994.05</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1003.07</v>
+        <v>1002.05</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>956.5</v>
+        <v>956.85</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2900</v>
+        <v>2916.5</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2984.1</v>
+        <v>2977.66</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2988.03</v>
+        <v>2985.23</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2723.67</v>
+        <v>2724.4</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>392</v>
+        <v>393.55</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>399.51</v>
+        <v>398.94</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>403.86</v>
+        <v>403.45</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>411.56</v>
+        <v>411.33</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11990</v>
+        <v>12065</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12543.66</v>
+        <v>12498.07</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>13008.27</v>
+        <v>12971.28</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13583.01</v>
+        <v>13573.95</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>422</v>
+        <v>426.1</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>417.7</v>
+        <v>418.5</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>416.21</v>
+        <v>416.6</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.94</v>
+        <v>414.03</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1785.3</v>
+        <v>1788</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1750.94</v>
+        <v>1754.47</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1737.42</v>
+        <v>1739.4</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1647.84</v>
+        <v>1648.45</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8888.5</v>
+        <v>8889</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8845.360000000001</v>
+        <v>8849.52</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8778.190000000001</v>
+        <v>8782.540000000001</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8220.42</v>
+        <v>8224.139999999999</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>265.84</v>
+        <v>266.14</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>271.4</v>
+        <v>271.3</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>300.99</v>
+        <v>300.61</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>990</v>
+        <v>994.1</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1027.16</v>
+        <v>1024.01</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1043.12</v>
+        <v>1041.2</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.23</v>
+        <v>974.3099999999999</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1563.57</v>
+        <v>1562.09</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1559.69</v>
+        <v>1559.23</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1506.6</v>
+        <v>1506.71</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4890</v>
+        <v>4940</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4983.93</v>
+        <v>4979.74</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5045.09</v>
+        <v>5040.96</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5005.7</v>
+        <v>5003.52</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1933.5</v>
+        <v>1942.9</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1961.7</v>
+        <v>1959.91</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2017.26</v>
+        <v>2014.34</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2157.33</v>
+        <v>2153.97</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2392.7</v>
+        <v>2444</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2490.69</v>
+        <v>2486.24</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2565.83</v>
+        <v>2561.05</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2556.51</v>
+        <v>2556.05</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11056</v>
+        <v>11155</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11120.39</v>
+        <v>11123.69</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11304.8</v>
+        <v>11298.93</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11465.49</v>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>11463.3</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>227.2</v>
+        <v>227</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>232.74</v>
+        <v>232.2</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>237.46</v>
+        <v>237.05</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>251.54</v>
+        <v>251.23</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>295</v>
+        <v>290.45</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>306.64</v>
+        <v>305.1</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>319.33</v>
+        <v>318.2</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>370.39</v>
+        <v>369.42</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7338.5</v>
+        <v>7360</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7601.23</v>
+        <v>7578.26</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7656.46</v>
+        <v>7644.84</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7281.89</v>
+        <v>7284.72</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,29 +2293,29 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4832.5</v>
+        <v>4884</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4936.32</v>
+        <v>4931.34</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4881.48</v>
+        <v>4881.58</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4433.02</v>
+        <v>4439.99</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2700</v>
+        <v>2669.3</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2812.81</v>
+        <v>2799.15</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2872.2</v>
+        <v>2864.25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3173.94</v>
+        <v>3173.29</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,24 +2381,24 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>266.4</v>
+        <v>269.5</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>267.35</v>
+        <v>267.5</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>271.96</v>
+        <v>271.5</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>280.26</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3166.5</v>
+        <v>3191</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3224.77</v>
+        <v>3221.55</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3215.29</v>
+        <v>3214.34</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3025.21</v>
+        <v>3027.02</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,29 +2469,29 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>239</v>
+        <v>235.86</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>235.53</v>
+        <v>235.56</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>238.6</v>
+        <v>238.49</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>248.37</v>
+        <v>248.17</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1243.6</v>
+        <v>1258</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1266.46</v>
+        <v>1265.66</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1267.94</v>
+        <v>1267.55</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1314.55</v>
+        <v>1313.46</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1351</v>
+        <v>1362.6</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1396.58</v>
+        <v>1393.35</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1422.67</v>
+        <v>1420.31</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1367.16</v>
+        <v>1366.69</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1273.2</v>
+        <v>1277</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1281.1</v>
+        <v>1280.71</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1280.46</v>
+        <v>1280.33</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1229.77</v>
+        <v>1229.71</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>526.9</v>
+        <v>531</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>542.03</v>
+        <v>540.98</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>547.64</v>
+        <v>546.99</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>610.63</v>
+        <v>609.53</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11208</v>
+        <v>11281</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11571.49</v>
+        <v>11543.82</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11408.9</v>
+        <v>11403.88</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10321.27</v>
+        <v>10329.79</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1762.3</v>
+        <v>1771</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1890.98</v>
+        <v>1879.55</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1915.43</v>
+        <v>1909.76</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1905.38</v>
+        <v>1903.16</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1200.4</v>
+        <v>1201</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1177.91</v>
+        <v>1180.11</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1189.29</v>
+        <v>1189.75</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1233.64</v>
+        <v>1233.09</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1399</v>
+        <v>1399.7</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1390.1</v>
+        <v>1391.01</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1404.16</v>
+        <v>1403.98</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1402.6</v>
+        <v>1402.36</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>986.3</v>
+        <v>983.2</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1008.98</v>
+        <v>1006.53</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1041.84</v>
+        <v>1039.54</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1092.44</v>
+        <v>1091.1</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>24-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1755</v>
+        <v>1742</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1739.85</v>
+        <v>1740.05</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1768.28</v>
+        <v>1767.25</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1837.58</v>
+        <v>1836.51</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 25-Sep-2026  15:42:52    |    Closing Price Date: 25-Sep-2026</t>
+          <t>Scan Run: 28-Sep-2026  18:23:08    |    Closing Price Date: 28-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>26</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>34</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>25-Sep-2026  15:42:52</t>
+          <t>28-Sep-2026  18:23:08</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 16.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 13 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 5 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 8 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 5 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 17 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 13 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1226</v>
+        <v>1197.6</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1258.46</v>
+        <v>1252.67</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1282.18</v>
+        <v>1278.86</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1342.12</v>
+        <v>1341.75</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,29 +797,29 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>735.6</v>
+        <v>719.05</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>723.55</v>
+        <v>723.12</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>732.34</v>
+        <v>731.8200000000001</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>797.8200000000001</v>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>797.3200000000001</v>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2082</v>
+        <v>2070.7</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2186.28</v>
+        <v>2175.28</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2238.59</v>
+        <v>2232.01</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2448.73</v>
+        <v>2442.71</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>164.02</v>
+        <v>161.56</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>169.25</v>
+        <v>168.51</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>174.57</v>
+        <v>174.06</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>194.98</v>
+        <v>194.7</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1326.8</v>
+        <v>1302</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1368.83</v>
+        <v>1362.46</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1384.67</v>
+        <v>1381.43</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1362.4</v>
+        <v>1362.09</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>983</v>
+        <v>962</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1002.05</v>
+        <v>998.24</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1018.38</v>
+        <v>1016.17</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1003.72</v>
+        <v>1003.23</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1785.4</v>
+        <v>1771.4</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1842.27</v>
+        <v>1835.52</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1868.06</v>
+        <v>1864.27</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1885.2</v>
+        <v>1886.88</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1000.2</v>
+        <v>1003.2</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1058.85</v>
+        <v>1053.55</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1090.23</v>
+        <v>1086.81</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1213.55</v>
+        <v>1209.52</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3035</v>
+        <v>2995</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3115.77</v>
+        <v>3104.27</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3185.58</v>
+        <v>3178.1</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3227.46</v>
+        <v>3228.87</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3876.2</v>
+        <v>3766.4</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3918.21</v>
+        <v>3903.75</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3954.44</v>
+        <v>3947.07</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3923.71</v>
+        <v>3921.39</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1222.4</v>
+        <v>1209.9</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1240.08</v>
+        <v>1237.21</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1253.36</v>
+        <v>1251.66</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1265.66</v>
+        <v>1264.83</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,17 +1237,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>187.97</v>
+        <v>186.3</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>186.13</v>
+        <v>186.14</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.2</v>
+        <v>187.16</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>187.14</v>
@@ -1257,14 +1257,14 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>335</v>
+        <v>330.95</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>328.02</v>
+        <v>328.3</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>315.72</v>
+        <v>316.31</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>287.73</v>
+        <v>288.42</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1852.2</v>
+        <v>1838</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1870.39</v>
+        <v>1867.31</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1886.93</v>
+        <v>1885.01</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1820.27</v>
+        <v>1821.03</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1014</v>
+        <v>1000.1</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1033.99</v>
+        <v>1030.77</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1038.21</v>
+        <v>1036.72</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1056.07</v>
+        <v>1055.86</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>404</v>
+        <v>401.55</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>411.9</v>
+        <v>410.92</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>405.91</v>
+        <v>405.74</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>400.9</v>
+        <v>401.33</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>326.6</v>
+        <v>321.1</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>329.37</v>
+        <v>328.58</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>335.41</v>
+        <v>334.85</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>346.57</v>
+        <v>346.32</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>996.9</v>
+        <v>985</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1031.49</v>
+        <v>1027.06</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1039.61</v>
+        <v>1037.47</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>992.5599999999999</v>
+        <v>992.35</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1526,9 +1526,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>977</v>
+        <v>955.9</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>994.05</v>
+        <v>990.41</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1002.05</v>
+        <v>1000.24</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>956.85</v>
+        <v>957.49</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1570,9 +1570,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2916.5</v>
+        <v>2831.1</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2977.66</v>
+        <v>2963.71</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2985.23</v>
+        <v>2979.18</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2724.4</v>
+        <v>2726.01</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>393.55</v>
+        <v>385.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>398.94</v>
+        <v>397.66</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>403.45</v>
+        <v>402.75</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>411.33</v>
+        <v>411.91</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12065</v>
+        <v>12008</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12498.07</v>
+        <v>12451.4</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12971.28</v>
+        <v>12933.51</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13573.95</v>
+        <v>13556.35</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>426.1</v>
+        <v>422.5</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>418.5</v>
+        <v>418.88</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>416.6</v>
+        <v>416.83</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414.03</v>
+        <v>414.19</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1765,24 +1765,24 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1788</v>
+        <v>1743.7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1754.47</v>
+        <v>1753.44</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1739.4</v>
+        <v>1739.57</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1648.45</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1648.69</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8889</v>
+        <v>8860</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8849.52</v>
+        <v>8850.52</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8782.540000000001</v>
+        <v>8785.58</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8224.139999999999</v>
+        <v>8233.42</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>269</v>
+        <v>265.2</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>266.14</v>
+        <v>266.05</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>271.3</v>
+        <v>271.06</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>300.61</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>300.18</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>994.1</v>
+        <v>976.3</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1024.01</v>
+        <v>1019.47</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1041.2</v>
+        <v>1038.65</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.3099999999999</v>
+        <v>974.3200000000001</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1548</v>
+        <v>1542.2</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1562.09</v>
+        <v>1560.2</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1559.23</v>
+        <v>1558.56</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1506.71</v>
+        <v>1505.95</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4940</v>
+        <v>4874.5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4979.74</v>
+        <v>4969.72</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5040.96</v>
+        <v>5034.44</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5003.52</v>
+        <v>5010.24</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1942.9</v>
+        <v>1896</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1959.91</v>
+        <v>1953.82</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2014.34</v>
+        <v>2009.7</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2153.97</v>
+        <v>2151.47</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2444</v>
+        <v>2420</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2486.24</v>
+        <v>2479.93</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2561.05</v>
+        <v>2555.52</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2556.05</v>
+        <v>2554</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11155</v>
+        <v>11025</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11123.69</v>
+        <v>11114.29</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11298.93</v>
+        <v>11288.18</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11463.3</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>11460.64</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>227</v>
+        <v>220.5</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>232.2</v>
+        <v>231.08</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>237.05</v>
+        <v>236.4</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>251.23</v>
+        <v>251.13</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>290.45</v>
+        <v>281.75</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>305.1</v>
+        <v>302.87</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>318.2</v>
+        <v>316.77</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>369.42</v>
+        <v>368.58</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7360</v>
+        <v>7213.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7578.26</v>
+        <v>7543.52</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7644.84</v>
+        <v>7627.92</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7284.72</v>
+        <v>7290.33</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2274,9 +2274,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J36" s="12" t="inlineStr">
@@ -2293,29 +2293,29 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4884</v>
+        <v>4819.5</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4931.34</v>
+        <v>4920.69</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4881.58</v>
+        <v>4879.15</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4439.99</v>
+        <v>4445.29</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2669.3</v>
+        <v>2626</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2799.15</v>
+        <v>2782.66</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2864.25</v>
+        <v>2854.9</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3173.29</v>
+        <v>3183.61</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,24 +2381,24 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>269.5</v>
+        <v>261.85</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>267.5</v>
+        <v>266.96</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>271.5</v>
+        <v>271.12</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>280.26</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>280.2</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3191</v>
+        <v>3150</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3221.55</v>
+        <v>3214.74</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3214.34</v>
+        <v>3211.82</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3027.02</v>
+        <v>3030.19</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,24 +2469,24 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>235.86</v>
+        <v>230</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>235.56</v>
+        <v>235.03</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>238.49</v>
+        <v>238.16</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>248.17</v>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>248.03</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1258</v>
+        <v>1252.6</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1265.66</v>
+        <v>1264.41</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1267.55</v>
+        <v>1266.96</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1313.46</v>
+        <v>1312.35</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1362.6</v>
+        <v>1346</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1393.35</v>
+        <v>1388.84</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1420.31</v>
+        <v>1417.4</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1366.69</v>
+        <v>1366.86</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1277</v>
+        <v>1264.1</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1280.71</v>
+        <v>1279.12</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1280.33</v>
+        <v>1279.69</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1229.71</v>
+        <v>1230.47</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>531</v>
+        <v>531.6</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>540.98</v>
+        <v>540.09</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>546.99</v>
+        <v>546.38</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>609.53</v>
+        <v>609.16</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11281</v>
+        <v>11024</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11543.82</v>
+        <v>11494.32</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11403.88</v>
+        <v>11388.98</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10329.79</v>
+        <v>10337.77</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1771</v>
+        <v>1752</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1879.55</v>
+        <v>1867.4</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1909.76</v>
+        <v>1903.58</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1903.16</v>
+        <v>1902.32</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1201</v>
+        <v>1221</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1180.11</v>
+        <v>1184</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1189.75</v>
+        <v>1190.97</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1233.09</v>
+        <v>1233.15</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,24 +2821,24 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1399.7</v>
+        <v>1383.7</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1391.01</v>
+        <v>1390.31</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1403.98</v>
+        <v>1403.19</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1402.36</v>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1402.22</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>983.2</v>
+        <v>960</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1006.53</v>
+        <v>1002.1</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1039.54</v>
+        <v>1036.42</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1091.1</v>
+        <v>1091.57</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,24 +2909,24 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1742</v>
+        <v>1728.1</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1740.05</v>
+        <v>1738.91</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1767.25</v>
+        <v>1765.71</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1836.51</v>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1836.31</v>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 28-Sep-2026  18:23:08    |    Closing Price Date: 28-Sep-2026</t>
+          <t>Scan Run: 29-Sep-2026  16:45:57    |    Closing Price Date: 29-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>28-Sep-2026  18:23:08</t>
+          <t>29-Sep-2026  16:45:57</t>
         </is>
       </c>
     </row>
@@ -624,14 +624,14 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 12.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -652,14 +652,14 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 5 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 6 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 13 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 14 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1197.6</v>
+        <v>1182</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1252.67</v>
+        <v>1245.94</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1278.86</v>
+        <v>1275.06</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1341.75</v>
+        <v>1340.16</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>719.05</v>
+        <v>722.7</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>723.12</v>
+        <v>723.08</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>731.8200000000001</v>
+        <v>731.46</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>797.3200000000001</v>
+        <v>796.58</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2070.7</v>
+        <v>2032.4</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2175.28</v>
+        <v>2161.67</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2232.01</v>
+        <v>2224.18</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2442.71</v>
+        <v>2438.62</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>161.56</v>
+        <v>156.79</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>168.51</v>
+        <v>167.4</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>174.06</v>
+        <v>173.38</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>194.7</v>
+        <v>194.33</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1302</v>
+        <v>1292.2</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1362.46</v>
+        <v>1355.77</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1381.43</v>
+        <v>1377.93</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1362.09</v>
+        <v>1361.4</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>962</v>
+        <v>964.7</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>998.24</v>
+        <v>995.04</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1016.17</v>
+        <v>1014.15</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1003.23</v>
+        <v>1002.85</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1771.4</v>
+        <v>1771.2</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1835.52</v>
+        <v>1829.39</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1864.27</v>
+        <v>1860.62</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1886.88</v>
+        <v>1885.73</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1003.2</v>
+        <v>1015.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1053.55</v>
+        <v>1049.91</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1086.81</v>
+        <v>1084.01</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1209.52</v>
+        <v>1207.59</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2995</v>
+        <v>2947.8</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3104.27</v>
+        <v>3089.37</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3178.1</v>
+        <v>3169.07</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3228.87</v>
+        <v>3226.07</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3766.4</v>
+        <v>3749.1</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3903.75</v>
+        <v>3889.02</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3947.07</v>
+        <v>3939.3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3921.39</v>
+        <v>3919.68</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1209.9</v>
+        <v>1212.1</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1237.21</v>
+        <v>1234.82</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1251.66</v>
+        <v>1250.11</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1264.83</v>
+        <v>1264.3</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,34 +1237,34 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>186.3</v>
+        <v>188</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>186.14</v>
+        <v>186.32</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.16</v>
+        <v>187.2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.14</v>
+        <v>187.15</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -1281,24 +1281,24 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>330.95</v>
+        <v>327.85</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>328.3</v>
+        <v>328.26</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>316.31</v>
+        <v>316.77</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>288.42</v>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>288.81</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1838</v>
+        <v>1865</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1867.31</v>
+        <v>1867.09</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1885.01</v>
+        <v>1884.22</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1821.03</v>
+        <v>1821.47</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1000.1</v>
+        <v>982.1</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1030.77</v>
+        <v>1026.13</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1036.72</v>
+        <v>1034.58</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1055.86</v>
+        <v>1055.13</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,29 +1413,29 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>401.55</v>
+        <v>406</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>410.92</v>
+        <v>410.45</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>405.74</v>
+        <v>405.75</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>401.33</v>
+        <v>401.38</v>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>321.1</v>
+        <v>323.5</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>328.58</v>
+        <v>328.09</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>334.85</v>
+        <v>334.41</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>346.32</v>
+        <v>346.1</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>985</v>
+        <v>973.8</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1027.06</v>
+        <v>1021.99</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1037.47</v>
+        <v>1034.97</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>992.35</v>
+        <v>992.17</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>955.9</v>
+        <v>955.2</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>990.41</v>
+        <v>987.0599999999999</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1000.24</v>
+        <v>998.47</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>957.49</v>
+        <v>957.47</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,24 +1589,24 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2831.1</v>
+        <v>2972.9</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2963.71</v>
+        <v>2964.58</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2979.18</v>
+        <v>2978.94</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2726.01</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2728.47</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>385.5</v>
+        <v>387.75</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>397.66</v>
+        <v>396.72</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>402.75</v>
+        <v>402.16</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>411.91</v>
+        <v>411.67</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>12008</v>
+        <v>11877</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12451.4</v>
+        <v>12396.7</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12933.51</v>
+        <v>12892.08</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13556.35</v>
+        <v>13539.64</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>422.5</v>
+        <v>425</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>418.88</v>
+        <v>419.46</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>416.83</v>
+        <v>417.15</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414.19</v>
+        <v>414.3</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1765,24 +1765,24 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1743.7</v>
+        <v>1822</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1753.44</v>
+        <v>1759.97</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1739.57</v>
+        <v>1742.8</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1648.69</v>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1650.41</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -1809,29 +1809,29 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8860</v>
+        <v>8659</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8850.52</v>
+        <v>8832.280000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8785.58</v>
+        <v>8780.610000000001</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8233.42</v>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>8237.65</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>265.2</v>
+        <v>265.1</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>266.05</v>
+        <v>265.96</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>271.06</v>
+        <v>270.83</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>300.18</v>
+        <v>299.83</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>976.3</v>
+        <v>971.5</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1019.47</v>
+        <v>1014.9</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1038.65</v>
+        <v>1036.02</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.3200000000001</v>
+        <v>974.29</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1922,9 +1922,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1542.2</v>
+        <v>1510.5</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1560.2</v>
+        <v>1555.46</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1558.56</v>
+        <v>1556.68</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1505.95</v>
+        <v>1505.99</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4874.5</v>
+        <v>4872</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4969.72</v>
+        <v>4960.41</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5034.44</v>
+        <v>5028.07</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5010.24</v>
+        <v>5008.87</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1896</v>
+        <v>1863.8</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1953.82</v>
+        <v>1945.25</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2009.7</v>
+        <v>2003.98</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2151.47</v>
+        <v>2148.6</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2420</v>
+        <v>2415</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2479.93</v>
+        <v>2473.75</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2555.52</v>
+        <v>2550.01</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2554</v>
+        <v>2552.62</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11025</v>
+        <v>10829</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11114.29</v>
+        <v>11087.12</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11288.18</v>
+        <v>11270.18</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11460.64</v>
+        <v>11454.35</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>220.5</v>
+        <v>217.56</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>231.08</v>
+        <v>229.79</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>236.4</v>
+        <v>235.67</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>251.13</v>
+        <v>250.8</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>281.75</v>
+        <v>280.95</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>302.87</v>
+        <v>300.79</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>316.77</v>
+        <v>315.36</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>368.58</v>
+        <v>367.71</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7213.5</v>
+        <v>7179</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7543.52</v>
+        <v>7508.8</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7627.92</v>
+        <v>7610.32</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7290.33</v>
+        <v>7289.22</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4819.5</v>
+        <v>4675</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4920.69</v>
+        <v>4897.29</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4879.15</v>
+        <v>4871.14</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4445.29</v>
+        <v>4447.57</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2626</v>
+        <v>2635</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2782.66</v>
+        <v>2768.59</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2854.9</v>
+        <v>2846.28</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3183.61</v>
+        <v>3178.15</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>261.85</v>
+        <v>261.5</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>266.96</v>
+        <v>266.44</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>271.12</v>
+        <v>270.74</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>280.2</v>
+        <v>280.01</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3214.74</v>
+        <v>3203.81</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3211.82</v>
+        <v>3207.43</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3030.19</v>
+        <v>3030.89</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
         <v>230</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>235.03</v>
+        <v>234.55</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>238.16</v>
+        <v>237.84</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>248.03</v>
+        <v>247.85</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1252.6</v>
+        <v>1222</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1264.41</v>
+        <v>1260.37</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1266.96</v>
+        <v>1265.2</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1312.35</v>
+        <v>1311.45</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1346</v>
+        <v>1345.7</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1388.84</v>
+        <v>1384.73</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1417.4</v>
+        <v>1414.59</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1366.86</v>
+        <v>1366.64</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1264.1</v>
+        <v>1272.4</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1279.12</v>
+        <v>1278.48</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1279.69</v>
+        <v>1279.4</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1230.47</v>
+        <v>1230.89</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>531.6</v>
+        <v>523.55</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>540.09</v>
+        <v>538.51</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>546.38</v>
+        <v>545.49</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>609.16</v>
+        <v>608.3099999999999</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>11024</v>
+        <v>10811</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11494.32</v>
+        <v>11429.24</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11388.98</v>
+        <v>11366.32</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10337.77</v>
+        <v>10342.48</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1752</v>
+        <v>1742.4</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1867.4</v>
+        <v>1855.5</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1903.58</v>
+        <v>1897.26</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1902.32</v>
+        <v>1900.73</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1221</v>
+        <v>1251.9</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1184</v>
+        <v>1190.47</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1190.97</v>
+        <v>1193.36</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1233.15</v>
+        <v>1233.34</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2802,9 +2802,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1383.7</v>
+        <v>1379.3</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1390.31</v>
+        <v>1389.27</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1403.19</v>
+        <v>1402.25</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1402.22</v>
+        <v>1401.99</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>960</v>
+        <v>967.7</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1002.1</v>
+        <v>998.8200000000001</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1036.42</v>
+        <v>1033.73</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1091.57</v>
+        <v>1090.34</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1728.1</v>
+        <v>1735</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1738.91</v>
+        <v>1738.54</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1765.71</v>
+        <v>1764.51</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1836.31</v>
+        <v>1835.3</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 29-Sep-2026  16:45:57    |    Closing Price Date: 29-Sep-2026</t>
+          <t>Scan Run: 30-Sep-2026  16:38:14    |    Closing Price Date: 30-Sep-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>29-Sep-2026  16:45:57</t>
+          <t>30-Sep-2026  16:38:14</t>
         </is>
       </c>
     </row>
@@ -624,14 +624,14 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 12.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -652,14 +652,14 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 6 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 5 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 14 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 11 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1245.94</v>
+        <v>1240.32</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1275.06</v>
+        <v>1271.61</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1340.16</v>
+        <v>1338.64</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>722.7</v>
+        <v>708.7</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>723.08</v>
+        <v>721.71</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>731.46</v>
+        <v>730.5700000000001</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>796.58</v>
+        <v>795.7</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2032.4</v>
+        <v>2050.6</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2161.67</v>
+        <v>2151.09</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2224.18</v>
+        <v>2217.37</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2438.62</v>
+        <v>2434.76</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>156.79</v>
+        <v>158.5</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>167.4</v>
+        <v>166.55</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>173.38</v>
+        <v>172.8</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>194.33</v>
+        <v>193.97</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1292.2</v>
+        <v>1321.7</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1355.77</v>
+        <v>1352.53</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1377.93</v>
+        <v>1375.73</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1361.4</v>
+        <v>1361</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>964.7</v>
+        <v>959.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>995.04</v>
+        <v>991.66</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1014.15</v>
+        <v>1012.01</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1002.85</v>
+        <v>1002.42</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1771.2</v>
+        <v>1757</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1829.39</v>
+        <v>1822.5</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1860.62</v>
+        <v>1856.56</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1885.73</v>
+        <v>1884.44</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1015.4</v>
+        <v>994.1</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1049.91</v>
+        <v>1044.6</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1084.01</v>
+        <v>1080.49</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1207.59</v>
+        <v>1205.47</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2947.8</v>
+        <v>2950</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3089.37</v>
+        <v>3076.09</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3169.07</v>
+        <v>3160.48</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3226.07</v>
+        <v>3223.32</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3749.1</v>
+        <v>3760</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3889.02</v>
+        <v>3876.73</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3939.3</v>
+        <v>3932.27</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3919.68</v>
+        <v>3918.09</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1212.1</v>
+        <v>1226</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1234.82</v>
+        <v>1233.98</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1250.11</v>
+        <v>1249.16</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1264.3</v>
+        <v>1263.92</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,34 +1237,34 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>188</v>
+        <v>184.3</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>186.32</v>
+        <v>186.13</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.2</v>
+        <v>187.08</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.15</v>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>187.12</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>327.85</v>
+        <v>320</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>328.26</v>
+        <v>327.47</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>316.77</v>
+        <v>316.89</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>288.81</v>
+        <v>289.12</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1865</v>
+        <v>1816.6</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1867.09</v>
+        <v>1862.28</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1884.22</v>
+        <v>1881.57</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1821.47</v>
+        <v>1821.42</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1350,9 +1350,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>982.1</v>
+        <v>929.8</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1026.13</v>
+        <v>1016.96</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1034.58</v>
+        <v>1030.47</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1055.13</v>
+        <v>1053.88</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,24 +1413,24 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>410.45</v>
+        <v>411.07</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>405.75</v>
+        <v>406.19</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>401.38</v>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>401.53</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>323.5</v>
+        <v>322.75</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>328.09</v>
+        <v>327.59</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>334.41</v>
+        <v>333.95</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>346.1</v>
+        <v>345.86</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>973.8</v>
+        <v>959.4</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1021.99</v>
+        <v>1016.03</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1034.97</v>
+        <v>1032.01</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>992.17</v>
+        <v>991.84</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>955.2</v>
+        <v>941.8</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>987.0599999999999</v>
+        <v>982.75</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>998.47</v>
+        <v>996.25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>957.47</v>
+        <v>957.3200000000001</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,24 +1589,24 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2972.9</v>
+        <v>2903.4</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2964.58</v>
+        <v>2958.76</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2978.94</v>
+        <v>2975.98</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2728.47</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>2730.21</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>387.75</v>
+        <v>388.3</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>396.72</v>
+        <v>395.92</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>402.16</v>
+        <v>401.62</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>411.67</v>
+        <v>411.44</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11877</v>
+        <v>11967</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12396.7</v>
+        <v>12355.77</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12892.08</v>
+        <v>12855.8</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13539.64</v>
+        <v>13524</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
         <v>425</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>419.46</v>
+        <v>419.99</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>417.15</v>
+        <v>417.46</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414.3</v>
+        <v>414.41</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1822</v>
+        <v>1798.3</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1759.97</v>
+        <v>1763.62</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1742.8</v>
+        <v>1744.98</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1650.41</v>
+        <v>1651.88</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8659</v>
+        <v>8165.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8832.280000000001</v>
+        <v>8768.77</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8780.610000000001</v>
+        <v>8756.49</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8237.65</v>
+        <v>8236.940000000001</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1834,9 +1834,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr">
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>265.1</v>
+        <v>262.75</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>265.96</v>
+        <v>265.66</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>270.83</v>
+        <v>270.51</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>299.83</v>
+        <v>299.46</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>971.5</v>
+        <v>982.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1014.9</v>
+        <v>1011.83</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1036.02</v>
+        <v>1033.93</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.29</v>
+        <v>974.37</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1922,9 +1922,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1510.5</v>
+        <v>1524</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1555.46</v>
+        <v>1552.47</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1556.68</v>
+        <v>1555.39</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1505.99</v>
+        <v>1506.17</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,24 +1985,24 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4872</v>
+        <v>4984</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4960.41</v>
+        <v>4962.66</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5028.07</v>
+        <v>5026.34</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5008.87</v>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5008.62</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1863.8</v>
+        <v>1879.1</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1945.25</v>
+        <v>1938.95</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>2003.98</v>
+        <v>1999.08</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2148.6</v>
+        <v>2145.92</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2415</v>
+        <v>2402.6</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2473.75</v>
+        <v>2466.97</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2550.01</v>
+        <v>2544.23</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2552.62</v>
+        <v>2551.12</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10829</v>
+        <v>10956</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11087.12</v>
+        <v>11074.63</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11270.18</v>
+        <v>11257.86</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11454.35</v>
+        <v>11449.4</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>217.56</v>
+        <v>216.88</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>229.79</v>
+        <v>228.56</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>235.67</v>
+        <v>234.93</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>250.8</v>
+        <v>250.46</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>280.95</v>
+        <v>283.5</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>300.79</v>
+        <v>299.14</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>315.36</v>
+        <v>314.11</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>367.71</v>
+        <v>366.87</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7179</v>
+        <v>7150</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7508.8</v>
+        <v>7474.63</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7610.32</v>
+        <v>7592.27</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7289.22</v>
+        <v>7287.84</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4675</v>
+        <v>4587</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4897.29</v>
+        <v>4867.74</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4871.14</v>
+        <v>4860</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4447.57</v>
+        <v>4448.96</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2635</v>
+        <v>2621.6</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2768.59</v>
+        <v>2754.59</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2846.28</v>
+        <v>2837.47</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3178.15</v>
+        <v>3172.61</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>261.5</v>
+        <v>260.5</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>266.44</v>
+        <v>265.88</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>270.74</v>
+        <v>270.34</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>280.01</v>
+        <v>279.82</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3100</v>
+        <v>3061.9</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3203.81</v>
+        <v>3190.3</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3207.43</v>
+        <v>3201.73</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3030.89</v>
+        <v>3031.2</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>230</v>
+        <v>225.8</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>234.55</v>
+        <v>233.72</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>237.84</v>
+        <v>237.37</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>247.85</v>
+        <v>247.63</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1260.37</v>
+        <v>1257.48</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1265.2</v>
+        <v>1263.82</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1311.45</v>
+        <v>1310.64</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1345.7</v>
+        <v>1310</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1384.73</v>
+        <v>1377.61</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1414.59</v>
+        <v>1410.49</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1366.64</v>
+        <v>1366.08</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1272.4</v>
+        <v>1253.4</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1278.48</v>
+        <v>1276.09</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1279.4</v>
+        <v>1278.38</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1230.89</v>
+        <v>1231.11</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>523.55</v>
+        <v>521.2</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>538.51</v>
+        <v>536.86</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>545.49</v>
+        <v>544.53</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>608.3099999999999</v>
+        <v>607.4400000000001</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10811</v>
+        <v>10874</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11429.24</v>
+        <v>11376.36</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11366.32</v>
+        <v>11347.01</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10342.48</v>
+        <v>10347.76</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1742.4</v>
+        <v>1731</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1855.5</v>
+        <v>1843.64</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1897.26</v>
+        <v>1890.74</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1900.73</v>
+        <v>1899.04</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1251.9</v>
+        <v>1233</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1190.47</v>
+        <v>1194.52</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1193.36</v>
+        <v>1194.92</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1233.34</v>
+        <v>1233.33</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2802,9 +2802,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1379.3</v>
+        <v>1346</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1389.27</v>
+        <v>1385.15</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1402.25</v>
+        <v>1400.04</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1401.99</v>
+        <v>1401.43</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>967.7</v>
+        <v>949.5</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>998.8200000000001</v>
+        <v>994.12</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1033.73</v>
+        <v>1030.42</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1090.34</v>
+        <v>1088.94</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1735</v>
+        <v>1696.4</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1738.54</v>
+        <v>1734.53</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1764.51</v>
+        <v>1761.83</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1835.3</v>
+        <v>1833.92</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 30-Sep-2026  16:38:14    |    Closing Price Date: 30-Sep-2026</t>
+          <t>Scan Run: 01-Oct-2026  17:14:05    |    Closing Price Date: 01-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>30-Sep-2026  16:38:14</t>
+          <t>01-Oct-2026  17:14:05</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 6.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 6.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 16.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 5 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 3 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 5 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 3 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 11 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 8 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1187</v>
+        <v>1167.7</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1240.32</v>
+        <v>1233.41</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1271.61</v>
+        <v>1267.53</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1338.64</v>
+        <v>1336.7</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>708.7</v>
+        <v>721.2</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>721.71</v>
+        <v>721.66</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>730.5700000000001</v>
+        <v>730.2</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>795.7</v>
+        <v>795.21</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2050.6</v>
+        <v>2075</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2151.09</v>
+        <v>2143.84</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2217.37</v>
+        <v>2211.79</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2434.76</v>
+        <v>2431.06</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>158.5</v>
+        <v>159.35</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>166.55</v>
+        <v>165.86</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>172.8</v>
+        <v>172.27</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>193.97</v>
+        <v>193.69</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1321.7</v>
+        <v>1310.6</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1352.53</v>
+        <v>1348.53</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1375.73</v>
+        <v>1373.17</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1361</v>
+        <v>1360.66</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>959.5</v>
+        <v>954.1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>991.66</v>
+        <v>988.08</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1012.01</v>
+        <v>1009.74</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1002.42</v>
+        <v>1002.14</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1757</v>
+        <v>1741.1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1822.5</v>
+        <v>1814.74</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1856.56</v>
+        <v>1852.03</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1884.44</v>
+        <v>1882.91</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>994.1</v>
+        <v>1035</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1044.6</v>
+        <v>1043.68</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1080.49</v>
+        <v>1078.7</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1205.47</v>
+        <v>1203.68</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2950</v>
+        <v>2860</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3076.09</v>
+        <v>3055.51</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3160.48</v>
+        <v>3148.7</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3223.32</v>
+        <v>3220.31</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3760</v>
+        <v>3693.4</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3876.73</v>
+        <v>3859.27</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3932.27</v>
+        <v>3922.91</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3918.09</v>
+        <v>3916.69</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1226</v>
+        <v>1217.1</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1233.98</v>
+        <v>1232.37</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1249.16</v>
+        <v>1247.91</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1263.92</v>
+        <v>1263.74</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>184.3</v>
+        <v>178</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>186.13</v>
+        <v>185.35</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>187.08</v>
+        <v>186.73</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.12</v>
+        <v>187.13</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,29 +1281,29 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>320</v>
+        <v>313.9</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>327.47</v>
+        <v>326.18</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>316.89</v>
+        <v>316.78</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>289.12</v>
+        <v>289.38</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1816.6</v>
+        <v>1801</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1862.28</v>
+        <v>1856.44</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1881.57</v>
+        <v>1878.41</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1821.42</v>
+        <v>1821.18</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>929.8</v>
+        <v>940.95</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1016.96</v>
+        <v>1009.72</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1030.47</v>
+        <v>1026.96</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1053.88</v>
+        <v>1053.08</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>417</v>
+        <v>418.35</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>411.07</v>
+        <v>411.77</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>406.19</v>
+        <v>406.67</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>401.53</v>
+        <v>402.02</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>322.75</v>
+        <v>315.1</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>327.59</v>
+        <v>326.4</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>333.95</v>
+        <v>333.21</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>345.86</v>
+        <v>345.45</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>959.4</v>
+        <v>948.3</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1016.03</v>
+        <v>1009.58</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1032.01</v>
+        <v>1028.73</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>991.84</v>
+        <v>991.45</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>941.8</v>
+        <v>941.85</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>982.75</v>
+        <v>978.85</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>996.25</v>
+        <v>994.12</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>957.3200000000001</v>
+        <v>957.48</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2903.4</v>
+        <v>2816.8</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2958.76</v>
+        <v>2945.24</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2975.98</v>
+        <v>2969.73</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2730.21</v>
+        <v>2732.43</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>388.3</v>
+        <v>383.1</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>395.92</v>
+        <v>394.7</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>401.62</v>
+        <v>400.89</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>411.44</v>
+        <v>411.06</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11967</v>
+        <v>11386</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12355.77</v>
+        <v>12263.41</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12855.8</v>
+        <v>12798.16</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13524</v>
+        <v>13499.24</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>425</v>
+        <v>420.4</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>419.99</v>
+        <v>420.03</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>417.46</v>
+        <v>417.57</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414.41</v>
+        <v>414.47</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1765,29 +1765,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1798.3</v>
+        <v>1737.8</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1763.62</v>
+        <v>1761.16</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1744.98</v>
+        <v>1744.7</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1651.88</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1654.13</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8165.5</v>
+        <v>8133.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8768.77</v>
+        <v>8708.27</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8756.49</v>
+        <v>8732.059999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8236.940000000001</v>
+        <v>8235.85</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>262.75</v>
+        <v>255.9</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>265.66</v>
+        <v>264.73</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>270.51</v>
+        <v>269.94</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>299.46</v>
+        <v>299.05</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>982.7</v>
+        <v>945</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1011.83</v>
+        <v>1005.47</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1033.93</v>
+        <v>1030.44</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.37</v>
+        <v>974.65</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1922,9 +1922,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1552.47</v>
+        <v>1550.61</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1555.39</v>
+        <v>1554.52</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1506.17</v>
+        <v>1506.26</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,24 +1985,24 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4984</v>
+        <v>4929.9</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4962.66</v>
+        <v>4959.54</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5026.34</v>
+        <v>5022.56</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5008.62</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>5013.51</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1879.1</v>
+        <v>1836</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1938.95</v>
+        <v>1929.14</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1999.08</v>
+        <v>1992.69</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2145.92</v>
+        <v>2142.36</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2402.6</v>
+        <v>2407</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2466.97</v>
+        <v>2461.26</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2544.23</v>
+        <v>2538.85</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2551.12</v>
+        <v>2550.14</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10956</v>
+        <v>10710</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11074.63</v>
+        <v>11039.91</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11257.86</v>
+        <v>11236.37</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11449.4</v>
+        <v>11447.15</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>216.88</v>
+        <v>212.5</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>228.56</v>
+        <v>227.03</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>234.93</v>
+        <v>234.05</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>250.46</v>
+        <v>250.39</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>283.5</v>
+        <v>279.4</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>299.14</v>
+        <v>297.26</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>314.11</v>
+        <v>312.75</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>366.87</v>
+        <v>366.1</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7150</v>
+        <v>6920</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7474.63</v>
+        <v>7421.81</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7592.27</v>
+        <v>7565.9</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7287.84</v>
+        <v>7287.2</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4587</v>
+        <v>4515.7</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4867.74</v>
+        <v>4834.21</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4860</v>
+        <v>4846.5</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4448.96</v>
+        <v>4450.44</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2621.6</v>
+        <v>2580</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2754.59</v>
+        <v>2737.97</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2837.47</v>
+        <v>2827.37</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3172.61</v>
+        <v>3164.2</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>260.5</v>
+        <v>254.55</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>265.88</v>
+        <v>264.8</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>270.34</v>
+        <v>269.72</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>279.82</v>
+        <v>279.4</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>3061.9</v>
+        <v>2962</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3190.3</v>
+        <v>3168.55</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3201.73</v>
+        <v>3192.33</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3031.2</v>
+        <v>3032.8</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2450,9 +2450,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>225.8</v>
+        <v>222.37</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>233.72</v>
+        <v>232.64</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>237.37</v>
+        <v>236.78</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>247.63</v>
+        <v>247.1</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1230</v>
+        <v>1243.1</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1257.48</v>
+        <v>1256.11</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1263.82</v>
+        <v>1263</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1310.64</v>
+        <v>1309.53</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1310</v>
+        <v>1307.7</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1377.61</v>
+        <v>1370.95</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1410.49</v>
+        <v>1406.46</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1366.08</v>
+        <v>1365.63</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1253.4</v>
+        <v>1233</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1276.09</v>
+        <v>1271.99</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1278.38</v>
+        <v>1276.6</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1231.11</v>
+        <v>1231.53</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>521.2</v>
+        <v>534.2</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>536.86</v>
+        <v>536.61</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>544.53</v>
+        <v>544.13</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>607.4400000000001</v>
+        <v>606.9400000000001</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10874</v>
+        <v>10045</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11376.36</v>
+        <v>11249.56</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11347.01</v>
+        <v>11295.95</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10347.76</v>
+        <v>10348.35</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2714,9 +2714,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1731</v>
+        <v>1732.6</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1843.64</v>
+        <v>1833.07</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1890.74</v>
+        <v>1884.54</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1899.04</v>
+        <v>1897.86</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1233</v>
+        <v>1206.2</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1194.52</v>
+        <v>1195.63</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1194.92</v>
+        <v>1195.36</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1233.33</v>
+        <v>1233.84</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1385.15</v>
+        <v>1381.23</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1400.04</v>
+        <v>1397.85</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1401.43</v>
+        <v>1400.99</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>949.5</v>
+        <v>957</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>994.12</v>
+        <v>990.59</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1030.42</v>
+        <v>1027.54</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1088.94</v>
+        <v>1087.56</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>30-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1696.4</v>
+        <v>1721.6</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1734.53</v>
+        <v>1733.3</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1761.83</v>
+        <v>1760.26</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1833.92</v>
+        <v>1833.78</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 01-Oct-2026  17:14:05    |    Closing Price Date: 01-Oct-2026</t>
+          <t>Scan Run: 02-Oct-2026  16:27:49    |    Closing Price Date: 01-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>01-Oct-2026  17:14:05</t>
+          <t>02-Oct-2026  16:27:49</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         <v>1267.53</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1336.7</v>
+        <v>1337.37</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>730.2</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>795.21</v>
+        <v>795.59</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>2211.79</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2431.06</v>
+        <v>2433.18</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>172.27</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>193.69</v>
+        <v>193.86</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>1373.17</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.66</v>
+        <v>1360.73</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>1009.74</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1002.14</v>
+        <v>1002.33</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>1852.03</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1882.91</v>
+        <v>1884.19</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>1078.7</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1203.68</v>
+        <v>1204.99</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>3148.7</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3220.31</v>
+        <v>3222.92</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>3922.91</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3916.69</v>
+        <v>3917.3</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>1247.91</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1263.74</v>
+        <v>1263.42</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>186.73</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.13</v>
+        <v>187.19</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>316.78</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>289.38</v>
+        <v>289.54</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>1878.41</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1821.18</v>
+        <v>1821.5</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>1026.96</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1053.08</v>
+        <v>1054.74</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>406.67</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>402.02</v>
+        <v>401.81</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>333.21</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>345.45</v>
+        <v>345.49</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>1028.73</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>991.45</v>
+        <v>991.91</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>994.12</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>957.48</v>
+        <v>957.61</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>2969.73</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2732.43</v>
+        <v>2733.31</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>400.89</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>411.06</v>
+        <v>410.55</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>12798.16</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13499.24</v>
+        <v>13505.47</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>417.57</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414.47</v>
+        <v>414.44</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>1744.7</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1654.13</v>
+        <v>1654.28</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>8732.059999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8235.85</v>
+        <v>8237.309999999999</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>269.94</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>299.05</v>
+        <v>299.12</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>1030.44</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.65</v>
+        <v>974.62</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>1554.52</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1506.26</v>
+        <v>1507.34</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>5022.56</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5013.51</v>
+        <v>5014.85</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>1992.69</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2142.36</v>
+        <v>2142.99</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>2538.85</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2550.14</v>
+        <v>2550.32</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>11236.37</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11447.15</v>
+        <v>11453.26</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>234.05</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>250.39</v>
+        <v>250.49</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>312.75</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>366.1</v>
+        <v>366.13</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>7565.9</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7287.2</v>
+        <v>7285.09</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>4846.5</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4450.44</v>
+        <v>4455.55</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>2827.37</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3164.2</v>
+        <v>3166.92</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>269.72</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>279.4</v>
+        <v>279.57</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>3192.33</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3032.8</v>
+        <v>3034.86</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>236.78</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>247.1</v>
+        <v>247.02</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>1263</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1309.53</v>
+        <v>1310.51</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>1406.46</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1365.63</v>
+        <v>1366.41</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>1276.6</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1231.53</v>
+        <v>1232.24</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>544.13</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>606.9400000000001</v>
+        <v>607.15</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>11295.95</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10348.35</v>
+        <v>10348.86</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>1884.54</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1897.86</v>
+        <v>1897.96</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>1195.36</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1233.84</v>
+        <v>1234.01</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>1397.85</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1400.99</v>
+        <v>1401.3</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>1027.54</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1087.56</v>
+        <v>1088.32</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>1760.26</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1833.78</v>
+        <v>1833.77</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 02-Oct-2026  16:27:49    |    Closing Price Date: 01-Oct-2026</t>
+          <t>Scan Run: 06-Oct-2026  17:01:23    |    Closing Price Date: 06-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>02-Oct-2026  16:27:49</t>
+          <t>06-Oct-2026  17:01:23</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 6.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 6.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 16.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 16.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 14.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 3 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 3 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 8 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 8 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 7 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1167.7</v>
+        <v>1218</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1233.41</v>
+        <v>1222.77</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1267.53</v>
+        <v>1258.92</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1337.37</v>
+        <v>1334.35</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>721.2</v>
+        <v>711.45</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>721.66</v>
+        <v>719.2</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>730.2</v>
+        <v>728.1799999999999</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>795.59</v>
+        <v>793.97</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2075</v>
+        <v>2100</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2143.84</v>
+        <v>2131.76</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2211.79</v>
+        <v>2198.78</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2433.18</v>
+        <v>2423.91</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>159.35</v>
+        <v>161.84</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>165.86</v>
+        <v>164.65</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>172.27</v>
+        <v>171.01</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>193.86</v>
+        <v>192.77</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1310.6</v>
+        <v>1342.8</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1348.53</v>
+        <v>1343.61</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1373.17</v>
+        <v>1368.16</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.73</v>
+        <v>1360.56</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>954.1</v>
+        <v>958.75</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>988.08</v>
+        <v>980.05</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1009.74</v>
+        <v>1003.77</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1002.33</v>
+        <v>1001.8</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1741.1</v>
+        <v>1810.5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1814.74</v>
+        <v>1805.6</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1852.03</v>
+        <v>1843.67</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1884.19</v>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1882.75</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1035</v>
+        <v>1013.85</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1043.68</v>
+        <v>1038.17</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1078.7</v>
+        <v>1072.39</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1204.99</v>
+        <v>1199.1</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2860</v>
+        <v>2855</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3055.51</v>
+        <v>3004.12</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3148.7</v>
+        <v>3115.76</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3222.92</v>
+        <v>3210.83</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3693.4</v>
+        <v>3770</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3859.27</v>
+        <v>3828.42</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3922.91</v>
+        <v>3902.09</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3917.3</v>
+        <v>3913.98</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,29 +1193,29 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1217.1</v>
+        <v>1248</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1232.37</v>
+        <v>1231.79</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1247.91</v>
+        <v>1245.83</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1263.42</v>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1261.82</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>178</v>
+        <v>178.69</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>185.35</v>
+        <v>183.52</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>186.73</v>
+        <v>185.77</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.19</v>
+        <v>187.06</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,29 +1281,29 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>313.9</v>
+        <v>329</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>326.18</v>
+        <v>325.03</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>316.78</v>
+        <v>317.3</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>289.54</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>290.69</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1801</v>
+        <v>1804.1</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1856.44</v>
+        <v>1840.52</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1878.41</v>
+        <v>1868.97</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1821.5</v>
+        <v>1820.96</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>940.95</v>
+        <v>902.5</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1009.72</v>
+        <v>986.16</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1026.96</v>
+        <v>1014.82</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1054.74</v>
+        <v>1052.23</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>418.35</v>
+        <v>431.9</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>411.77</v>
+        <v>414.05</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>406.67</v>
+        <v>408.01</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>401.81</v>
+        <v>401.96</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>315.1</v>
+        <v>321.45</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>326.4</v>
+        <v>325.53</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>333.21</v>
+        <v>332.32</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>345.49</v>
+        <v>345.17</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>948.3</v>
+        <v>963.1</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>1009.58</v>
+        <v>996.96</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1028.73</v>
+        <v>1021.03</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>991.91</v>
+        <v>991.3099999999999</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>941.85</v>
+        <v>940.5</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>978.85</v>
+        <v>968.83</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>994.12</v>
+        <v>988.02</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>957.61</v>
+        <v>957.89</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2816.8</v>
+        <v>2849.9</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2945.24</v>
+        <v>2919.14</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2969.73</v>
+        <v>2955.51</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2733.31</v>
+        <v>2740.26</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>383.1</v>
+        <v>387.4</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>394.7</v>
+        <v>392.25</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>400.89</v>
+        <v>399.11</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>410.55</v>
+        <v>410.42</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11386</v>
+        <v>11625</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12263.41</v>
+        <v>12139.59</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12798.16</v>
+        <v>12704.45</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13505.47</v>
+        <v>13452.59</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,34 +1721,34 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>420.4</v>
+        <v>411.65</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>420.03</v>
+        <v>419.7</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>417.57</v>
+        <v>417.73</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414.44</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>414.58</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -1765,29 +1765,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1737.8</v>
+        <v>1783.4</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1761.16</v>
+        <v>1762.57</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1744.7</v>
+        <v>1747.07</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1654.28</v>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1659.84</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8133.5</v>
+        <v>7914.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8708.27</v>
+        <v>8525.540000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8732.059999999999</v>
+        <v>8650.18</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8237.309999999999</v>
+        <v>8238.59</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>255.9</v>
+        <v>266.7</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>264.73</v>
+        <v>264.59</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>269.94</v>
+        <v>269.26</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>299.12</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>298.08</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>945</v>
+        <v>965.05</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1005.47</v>
+        <v>993.97</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1030.44</v>
+        <v>1022.56</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.62</v>
+        <v>975.45</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1533</v>
+        <v>1504.5</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1550.61</v>
+        <v>1543.58</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1554.52</v>
+        <v>1551.07</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1507.34</v>
+        <v>1507.16</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1966,9 +1966,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
@@ -1985,34 +1985,34 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4929.9</v>
+        <v>5050.5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4959.54</v>
+        <v>4963.78</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5022.56</v>
+        <v>5017</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5014.85</v>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>5027.37</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1836</v>
+        <v>1895.2</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1929.14</v>
+        <v>1910.83</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1992.69</v>
+        <v>1977.38</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2142.99</v>
+        <v>2135.15</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2407</v>
+        <v>2424.2</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2461.26</v>
+        <v>2445.29</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2538.85</v>
+        <v>2523.07</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2550.32</v>
+        <v>2548.29</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10710</v>
+        <v>10750</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>11039.91</v>
+        <v>10995.93</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11236.37</v>
+        <v>11202.74</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11453.26</v>
+        <v>11454.48</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>212.5</v>
+        <v>217.9</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>227.03</v>
+        <v>223.74</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>234.05</v>
+        <v>231.81</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>250.49</v>
+        <v>250.36</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>279.4</v>
+        <v>285.8</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>297.26</v>
+        <v>294.03</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>312.75</v>
+        <v>309.58</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>366.13</v>
+        <v>364.26</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>6920</v>
+        <v>7051</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7421.81</v>
+        <v>7352</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7565.9</v>
+        <v>7525.2</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7285.09</v>
+        <v>7283.35</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4515.7</v>
+        <v>4550</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4834.21</v>
+        <v>4760.41</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4846.5</v>
+        <v>4812.85</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4455.55</v>
+        <v>4459.82</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,29 +2337,29 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2580</v>
+        <v>2906</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2737.97</v>
+        <v>2728.04</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2827.37</v>
+        <v>2812.18</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3166.92</v>
-      </c>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3156.66</v>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>254.55</v>
+        <v>257.2</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>264.8</v>
+        <v>262.6</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>269.72</v>
+        <v>268.2</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>279.57</v>
+        <v>279.25</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2962</v>
+        <v>2969</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3168.55</v>
+        <v>3132.61</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3192.33</v>
+        <v>3175.27</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3034.86</v>
+        <v>3034.07</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>222.37</v>
+        <v>224.2</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>232.64</v>
+        <v>230.37</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>236.78</v>
+        <v>235.32</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>247.02</v>
+        <v>246.42</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1243.1</v>
+        <v>1204.4</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1256.11</v>
+        <v>1245.5</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1263</v>
+        <v>1257.68</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1310.51</v>
+        <v>1308.17</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1307.7</v>
+        <v>1341.4</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1370.95</v>
+        <v>1361.77</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1406.46</v>
+        <v>1399.78</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1366.41</v>
+        <v>1366.7</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1233</v>
+        <v>1259.6</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1271.99</v>
+        <v>1264.61</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1276.6</v>
+        <v>1272.8</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1232.24</v>
+        <v>1232.38</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,29 +2645,29 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>534.2</v>
+        <v>543.95</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>536.61</v>
+        <v>536.8200000000001</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>544.13</v>
+        <v>543.63</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>607.15</v>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>606.96</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10045</v>
+        <v>10017</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11249.56</v>
+        <v>11026.57</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11295.95</v>
+        <v>11197.87</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10348.86</v>
+        <v>10341.77</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1732.6</v>
+        <v>1752.4</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1833.07</v>
+        <v>1810.51</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1884.54</v>
+        <v>1868.84</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1897.96</v>
+        <v>1895.27</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1206.2</v>
+        <v>1208</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1195.63</v>
+        <v>1197.45</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1195.36</v>
+        <v>1196.14</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1234.01</v>
+        <v>1231.1</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1344</v>
+        <v>1340.2</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1381.23</v>
+        <v>1370.48</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1397.85</v>
+        <v>1391.29</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1401.3</v>
+        <v>1399.96</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>957</v>
+        <v>976</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>990.59</v>
+        <v>983.41</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1027.54</v>
+        <v>1020.19</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1088.32</v>
+        <v>1083.47</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,24 +2909,24 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>06-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1721.6</v>
+        <v>1750</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1733.3</v>
+        <v>1732.84</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1760.26</v>
+        <v>1757.94</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1833.77</v>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1831.52</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 06-Oct-2026  17:01:23    |    Closing Price Date: 06-Oct-2026</t>
+          <t>Scan Run: 07-Oct-2026  17:39:06    |    Closing Price Date: 07-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>06-Oct-2026  17:01:23</t>
+          <t>07-Oct-2026  17:39:06</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 16.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 12.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 14.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 8.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 8 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 6 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 7 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 4 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1218</v>
+        <v>1207.7</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1222.77</v>
+        <v>1221.33</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1258.92</v>
+        <v>1256.91</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1334.35</v>
+        <v>1333.09</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>711.45</v>
+        <v>702.75</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>719.2</v>
+        <v>717.63</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>728.1799999999999</v>
+        <v>727.1799999999999</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>793.97</v>
+        <v>793.0599999999999</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2100</v>
+        <v>2080.3</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2131.76</v>
+        <v>2126.86</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2198.78</v>
+        <v>2194.14</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2423.91</v>
+        <v>2420.49</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>161.84</v>
+        <v>159.6</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>164.65</v>
+        <v>164.17</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>171.01</v>
+        <v>170.56</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>192.77</v>
+        <v>192.44</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,24 +929,24 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1342.8</v>
+        <v>1357.5</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1343.61</v>
+        <v>1344.93</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1368.16</v>
+        <v>1367.75</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.56</v>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1360.53</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>958.75</v>
+        <v>954</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>980.05</v>
+        <v>977.5700000000001</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1003.77</v>
+        <v>1001.82</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1001.8</v>
+        <v>1001.33</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1810.5</v>
+        <v>1833.9</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1805.6</v>
+        <v>1808.29</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1843.67</v>
+        <v>1843.29</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1882.75</v>
+        <v>1882.26</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1013.85</v>
+        <v>992</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1038.17</v>
+        <v>1033.77</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1072.39</v>
+        <v>1069.23</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1199.1</v>
+        <v>1197.04</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2855</v>
+        <v>2800</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3004.12</v>
+        <v>2984.68</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3115.76</v>
+        <v>3103.38</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3210.83</v>
+        <v>3206.75</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3770</v>
+        <v>3701.5</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3828.42</v>
+        <v>3816.34</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3902.09</v>
+        <v>3894.22</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3913.98</v>
+        <v>3911.87</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,29 +1193,29 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1248</v>
+        <v>1242.5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1231.79</v>
+        <v>1232.81</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1245.83</v>
+        <v>1245.7</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1261.82</v>
+        <v>1261.63</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>178.69</v>
+        <v>175.64</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>183.52</v>
+        <v>182.77</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>185.77</v>
+        <v>185.37</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>187.06</v>
+        <v>186.94</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>325.03</v>
+        <v>325.31</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>317.3</v>
+        <v>317.72</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>290.69</v>
+        <v>291.06</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1804.1</v>
+        <v>1781</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1840.52</v>
+        <v>1834.85</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1868.97</v>
+        <v>1865.52</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1820.96</v>
+        <v>1820.56</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>902.5</v>
+        <v>908</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>986.16</v>
+        <v>978.71</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1014.82</v>
+        <v>1010.63</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1052.23</v>
+        <v>1050.8</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>431.9</v>
+        <v>440</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>414.05</v>
+        <v>416.98</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>408.01</v>
+        <v>409.67</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>401.96</v>
+        <v>402.51</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>321.45</v>
+        <v>316.75</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>325.53</v>
+        <v>323.9</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>332.32</v>
+        <v>331.08</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>345.17</v>
+        <v>344.59</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>963.1</v>
+        <v>963.85</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>996.96</v>
+        <v>993.8099999999999</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1021.03</v>
+        <v>1018.79</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>991.3099999999999</v>
+        <v>991.04</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>940.5</v>
+        <v>910.85</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>968.83</v>
+        <v>963.3099999999999</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>988.02</v>
+        <v>985</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>957.89</v>
+        <v>957.4299999999999</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2849.9</v>
+        <v>2743</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2919.14</v>
+        <v>2902.37</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2955.51</v>
+        <v>2947.18</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2740.26</v>
+        <v>2740.28</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>387.4</v>
+        <v>378.3</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>392.25</v>
+        <v>390.92</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>399.11</v>
+        <v>398.3</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>410.42</v>
+        <v>410.1</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11625</v>
+        <v>11450</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12139.59</v>
+        <v>12012.02</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12704.45</v>
+        <v>12606.14</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13452.59</v>
+        <v>13412.34</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>411.65</v>
+        <v>414.5</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>419.7</v>
+        <v>419.2</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>417.73</v>
+        <v>417.6</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>414.58</v>
@@ -1765,24 +1765,24 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1783.4</v>
+        <v>1750.1</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1762.57</v>
+        <v>1761.38</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1747.07</v>
+        <v>1747.19</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1659.84</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1660.74</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7914.5</v>
+        <v>7917</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8525.540000000001</v>
+        <v>8467.59</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8650.18</v>
+        <v>8621.43</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8238.59</v>
+        <v>8235.389999999999</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>266.7</v>
+        <v>265.7</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>264.59</v>
+        <v>264.69</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>269.26</v>
+        <v>269.12</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>298.08</v>
+        <v>297.76</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>965.05</v>
+        <v>948</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>993.97</v>
+        <v>989.59</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1022.56</v>
+        <v>1019.64</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>975.45</v>
+        <v>975.1799999999999</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1504.5</v>
+        <v>1491.1</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1543.58</v>
+        <v>1538.58</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1551.07</v>
+        <v>1548.72</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1507.16</v>
+        <v>1507</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,34 +1985,34 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>5050.5</v>
+        <v>4990</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4963.78</v>
+        <v>4966.27</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5017</v>
+        <v>5015.94</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5027.37</v>
+        <v>5026.99</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1895.2</v>
+        <v>1865.4</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1910.83</v>
+        <v>1906.5</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1977.38</v>
+        <v>1972.99</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2135.15</v>
+        <v>2132.47</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2424.2</v>
+        <v>2372.1</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2445.29</v>
+        <v>2438.32</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2523.07</v>
+        <v>2517.15</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2548.29</v>
+        <v>2546.53</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10750</v>
+        <v>10658</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10995.93</v>
+        <v>10940.48</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11202.74</v>
+        <v>11163.07</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11454.48</v>
+        <v>11439.23</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>217.9</v>
+        <v>216.44</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>223.74</v>
+        <v>223.04</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>231.81</v>
+        <v>231.2</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>250.36</v>
+        <v>250.02</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>285.8</v>
+        <v>283</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>294.03</v>
+        <v>292.98</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>309.58</v>
+        <v>308.54</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>364.26</v>
+        <v>363.45</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7051</v>
+        <v>6960</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7352</v>
+        <v>7279.27</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7525.2</v>
+        <v>7480.57</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7283.35</v>
+        <v>7276.58</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4550</v>
+        <v>4377</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4760.41</v>
+        <v>4723.89</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4812.85</v>
+        <v>4795.76</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4459.82</v>
+        <v>4458.99</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2318,9 +2318,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2906</v>
+        <v>2890.3</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2728.04</v>
+        <v>2743.5</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2812.18</v>
+        <v>2815.24</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3156.66</v>
+        <v>3154.01</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>257.2</v>
+        <v>253.05</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>262.6</v>
+        <v>261.69</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>268.2</v>
+        <v>267.61</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>279.25</v>
+        <v>278.99</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2969</v>
+        <v>2921.1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3132.61</v>
+        <v>3112.47</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3175.27</v>
+        <v>3165.3</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3034.07</v>
+        <v>3032.95</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>224.2</v>
+        <v>221.88</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>230.37</v>
+        <v>229.56</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>235.32</v>
+        <v>234.79</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>246.42</v>
+        <v>246.18</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1204.4</v>
+        <v>1185</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1245.5</v>
+        <v>1239.74</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1257.68</v>
+        <v>1254.83</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1308.17</v>
+        <v>1306.94</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1341.4</v>
+        <v>1324</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1361.77</v>
+        <v>1358.18</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1399.78</v>
+        <v>1396.81</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1366.7</v>
+        <v>1366.27</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1259.6</v>
+        <v>1230</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1264.61</v>
+        <v>1261.31</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1272.8</v>
+        <v>1271.12</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1232.38</v>
+        <v>1232.36</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2626,9 +2626,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>543.95</v>
+        <v>546.05</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>536.8200000000001</v>
+        <v>537.53</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>543.63</v>
+        <v>543.38</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>606.96</v>
+        <v>605.64</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10017</v>
+        <v>9884</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>11026.57</v>
+        <v>10832.79</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11197.87</v>
+        <v>11102.84</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10341.77</v>
+        <v>10334.29</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1752.4</v>
+        <v>1743.3</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1810.51</v>
+        <v>1804.11</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1868.84</v>
+        <v>1863.91</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1895.27</v>
+        <v>1893.75</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1208</v>
+        <v>1203.8</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1197.45</v>
+        <v>1198.8</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1196.14</v>
+        <v>1196.82</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1231.1</v>
+        <v>1230.58</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1340.2</v>
+        <v>1327.2</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1370.48</v>
+        <v>1366.36</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1391.29</v>
+        <v>1388.77</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1399.96</v>
+        <v>1399.23</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>976</v>
+        <v>968.5</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>983.41</v>
+        <v>981.99</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1020.19</v>
+        <v>1018.16</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1083.47</v>
+        <v>1082.33</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,24 +2909,24 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>06-Oct-2026</t>
+          <t>07-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1750</v>
+        <v>1726.1</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1732.84</v>
+        <v>1731.37</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1757.94</v>
+        <v>1755.35</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1831.52</v>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1829.39</v>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 07-Oct-2026  17:39:06    |    Closing Price Date: 07-Oct-2026</t>
+          <t>Scan Run: 08-Oct-2026  17:41:31    |    Closing Price Date: 08-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>07-Oct-2026  17:39:06</t>
+          <t>08-Oct-2026  17:41:31</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 12.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 8.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 8.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 6.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 5 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 6 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 4 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 4 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 3 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1207.7</v>
+        <v>1178</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1221.33</v>
+        <v>1217.2</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1256.91</v>
+        <v>1253.82</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1333.09</v>
+        <v>1332.66</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>702.75</v>
+        <v>692.25</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>717.63</v>
+        <v>715.22</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>727.1799999999999</v>
+        <v>725.8099999999999</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>793.0599999999999</v>
+        <v>792.27</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2080.3</v>
+        <v>2076</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2126.86</v>
+        <v>2122.02</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2194.14</v>
+        <v>2189.51</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2420.49</v>
+        <v>2415.81</v>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>159.6</v>
+        <v>158.38</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>164.17</v>
+        <v>163.62</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>170.56</v>
+        <v>170.09</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>192.44</v>
+        <v>192.04</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1357.5</v>
+        <v>1349</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1344.93</v>
+        <v>1345.32</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1367.75</v>
+        <v>1367.01</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.53</v>
+        <v>1359.87</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>977.5700000000001</v>
+        <v>973.99</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1001.82</v>
+        <v>999.4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1001.33</v>
+        <v>1000.71</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1833.9</v>
+        <v>1804.6</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1808.29</v>
+        <v>1807.94</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1843.29</v>
+        <v>1841.77</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1882.26</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1881.87</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1033.77</v>
+        <v>1030.27</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1069.23</v>
+        <v>1066.4</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1197.04</v>
+        <v>1195.24</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2800</v>
+        <v>2751.2</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2984.68</v>
+        <v>2962.44</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3103.38</v>
+        <v>3089.57</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3206.75</v>
+        <v>3201.93</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3701.5</v>
+        <v>3625.1</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3816.34</v>
+        <v>3798.12</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3894.22</v>
+        <v>3883.67</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3911.87</v>
+        <v>3908.89</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1242.5</v>
+        <v>1245</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1232.81</v>
+        <v>1233.97</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1245.7</v>
+        <v>1245.67</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1261.63</v>
+        <v>1260.42</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>175.64</v>
+        <v>171.96</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>182.77</v>
+        <v>181.74</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>185.37</v>
+        <v>184.85</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>186.94</v>
+        <v>186.81</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,24 +1281,24 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>328</v>
+        <v>319.05</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>325.31</v>
+        <v>324.71</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>317.72</v>
+        <v>317.77</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>291.06</v>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>291.21</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1781</v>
+        <v>1759.8</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1834.85</v>
+        <v>1827.71</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1865.52</v>
+        <v>1861.38</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1820.56</v>
+        <v>1819.61</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>908</v>
+        <v>873.4</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>978.71</v>
+        <v>968.6799999999999</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1010.63</v>
+        <v>1005.25</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1050.8</v>
+        <v>1049.18</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>416.98</v>
+        <v>418.7</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>409.67</v>
+        <v>410.67</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>402.51</v>
+        <v>402.99</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>316.75</v>
+        <v>309.7</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>323.9</v>
+        <v>322.54</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>331.08</v>
+        <v>330.24</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>344.59</v>
+        <v>344.16</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>963.85</v>
+        <v>955.95</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>993.8099999999999</v>
+        <v>990.21</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1018.79</v>
+        <v>1016.32</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>991.04</v>
+        <v>990.7</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>910.85</v>
+        <v>890.15</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>963.3099999999999</v>
+        <v>956.34</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>985</v>
+        <v>981.28</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>957.4299999999999</v>
+        <v>956.8099999999999</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2743</v>
+        <v>2596</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2902.37</v>
+        <v>2873.19</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2947.18</v>
+        <v>2933.41</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2740.28</v>
+        <v>2738.94</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1614,9 +1614,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>378.3</v>
+        <v>367.3</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>390.92</v>
+        <v>388.67</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>398.3</v>
+        <v>397.08</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>410.1</v>
+        <v>410.11</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11450</v>
+        <v>11228</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>12012.02</v>
+        <v>11937.35</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12606.14</v>
+        <v>12552.09</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13412.34</v>
+        <v>13392.27</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>414.5</v>
+        <v>409.35</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>419.2</v>
+        <v>418.26</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>417.6</v>
+        <v>417.28</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414.58</v>
+        <v>414.45</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,29 +1765,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1750.1</v>
+        <v>1708</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1761.38</v>
+        <v>1756.3</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1747.19</v>
+        <v>1745.65</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1660.74</v>
+        <v>1661.08</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7917</v>
+        <v>7666</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8467.59</v>
+        <v>8391.24</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8621.43</v>
+        <v>8583.959999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8235.389999999999</v>
+        <v>8239.940000000001</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>265.7</v>
+        <v>255</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>264.69</v>
+        <v>263.77</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>269.12</v>
+        <v>268.57</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>297.76</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>297.28</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>948</v>
+        <v>917.25</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>989.59</v>
+        <v>982.7</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1019.64</v>
+        <v>1015.62</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>975.1799999999999</v>
+        <v>974.1900000000001</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1491.1</v>
+        <v>1496.2</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1538.58</v>
+        <v>1534.55</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1548.72</v>
+        <v>1546.66</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1507</v>
+        <v>1506.29</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1985,24 +1985,24 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4990</v>
+        <v>4813.1</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4966.27</v>
+        <v>4951.69</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5015.94</v>
+        <v>5007.99</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5026.99</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>5024.4</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1865.4</v>
+        <v>1844.5</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1906.5</v>
+        <v>1900.6</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1972.99</v>
+        <v>1967.95</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2132.47</v>
+        <v>2129.64</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2372.1</v>
+        <v>2311.6</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2438.32</v>
+        <v>2426.25</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2517.15</v>
+        <v>2509.09</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2546.53</v>
+        <v>2545.33</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10658</v>
+        <v>10426</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10940.48</v>
+        <v>10891.48</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11163.07</v>
+        <v>11134.17</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11439.23</v>
+        <v>11433.75</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>216.44</v>
+        <v>211</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>223.04</v>
+        <v>221.89</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>231.2</v>
+        <v>230.41</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>250.02</v>
+        <v>249.75</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>292.98</v>
+        <v>291.08</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>308.54</v>
+        <v>307.14</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>363.45</v>
+        <v>362.39</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>6960</v>
+        <v>6767.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7279.27</v>
+        <v>7230.53</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7480.57</v>
+        <v>7452.61</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7276.58</v>
+        <v>7273.84</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4377</v>
+        <v>4359.5</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4723.89</v>
+        <v>4689.19</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4795.76</v>
+        <v>4778.65</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4458.99</v>
+        <v>4458.42</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2890.3</v>
+        <v>2876.3</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2743.5</v>
+        <v>2756.14</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2815.24</v>
+        <v>2817.64</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3154.01</v>
+        <v>3148.28</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>253.05</v>
+        <v>244.65</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>261.69</v>
+        <v>260.07</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>267.61</v>
+        <v>266.71</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>278.99</v>
+        <v>278.56</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2921.1</v>
+        <v>2856.8</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3112.47</v>
+        <v>3074.94</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3165.3</v>
+        <v>3145.5</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3032.95</v>
+        <v>3030.64</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>221.88</v>
+        <v>219.8</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>229.56</v>
+        <v>228.63</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>234.79</v>
+        <v>234.2</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>246.18</v>
+        <v>245.88</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1185</v>
+        <v>1176.9</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1239.74</v>
+        <v>1233.75</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1254.83</v>
+        <v>1251.78</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1306.94</v>
+        <v>1305.25</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1358.18</v>
+        <v>1350.41</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1396.81</v>
+        <v>1390.46</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1366.27</v>
+        <v>1364.13</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1230</v>
+        <v>1175.2</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1261.31</v>
+        <v>1253.11</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1271.12</v>
+        <v>1267.36</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1232.36</v>
+        <v>1232.15</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>546.05</v>
+        <v>544.5</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>537.53</v>
+        <v>538.2</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>543.38</v>
+        <v>543.42</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>605.64</v>
+        <v>604.85</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>9884</v>
+        <v>9637</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10832.79</v>
+        <v>10718.9</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11102.84</v>
+        <v>11045.36</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10334.29</v>
+        <v>10328.26</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1743.3</v>
+        <v>1708</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1804.11</v>
+        <v>1794.96</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1863.91</v>
+        <v>1857.8</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1893.75</v>
+        <v>1891.82</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,29 +2777,29 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1203.8</v>
+        <v>1180</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1198.8</v>
+        <v>1197.01</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1196.82</v>
+        <v>1196.16</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1230.58</v>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1229.82</v>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1327.2</v>
+        <v>1306.8</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1366.36</v>
+        <v>1360.68</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1388.77</v>
+        <v>1385.56</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1399.23</v>
+        <v>1398.7</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>968.5</v>
+        <v>951.9</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>981.99</v>
+        <v>979.12</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1018.16</v>
+        <v>1015.56</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1082.33</v>
+        <v>1080.9</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>07-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1726.1</v>
+        <v>1682.5</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1731.37</v>
+        <v>1726.72</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1755.35</v>
+        <v>1752.49</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1829.39</v>
+        <v>1828.91</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 08-Oct-2026  17:41:31    |    Closing Price Date: 08-Oct-2026</t>
+          <t>Scan Run: 09-Oct-2026  17:16:44    |    Closing Price Date: 09-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>8</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>08-Oct-2026  17:41:31</t>
+          <t>09-Oct-2026  17:16:44</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 10.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 8.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 14.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 6.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 8.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 5 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 9 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 4 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 7 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 3 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 4 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1178</v>
+        <v>1170.3</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1217.2</v>
+        <v>1217.14</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1253.82</v>
+        <v>1254.68</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1332.66</v>
+        <v>1333.83</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>692.25</v>
+        <v>707.25</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>715.22</v>
+        <v>714.5700000000001</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>725.8099999999999</v>
+        <v>725.88</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>792.27</v>
+        <v>793.67</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,24 +841,24 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2076</v>
+        <v>2156</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2122.02</v>
+        <v>2130.57</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2189.51</v>
+        <v>2194.83</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2415.81</v>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2424.52</v>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>158.38</v>
+        <v>162.57</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>163.62</v>
+        <v>164.02</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>170.09</v>
+        <v>170.46</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>192.04</v>
+        <v>192.79</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1345.32</v>
+        <v>1348.97</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1367.01</v>
+        <v>1368.89</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1359.87</v>
+        <v>1360.37</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>940</v>
+        <v>959.1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>973.99</v>
+        <v>975.02</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>999.4</v>
+        <v>1000.31</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1000.71</v>
+        <v>1000.05</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1804.6</v>
+        <v>1805.1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1807.94</v>
+        <v>1812.58</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1841.77</v>
+        <v>1845</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1881.87</v>
+        <v>1884.5</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>997</v>
+        <v>1023.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1030.27</v>
+        <v>1031.15</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1066.4</v>
+        <v>1067.99</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1195.24</v>
+        <v>1200.02</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2751.2</v>
+        <v>2796.2</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2962.44</v>
+        <v>2960.01</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3089.57</v>
+        <v>3090.11</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3201.93</v>
+        <v>3204.17</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3625.1</v>
+        <v>3703.3</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3798.12</v>
+        <v>3799.6</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3883.67</v>
+        <v>3884.56</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3908.89</v>
+        <v>3903.27</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,29 +1193,29 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1245</v>
+        <v>1259.1</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1233.97</v>
+        <v>1237.35</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1245.67</v>
+        <v>1247.36</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1260.42</v>
+        <v>1260.31</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>171.96</v>
+        <v>173.8</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>181.74</v>
+        <v>181.46</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>184.85</v>
+        <v>184.8</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>186.81</v>
+        <v>186.86</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>319.05</v>
+        <v>323.45</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>324.71</v>
+        <v>325.27</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>317.77</v>
+        <v>317.79</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>291.21</v>
+        <v>291.1</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1759.8</v>
+        <v>1760</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1827.71</v>
+        <v>1825.42</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1861.38</v>
+        <v>1860.91</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1819.61</v>
+        <v>1818.09</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>873.4</v>
+        <v>883.8</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>968.6799999999999</v>
+        <v>964.28</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1005.25</v>
+        <v>1003.04</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1049.18</v>
+        <v>1049.43</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>418.7</v>
+        <v>420.35</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>410.67</v>
+        <v>411.13</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>402.99</v>
+        <v>403.04</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>309.7</v>
+        <v>312</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>322.54</v>
+        <v>322.19</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>330.24</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>344.16</v>
+        <v>344.03</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>955.95</v>
+        <v>960</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>990.21</v>
+        <v>991.3</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1016.32</v>
+        <v>1016.9</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>990.7</v>
+        <v>989.79</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>890.15</v>
+        <v>900.35</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>956.34</v>
+        <v>953.7</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>981.28</v>
+        <v>980.4</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>956.8099999999999</v>
+        <v>954.72</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2596</v>
+        <v>2634.4</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2873.19</v>
+        <v>2857.08</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2933.41</v>
+        <v>2924.11</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2738.94</v>
+        <v>2728.77</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>367.3</v>
+        <v>368.15</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>388.67</v>
+        <v>387.43</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>397.08</v>
+        <v>396.63</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>410.11</v>
+        <v>409.88</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11228</v>
+        <v>11420</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>11937.35</v>
+        <v>11949.32</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12552.09</v>
+        <v>12570.83</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13392.27</v>
+        <v>13418.16</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>409.35</v>
+        <v>411.55</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>418.26</v>
+        <v>417.4</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>417.28</v>
+        <v>416.74</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>414.45</v>
+        <v>413.69</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,29 +1765,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1708</v>
+        <v>1761</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1756.3</v>
+        <v>1757.28</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1745.65</v>
+        <v>1745.28</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1661.08</v>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1657.17</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7666</v>
+        <v>8027.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8391.24</v>
+        <v>8389.35</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8583.959999999999</v>
+        <v>8578.219999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8239.940000000001</v>
+        <v>8223.690000000001</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>263.77</v>
+        <v>264.6</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>268.57</v>
+        <v>269.21</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>297.28</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>298.12</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>917.25</v>
+        <v>940.45</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>982.7</v>
+        <v>982.73</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1015.62</v>
+        <v>1015.93</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>974.1900000000001</v>
+        <v>971.8</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1496.2</v>
+        <v>1514.1</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1534.55</v>
+        <v>1534.22</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1546.66</v>
+        <v>1546.49</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1506.29</v>
+        <v>1506.52</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1966,9 +1966,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4813.1</v>
+        <v>4833</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4951.69</v>
+        <v>4943.77</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5007.99</v>
+        <v>5004.79</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5024.4</v>
+        <v>5022.72</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1844.5</v>
+        <v>1856.7</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1900.6</v>
+        <v>1902.82</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1967.95</v>
+        <v>1971.01</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2129.64</v>
+        <v>2133.48</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2311.6</v>
+        <v>2339.1</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2426.25</v>
+        <v>2422.64</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2509.09</v>
+        <v>2509.2</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2545.33</v>
+        <v>2546.36</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10426</v>
+        <v>10675</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10891.48</v>
+        <v>10895.22</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11134.17</v>
+        <v>11141.77</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11433.75</v>
+        <v>11451.09</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>211</v>
+        <v>214.62</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>221.89</v>
+        <v>222.17</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>230.41</v>
+        <v>230.7</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>249.75</v>
+        <v>250.21</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>273</v>
+        <v>279.9</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>291.08</v>
+        <v>291.25</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>307.14</v>
+        <v>307.62</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>362.39</v>
+        <v>363.94</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>6767.5</v>
+        <v>7050</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7230.53</v>
+        <v>7246.64</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7452.61</v>
+        <v>7460.67</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7273.84</v>
+        <v>7267.96</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4359.5</v>
+        <v>4410</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4689.19</v>
+        <v>4681.23</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4778.65</v>
+        <v>4772.31</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4458.42</v>
+        <v>4449.86</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2876.3</v>
+        <v>2918.2</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2756.14</v>
+        <v>2781.76</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2817.64</v>
+        <v>2830.81</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3148.28</v>
+        <v>3165.63</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>244.65</v>
+        <v>249.15</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>260.07</v>
+        <v>259.61</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>266.71</v>
+        <v>266.61</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>278.56</v>
+        <v>278.38</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2856.8</v>
+        <v>2890</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3074.94</v>
+        <v>3069.37</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3145.5</v>
+        <v>3141.34</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3030.64</v>
+        <v>3025.17</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>219.8</v>
+        <v>221.27</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>228.63</v>
+        <v>228.57</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>234.2</v>
+        <v>234.37</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>245.88</v>
+        <v>245.83</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1176.9</v>
+        <v>1216.7</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1233.75</v>
+        <v>1234.11</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1251.78</v>
+        <v>1252.7</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1305.25</v>
+        <v>1309.18</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1319</v>
+        <v>1333</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1350.41</v>
+        <v>1353.17</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1390.46</v>
+        <v>1392.38</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1364.13</v>
+        <v>1362.09</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1175.2</v>
+        <v>1168</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1253.11</v>
+        <v>1247.82</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1267.36</v>
+        <v>1265.28</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1232.15</v>
+        <v>1231.45</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>544.5</v>
+        <v>556.65</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>538.2</v>
+        <v>540.21</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>543.42</v>
+        <v>544.6799999999999</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>604.85</v>
+        <v>606.12</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>9637</v>
+        <v>9778</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10718.9</v>
+        <v>10700.63</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11045.36</v>
+        <v>11029.78</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10328.26</v>
+        <v>10301.49</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1708</v>
+        <v>1734.7</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1794.96</v>
+        <v>1795.91</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1857.8</v>
+        <v>1858.53</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1891.82</v>
+        <v>1891.57</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,29 +2777,29 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1180</v>
+        <v>1197</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1197.01</v>
+        <v>1196.38</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>1196.16</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1229.82</v>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1229.3</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1306.8</v>
+        <v>1301</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1360.68</v>
+        <v>1357.74</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1385.56</v>
+        <v>1384.66</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1398.7</v>
+        <v>1397.85</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>951.9</v>
+        <v>955</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>979.12</v>
+        <v>979.39</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1015.56</v>
+        <v>1016.76</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1080.9</v>
+        <v>1081.43</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1682.5</v>
+        <v>1684.6</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1726.72</v>
+        <v>1724.33</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1752.49</v>
+        <v>1753.19</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1828.91</v>
+        <v>1830.93</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 09-Oct-2026  17:16:44    |    Closing Price Date: 09-Oct-2026</t>
+          <t>Scan Run: 12-Oct-2026  20:05:32    |    Closing Price Date: 09-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>09-Oct-2026  17:16:44</t>
+          <t>12-Oct-2026  20:05:32</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         <v>1254.68</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1333.83</v>
+        <v>1334.81</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>725.88</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>793.67</v>
+        <v>793.7</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>2194.83</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2424.52</v>
+        <v>2424.04</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>170.46</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>192.79</v>
+        <v>192.82</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>1368.89</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.37</v>
+        <v>1360.7</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>1000.31</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1000.05</v>
+        <v>999.79</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>1845</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1884.5</v>
+        <v>1884.54</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>1067.99</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1200.02</v>
+        <v>1200.7</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>3090.11</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3204.17</v>
+        <v>3205.03</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>3884.56</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3903.27</v>
+        <v>3902.61</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>1247.36</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1260.31</v>
+        <v>1260.35</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>184.8</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>186.86</v>
+        <v>186.71</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>317.79</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>291.1</v>
+        <v>291.05</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>1860.91</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1818.09</v>
+        <v>1818.43</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>1003.04</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1049.43</v>
+        <v>1050.13</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>411.13</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>403.04</v>
+        <v>402.88</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>330.24</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>344.03</v>
+        <v>344.19</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>1016.9</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>989.79</v>
+        <v>989.87</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>980.4</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>954.72</v>
+        <v>954.45</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         <v>2857.08</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2924.11</v>
+        <v>2924.1</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2728.77</v>
+        <v>2726.43</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>396.63</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>409.88</v>
+        <v>409.45</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>11949.32</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12570.83</v>
+        <v>12570.82</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13418.16</v>
+        <v>13413.73</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>416.74</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.69</v>
+        <v>413.58</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>1745.28</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1657.17</v>
+        <v>1656.82</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>8578.219999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8223.690000000001</v>
+        <v>8231.209999999999</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>269.21</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>298.12</v>
+        <v>298.25</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>1015.93</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>971.8</v>
+        <v>971.5599999999999</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>1546.49</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1506.52</v>
+        <v>1505.54</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         <v>4943.77</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5004.79</v>
+        <v>5004.78</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5022.72</v>
+        <v>5013.82</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>1971.01</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2133.48</v>
+        <v>2137.9</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>2509.2</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2546.36</v>
+        <v>2547.37</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>11141.77</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11451.09</v>
+        <v>11447.2</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>230.7</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>250.21</v>
+        <v>250.27</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>307.62</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>363.94</v>
+        <v>363.95</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>7460.67</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7267.96</v>
+        <v>7266.29</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>4772.31</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4449.86</v>
+        <v>4448.06</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>2830.81</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3165.63</v>
+        <v>3134.39</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>266.61</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>278.38</v>
+        <v>278.43</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>3141.34</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3025.17</v>
+        <v>3022.13</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>234.37</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>245.83</v>
+        <v>245.85</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>1252.7</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1309.18</v>
+        <v>1308.84</v>
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         <v>1353.17</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1392.38</v>
+        <v>1392.39</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1362.09</v>
+        <v>1363.04</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>1265.28</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1231.45</v>
+        <v>1230.71</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>544.6799999999999</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>606.12</v>
+        <v>606.11</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>11029.78</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10301.49</v>
+        <v>10306.06</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>1858.53</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1891.57</v>
+        <v>1891.52</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>1196.16</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1229.3</v>
+        <v>1230.99</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>1384.66</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1397.85</v>
+        <v>1398.4</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>1016.76</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1081.43</v>
+        <v>1081.7</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>1753.19</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1830.93</v>
+        <v>1828.86</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 12-Oct-2026  20:05:32    |    Closing Price Date: 09-Oct-2026</t>
+          <t>Scan Run: 13-Oct-2026  17:55:05    |    Closing Price Date: 13-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>14</v>
-      </c>
       <c r="D5" s="5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>12-Oct-2026  20:05:32</t>
+          <t>13-Oct-2026  17:55:05</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 14.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 8.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 9 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 13 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 7 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 9 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 4 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 10 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1170.3</v>
+        <v>1166.7</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1217.14</v>
+        <v>1212.33</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1254.68</v>
+        <v>1251.23</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1334.81</v>
+        <v>1333.13</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>707.25</v>
+        <v>714</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>714.5700000000001</v>
+        <v>714.51</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>725.88</v>
+        <v>725.41</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>793.7</v>
+        <v>792.91</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,29 +841,29 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2156</v>
+        <v>2269.3</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2130.57</v>
+        <v>2143.78</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2194.83</v>
+        <v>2197.75</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2424.04</v>
+        <v>2422.5</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -885,24 +885,24 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>162.57</v>
+        <v>169</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>164.02</v>
+        <v>164.5</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>170.46</v>
+        <v>170.41</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>192.82</v>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>192.59</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1355</v>
+        <v>1360.2</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1348.97</v>
+        <v>1350.04</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1368.89</v>
+        <v>1368.55</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>1360.7</v>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>959.1</v>
+        <v>957</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>975.02</v>
+        <v>973.3099999999999</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1000.31</v>
+        <v>998.61</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>999.79</v>
+        <v>999.36</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1805.1</v>
+        <v>1806.5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1812.58</v>
+        <v>1812</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1845</v>
+        <v>1843.49</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1884.54</v>
+        <v>1883.76</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,24 +1061,24 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1023.4</v>
+        <v>1062.1</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1031.15</v>
+        <v>1034.09</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1067.99</v>
+        <v>1067.76</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1200.7</v>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1199.32</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2796.2</v>
+        <v>2864.4</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2960.01</v>
+        <v>2950.91</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3090.11</v>
+        <v>3081.26</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3205.03</v>
+        <v>3201.64</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3703.3</v>
+        <v>3675</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3799.6</v>
+        <v>3787.74</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3884.56</v>
+        <v>3876.34</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3902.61</v>
+        <v>3900.34</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1259.1</v>
+        <v>1268.4</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1237.35</v>
+        <v>1240.31</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1247.36</v>
+        <v>1248.19</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1260.35</v>
+        <v>1260.43</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1218,9 +1218,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>173.8</v>
+        <v>175</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>181.46</v>
+        <v>180.84</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>184.8</v>
+        <v>184.42</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>186.71</v>
+        <v>186.6</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>323.45</v>
+        <v>320.45</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>325.27</v>
+        <v>324.81</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>317.79</v>
+        <v>317.89</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>291.05</v>
+        <v>291.34</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1760</v>
+        <v>1770.7</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1825.42</v>
+        <v>1820.21</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1860.91</v>
+        <v>1857.37</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1818.43</v>
+        <v>1817.96</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>883.8</v>
+        <v>861</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>964.28</v>
+        <v>954.4400000000001</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1003.04</v>
+        <v>997.47</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1050.13</v>
+        <v>1048.25</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>420.35</v>
+        <v>422.12</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>411.13</v>
+        <v>412.22</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>402.88</v>
+        <v>403.24</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>322.19</v>
+        <v>321.12</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>330.24</v>
+        <v>329.49</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>344.19</v>
+        <v>343.86</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>960</v>
+        <v>982.75</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>991.3</v>
+        <v>990.49</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1016.9</v>
+        <v>1015.56</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>989.87</v>
+        <v>989.8</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>900.35</v>
+        <v>902.25</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>953.7</v>
+        <v>948.8</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>980.4</v>
+        <v>977.34</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>954.45</v>
+        <v>953.9299999999999</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2634.4</v>
+        <v>2695</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2857.08</v>
+        <v>2841.64</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2924.1</v>
+        <v>2915.12</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2726.43</v>
+        <v>2726.12</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>368.15</v>
+        <v>380</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>387.43</v>
+        <v>386.72</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>396.63</v>
+        <v>395.98</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>409.45</v>
+        <v>409.16</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11420</v>
+        <v>11245</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>11949.32</v>
+        <v>11882.24</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12570.82</v>
+        <v>12518.83</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13413.73</v>
+        <v>13392.15</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>411.55</v>
+        <v>408.5</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>417.4</v>
+        <v>416.55</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>416.74</v>
+        <v>416.42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.58</v>
+        <v>413.53</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1757.28</v>
+        <v>1757.82</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1745.28</v>
+        <v>1745.97</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1656.82</v>
+        <v>1657.88</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>8027.5</v>
+        <v>7871</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8389.35</v>
+        <v>8339.98</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8578.219999999999</v>
+        <v>8550.48</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8231.209999999999</v>
+        <v>8227.620000000001</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>264.6</v>
+        <v>264.25</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>269.21</v>
+        <v>268.88</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>298.25</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>297.88</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -1897,24 +1897,24 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>940.45</v>
+        <v>988</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>982.73</v>
+        <v>983.24</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1015.93</v>
+        <v>1014.83</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>971.5599999999999</v>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>971.72</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -1922,9 +1922,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
@@ -1941,24 +1941,24 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1514.1</v>
+        <v>1543.5</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1534.22</v>
+        <v>1535.1</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1546.49</v>
+        <v>1546.38</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1505.54</v>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1505.92</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4833</v>
+        <v>4800.4</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4943.77</v>
+        <v>4930.12</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>5004.78</v>
+        <v>4996.77</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5013.82</v>
+        <v>5011.69</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1856.7</v>
+        <v>1875.5</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1902.82</v>
+        <v>1900.22</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1971.01</v>
+        <v>1967.26</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2137.9</v>
+        <v>2135.29</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2339.1</v>
+        <v>2376</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2422.64</v>
+        <v>2418.2</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2509.2</v>
+        <v>2503.98</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2547.37</v>
+        <v>2545.66</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10675</v>
+        <v>10750</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10895.22</v>
+        <v>10881.39</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11141.77</v>
+        <v>11126.41</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11447.2</v>
+        <v>11440.27</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>214.62</v>
+        <v>217.8</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>222.17</v>
+        <v>221.75</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>230.7</v>
+        <v>230.2</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>250.27</v>
+        <v>249.95</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>279.9</v>
+        <v>285.85</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>291.25</v>
+        <v>290.73</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>307.62</v>
+        <v>306.76</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>363.95</v>
+        <v>363.17</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7050</v>
+        <v>7163</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7246.64</v>
+        <v>7238.67</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7460.67</v>
+        <v>7448.99</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7266.29</v>
+        <v>7265.26</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4410</v>
+        <v>4487</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4681.23</v>
+        <v>4662.74</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4772.31</v>
+        <v>4761.12</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4448.06</v>
+        <v>4448.44</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2318,9 +2318,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2918.2</v>
+        <v>2987.8</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2781.76</v>
+        <v>2801.38</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2830.81</v>
+        <v>2836.96</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3134.39</v>
+        <v>3132.94</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>249.15</v>
+        <v>250.5</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>259.61</v>
+        <v>258.74</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>266.61</v>
+        <v>265.98</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>278.43</v>
+        <v>278.15</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2890</v>
+        <v>2912</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3069.37</v>
+        <v>3054.38</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3141.34</v>
+        <v>3132.35</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3022.13</v>
+        <v>3021.03</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>221.27</v>
+        <v>222.65</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>228.57</v>
+        <v>228</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>234.37</v>
+        <v>233.91</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>245.85</v>
+        <v>245.62</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,34 +2513,34 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1216.7</v>
+        <v>1326</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1234.11</v>
+        <v>1242.86</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1252.7</v>
+        <v>1255.58</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1308.84</v>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H42" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1309.01</v>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1353.17</v>
+        <v>1351.34</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1392.39</v>
+        <v>1390.1</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1363.04</v>
+        <v>1362.75</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1168</v>
+        <v>1176.6</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1247.82</v>
+        <v>1241.04</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1265.28</v>
+        <v>1261.8</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1230.71</v>
+        <v>1230.17</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>556.65</v>
+        <v>560</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>540.21</v>
+        <v>542.09</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>544.6799999999999</v>
+        <v>545.28</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>606.11</v>
+        <v>605.65</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>9778</v>
+        <v>10318</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10700.63</v>
+        <v>10664.19</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11029.78</v>
+        <v>11001.86</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10306.06</v>
+        <v>10306.18</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2714,9 +2714,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1734.7</v>
+        <v>1755.7</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1795.91</v>
+        <v>1792.08</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1858.53</v>
+        <v>1854.5</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1891.52</v>
+        <v>1890.17</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1197</v>
+        <v>1240</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1196.38</v>
+        <v>1200.54</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1196.16</v>
+        <v>1197.88</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1230.99</v>
+        <v>1231.08</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2802,9 +2802,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1301</v>
+        <v>1329.6</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1357.74</v>
+        <v>1355.06</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1384.66</v>
+        <v>1382.5</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1398.4</v>
+        <v>1397.71</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>979.39</v>
+        <v>977.54</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1016.76</v>
+        <v>1014.54</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1081.7</v>
+        <v>1080.49</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1684.6</v>
+        <v>1687.2</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1724.33</v>
+        <v>1720.79</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1753.19</v>
+        <v>1750.6</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1828.86</v>
+        <v>1827.45</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 13-Oct-2026  17:55:05    |    Closing Price Date: 13-Oct-2026</t>
+          <t>Scan Run: 14-Oct-2026  15:40:20    |    Closing Price Date: 14-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>13-Oct-2026  17:55:05</t>
+          <t>14-Oct-2026  15:40:20</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 16.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 13 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 14 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 9 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 11 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 8 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1166.7</v>
+        <v>1174.6</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1212.33</v>
+        <v>1204.2</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1251.23</v>
+        <v>1244.76</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1333.13</v>
+        <v>1329.84</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>714</v>
+        <v>710.7</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>714.51</v>
+        <v>713.4</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>725.41</v>
+        <v>724.08</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>792.91</v>
+        <v>791.23</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2269.3</v>
+        <v>2304.9</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2143.78</v>
+        <v>2148.44</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2197.75</v>
+        <v>2188.27</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2422.5</v>
+        <v>2405.75</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -885,29 +885,29 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>169</v>
+        <v>170.92</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>164.5</v>
+        <v>164.94</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>170.41</v>
+        <v>170.11</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>192.59</v>
+        <v>192.07</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
@@ -929,24 +929,24 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1360.2</v>
+        <v>1338.6</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1350.04</v>
+        <v>1348.25</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1368.55</v>
+        <v>1366.33</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.7</v>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1360.28</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>957</v>
+        <v>954.9</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>973.3099999999999</v>
+        <v>968.9</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>998.61</v>
+        <v>994.75</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>999.36</v>
+        <v>998.35</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1806.5</v>
+        <v>1794.6</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1812</v>
+        <v>1807.7</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1843.49</v>
+        <v>1839.17</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1883.76</v>
+        <v>1881.84</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -1061,29 +1061,29 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1062.1</v>
+        <v>1088</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1034.09</v>
+        <v>1038.36</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1067.76</v>
+        <v>1066.82</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1199.32</v>
+        <v>1196.45</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2864.4</v>
+        <v>2793.7</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2950.91</v>
+        <v>2924.47</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3081.26</v>
+        <v>3059.95</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3201.64</v>
+        <v>3193.75</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3675</v>
+        <v>3642</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3787.74</v>
+        <v>3760.44</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3876.34</v>
+        <v>3857.85</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3900.34</v>
+        <v>3895.09</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1268.4</v>
+        <v>1264.6</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1240.31</v>
+        <v>1243.84</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1248.19</v>
+        <v>1249.03</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1260.43</v>
+        <v>1260.4</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>175</v>
+        <v>174.49</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>180.84</v>
+        <v>179.52</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>184.42</v>
+        <v>183.57</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>186.6</v>
+        <v>186.34</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,29 +1281,29 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>320.45</v>
+        <v>316</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>324.81</v>
+        <v>323.8</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>317.89</v>
+        <v>318.01</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>291.34</v>
+        <v>291.9</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1770.7</v>
+        <v>1746.4</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1820.21</v>
+        <v>1808.08</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1857.37</v>
+        <v>1849.37</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1817.96</v>
+        <v>1816.68</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>861</v>
+        <v>852.5</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>954.4400000000001</v>
+        <v>937.0700000000001</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>997.47</v>
+        <v>986.8200000000001</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1048.25</v>
+        <v>1044.5</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>439</v>
+        <v>438.05</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>422.12</v>
+        <v>425.44</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>412.22</v>
+        <v>414.41</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>403.24</v>
+        <v>403.98</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>311</v>
+        <v>313.7</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>321.12</v>
+        <v>319.46</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>329.49</v>
+        <v>328.14</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>343.86</v>
+        <v>343.22</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>982.75</v>
+        <v>957</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>990.49</v>
+        <v>984.64</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1015.56</v>
+        <v>1011.1</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>989.8</v>
+        <v>989.15</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>902.25</v>
+        <v>882.5</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>948.8</v>
+        <v>936.9400000000001</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>977.34</v>
+        <v>970.0700000000001</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>953.9299999999999</v>
+        <v>952.52</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2695</v>
+        <v>2722.6</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2841.64</v>
+        <v>2812.6</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2915.12</v>
+        <v>2896.92</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2726.12</v>
+        <v>2725.14</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>380</v>
+        <v>382.35</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>386.72</v>
+        <v>385.25</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>395.98</v>
+        <v>394.62</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>409.16</v>
+        <v>408.54</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11245</v>
+        <v>11178</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>11882.24</v>
+        <v>11765.72</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12518.83</v>
+        <v>12420.79</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13392.15</v>
+        <v>13349.65</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,34 +1721,34 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>408.5</v>
+        <v>417</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>416.55</v>
+        <v>415.61</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>416.42</v>
+        <v>416.01</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.53</v>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>413.48</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -1765,24 +1765,24 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1763</v>
+        <v>1748.7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1757.82</v>
+        <v>1756.7</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1745.97</v>
+        <v>1746.4</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1657.88</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>1659.73</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7871</v>
+        <v>7824</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8339.98</v>
+        <v>8242.950000000001</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8550.48</v>
+        <v>8492.92</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8227.620000000001</v>
+        <v>8219.16</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>261</v>
+        <v>261.5</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>264.25</v>
+        <v>263.47</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>268.88</v>
+        <v>268.19</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>297.88</v>
+        <v>297.13</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,24 +1897,24 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>988</v>
+        <v>950</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>983.24</v>
+        <v>975.91</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1014.83</v>
+        <v>1009.16</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>971.72</v>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>971.09</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -1922,9 +1922,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
@@ -1941,29 +1941,29 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1543.5</v>
+        <v>1575.2</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1535.1</v>
+        <v>1533.99</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1546.38</v>
+        <v>1544.77</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1505.92</v>
+        <v>1506.27</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4800.4</v>
+        <v>4718.5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4930.12</v>
+        <v>4898.37</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4996.77</v>
+        <v>4978.26</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5011.69</v>
+        <v>5006.64</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,24 +2029,24 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1875.5</v>
+        <v>1895.5</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1900.22</v>
+        <v>1893.37</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1967.26</v>
+        <v>1959.01</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2135.29</v>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2129.81</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2376</v>
+        <v>2344.7</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2418.2</v>
+        <v>2404.05</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2503.98</v>
+        <v>2491.28</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2545.66</v>
+        <v>2541.55</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10750</v>
+        <v>10795</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10881.39</v>
+        <v>10843.91</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11126.41</v>
+        <v>11090.9</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11440.27</v>
+        <v>11424.8</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>217.8</v>
+        <v>219</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>221.75</v>
+        <v>220.81</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>230.2</v>
+        <v>229.13</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>249.95</v>
+        <v>249.28</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>285.85</v>
+        <v>283.8</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>290.73</v>
+        <v>289.54</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>306.76</v>
+        <v>305.02</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>363.17</v>
+        <v>361.61</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7163</v>
+        <v>7082.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7238.67</v>
+        <v>7213.85</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7448.99</v>
+        <v>7422.25</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7265.26</v>
+        <v>7262.01</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4487</v>
+        <v>4444</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4662.74</v>
+        <v>4619.98</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4761.12</v>
+        <v>4735.21</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4448.44</v>
+        <v>4447.93</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2318,9 +2318,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2987.8</v>
+        <v>2971</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2801.38</v>
+        <v>2827.77</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2836.96</v>
+        <v>2845.2</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3132.94</v>
+        <v>3129.17</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>250.5</v>
+        <v>248.95</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>258.74</v>
+        <v>256.98</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>265.98</v>
+        <v>264.67</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>278.15</v>
+        <v>277.57</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2912</v>
+        <v>2873</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3054.38</v>
+        <v>3020.63</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3132.35</v>
+        <v>3111.92</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3021.03</v>
+        <v>3017.96</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>222.65</v>
+        <v>225.5</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>228</v>
+        <v>227.1</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>233.91</v>
+        <v>233.06</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>245.62</v>
+        <v>245.16</v>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1242.86</v>
+        <v>1250.01</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1255.58</v>
+        <v>1257.3</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1309.01</v>
+        <v>1308.35</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2557,24 +2557,24 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1334</v>
+        <v>1383.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1351.34</v>
+        <v>1352.16</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1390.1</v>
+        <v>1387.37</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1362.75</v>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1362.58</v>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -2582,9 +2582,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1176.6</v>
+        <v>1176.2</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1241.04</v>
+        <v>1229.03</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1261.8</v>
+        <v>1255.1</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1230.17</v>
+        <v>1229.07</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,29 +2645,29 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>560</v>
+        <v>544.05</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>542.09</v>
+        <v>543.77</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>545.28</v>
+        <v>545.76</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>605.65</v>
+        <v>604.58</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10318</v>
+        <v>10250</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10664.19</v>
+        <v>10572.77</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>11001.86</v>
+        <v>10936.33</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10306.18</v>
+        <v>10302.96</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2714,9 +2714,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1755.7</v>
+        <v>1721.7</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1792.08</v>
+        <v>1779.45</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1854.5</v>
+        <v>1844.27</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1890.17</v>
+        <v>1886.82</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1240</v>
+        <v>1216</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1200.54</v>
+        <v>1204.58</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1197.88</v>
+        <v>1199.8</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1231.08</v>
+        <v>1230.91</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2802,9 +2802,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1329.6</v>
+        <v>1314.6</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1355.06</v>
+        <v>1347.59</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1382.5</v>
+        <v>1377.18</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1397.71</v>
+        <v>1396.04</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,24 +2865,24 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>960</v>
+        <v>987.9</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>977.54</v>
+        <v>976.92</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1014.54</v>
+        <v>1011.39</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1080.49</v>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1078.37</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1687.2</v>
+        <v>1650</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1720.79</v>
+        <v>1710.66</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1750.6</v>
+        <v>1744.04</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1827.45</v>
+        <v>1824.24</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 15-Oct-2026  15:28:21    |    Closing Price Date: 15-Oct-2026</t>
+          <t>Scan Run: 16-Oct-2026  15:09:02    |    Closing Price Date: 16-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>15-Oct-2026  15:28:21</t>
+          <t>16-Oct-2026  15:09:02</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 40.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 28.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 20 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 21 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 15 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 14 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1215</v>
+        <v>1211.2</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1205.23</v>
+        <v>1205.8</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1243.59</v>
+        <v>1242.32</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1328.53</v>
+        <v>1326.58</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>726.85</v>
+        <v>728.85</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>714.6799999999999</v>
+        <v>716.03</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>724.1900000000001</v>
+        <v>724.37</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>790.88</v>
+        <v>790.46</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2350</v>
+        <v>2465</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2167.63</v>
+        <v>2195.95</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2194.61</v>
+        <v>2205.22</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2404.97</v>
+        <v>2404.67</v>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
@@ -874,9 +874,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J4" s="14" t="inlineStr">
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>174.05</v>
+        <v>184.4</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>165.8</v>
+        <v>167.57</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>170.27</v>
+        <v>170.82</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>191.96</v>
+        <v>191.81</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1389.4</v>
+        <v>1397</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1352.17</v>
+        <v>1356.44</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1367.23</v>
+        <v>1368.4</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1360.83</v>
+        <v>1360.77</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -981,20 +981,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>960</v>
+        <v>962.6</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>968.05</v>
+        <v>967.53</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>993.38</v>
+        <v>992.1799999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>998.21</v>
+        <v>997.78</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1854</v>
+        <v>1905</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1812.11</v>
+        <v>1820.96</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1839.75</v>
+        <v>1842.31</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1881.4</v>
+        <v>1881.21</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -1050,9 +1050,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1110</v>
+        <v>1161.2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1045.18</v>
+        <v>1056.23</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1068.51</v>
+        <v>1072.15</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1196.07</v>
+        <v>1195.52</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -1113,24 +1113,24 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2861.7</v>
+        <v>2920.9</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2918.49</v>
+        <v>2918.72</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3052.18</v>
+        <v>3047.03</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3190.35</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3188.45</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3632</v>
+        <v>3627.1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3748.21</v>
+        <v>3736.67</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3848.99</v>
+        <v>3840.29</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3893.52</v>
+        <v>3889.75</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1248.05</v>
+        <v>1252.04</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1250.56</v>
+        <v>1252.11</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1260.26</v>
+        <v>1260.53</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>176.4</v>
+        <v>175.5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>179.22</v>
+        <v>178.87</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>183.29</v>
+        <v>182.99</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>186.22</v>
+        <v>185.99</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1289,24 +1289,24 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>323</v>
+        <v>325.3</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>323.72</v>
+        <v>323.87</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>318.2</v>
+        <v>318.48</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>292.42</v>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>292.79</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1764</v>
+        <v>1758.8</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1803.88</v>
+        <v>1799.59</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1846.02</v>
+        <v>1842.6</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1815.84</v>
+        <v>1815.14</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>929.54</v>
+        <v>921.58</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>981.77</v>
+        <v>976.45</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1042.48</v>
+        <v>1038.48</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>447.95</v>
+        <v>447.4</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>427.58</v>
+        <v>429.47</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>415.72</v>
+        <v>416.96</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>405.05</v>
+        <v>405.51</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>314.65</v>
+        <v>315.15</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>319.01</v>
+        <v>318.64</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>327.61</v>
+        <v>327.12</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>343.17</v>
+        <v>342.93</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>965.25</v>
+        <v>982.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>982.79</v>
+        <v>982.73</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1009.31</v>
+        <v>1008.24</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>989.04</v>
+        <v>989.52</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>893.85</v>
+        <v>908</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>932.83</v>
+        <v>930.47</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>967.08</v>
+        <v>964.77</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>951.66</v>
+        <v>950.74</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2700</v>
+        <v>2692</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2801.88</v>
+        <v>2791.41</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2889.2</v>
+        <v>2881.47</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2725.54</v>
+        <v>2724.85</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>380.4</v>
+        <v>376.85</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>384.79</v>
+        <v>384.03</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>394.06</v>
+        <v>393.39</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>408.47</v>
+        <v>407.97</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>11445</v>
+        <v>11489</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>11735.17</v>
+        <v>11711.73</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>12382.52</v>
+        <v>12347.48</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13326.29</v>
+        <v>13310.34</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>418</v>
+        <v>417.2</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>415.84</v>
+        <v>415.97</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>416.09</v>
+        <v>416.13</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>413.47</v>
+        <v>413.69</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,29 +1773,29 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1743.2</v>
+        <v>1750.8</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1755.41</v>
+        <v>1754.97</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1746.27</v>
+        <v>1746.45</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1661.1</v>
+        <v>1661.76</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>7889.5</v>
+        <v>7890</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8209.280000000001</v>
+        <v>8178.88</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8469.25</v>
+        <v>8446.540000000001</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8213.719999999999</v>
+        <v>8206.440000000001</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>263.9</v>
+        <v>263.5</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>263.51</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>268.02</v>
+        <v>267.84</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>296.84</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>296.6</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>943.8</v>
+        <v>939.95</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>972.85</v>
+        <v>969.72</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1006.6</v>
+        <v>1003.98</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>970.73</v>
+        <v>970.92</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1650</v>
+        <v>1790</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1545.04</v>
+        <v>1568.37</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1548.9</v>
+        <v>1558.35</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1508.17</v>
+        <v>1510.13</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4778.3</v>
+        <v>4686.9</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4886.93</v>
+        <v>4867.88</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4970.42</v>
+        <v>4959.3</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5006.66</v>
+        <v>5005.59</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1897.1</v>
+        <v>1893.8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>1893.72</v>
+        <v>1893.73</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>1956.58</v>
+        <v>1954.12</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2126.76</v>
+        <v>2125.72</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2350</v>
+        <v>2331.9</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2398.9</v>
+        <v>2392.52</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2485.74</v>
+        <v>2479.71</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2541.4</v>
+        <v>2539.92</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>10862</v>
+        <v>10907</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>10845.63</v>
+        <v>10851.47</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11081.93</v>
+        <v>11075.07</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11423.33</v>
+        <v>11423.03</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>219.01</v>
+        <v>216.25</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>220.64</v>
+        <v>220.22</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>228.73</v>
+        <v>228.24</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>249.02</v>
+        <v>248.73</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>287.05</v>
+        <v>286.85</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>289.31</v>
+        <v>289.07</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>304.32</v>
+        <v>303.63</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>361.05</v>
+        <v>360.29</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7225</v>
+        <v>7284.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7214.91</v>
+        <v>7221.54</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7414.52</v>
+        <v>7409.42</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7261.52</v>
+        <v>7262.39</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -2282,9 +2282,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4455.8</v>
+        <v>4444.8</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4604.34</v>
+        <v>4589.15</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4724.25</v>
+        <v>4713.29</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4438.97</v>
+        <v>4438.64</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2949.7</v>
+        <v>2958.7</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2839.38</v>
+        <v>2850.74</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2849.29</v>
+        <v>2853.58</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3124.88</v>
+        <v>3121.87</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>249.85</v>
+        <v>250.45</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>256.3</v>
+        <v>255.75</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>264.09</v>
+        <v>263.56</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>277.37</v>
+        <v>277.18</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2885.9</v>
+        <v>2920</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>3007.8</v>
+        <v>2999.44</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3103.06</v>
+        <v>3095.88</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3018.4</v>
+        <v>3016.46</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>224.64</v>
+        <v>222</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>226.86</v>
+        <v>226.4</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>232.73</v>
+        <v>232.31</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>245.03</v>
+        <v>244.8</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1360</v>
+        <v>1380</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1260.48</v>
+        <v>1261.8</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1261.33</v>
+        <v>1255.29</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1308.77</v>
+        <v>1296.69</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1275.8</v>
+        <v>1265.5</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1344.89</v>
+        <v>1337.33</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1383</v>
+        <v>1378.39</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1361.63</v>
+        <v>1360.88</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1200.4</v>
+        <v>1216.3</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1226.31</v>
+        <v>1225.35</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1252.96</v>
+        <v>1251.52</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1229.01</v>
+        <v>1228.69</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>550.55</v>
+        <v>553</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>544.41</v>
+        <v>545.23</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>545.95</v>
+        <v>546.23</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>604.24</v>
+        <v>603.4</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10385</v>
+        <v>10405</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10554.89</v>
+        <v>10540.61</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10914.71</v>
+        <v>10894.72</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10298.59</v>
+        <v>10300.55</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1774.93</v>
+        <v>1770.56</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1839.87</v>
+        <v>1835.52</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1885.79</v>
+        <v>1884.57</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1218.8</v>
+        <v>1233</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1205.94</v>
+        <v>1208.52</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1200.54</v>
+        <v>1201.81</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1229.67</v>
+        <v>1229.1</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -2810,9 +2810,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
@@ -2829,20 +2829,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1328</v>
+        <v>1325.1</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1345.72</v>
+        <v>1343.76</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1375.25</v>
+        <v>1373.29</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1394.43</v>
+        <v>1393.88</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>991.45</v>
+        <v>978.9</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>978.3099999999999</v>
+        <v>978.36</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1010.61</v>
+        <v>1009.37</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1077.42</v>
+        <v>1076.36</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1661.8</v>
+        <v>1656.8</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1706</v>
+        <v>1701.32</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1740.81</v>
+        <v>1737.52</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1822.99</v>
+        <v>1821.25</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 19-Oct-2026  17:18:19    |    Closing Price Date: 19-Oct-2026</t>
+          <t>Scan Run: 20-Oct-2026  15:32:02    |    Closing Price Date: 19-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>19-Oct-2026  17:18:19</t>
+          <t>20-Oct-2026  15:32:02</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -152,13 +152,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 20-Oct-2026  15:32:02    |    Closing Price Date: 19-Oct-2026</t>
+          <t>Scan Run: 21-Oct-2026  15:48:27    |    Closing Price Date: 21-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>20-Oct-2026  15:32:02</t>
+          <t>21-Oct-2026  15:48:27</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 15 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 12 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 10 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 9 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,37 +753,37 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1205.43</v>
+        <v>1205.77</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1240.74</v>
+        <v>1239.49</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1323.84</v>
+        <v>1322.7</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -797,37 +797,37 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>712</v>
+        <v>706.95</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>715.64</v>
+        <v>714.8200000000001</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>723.88</v>
+        <v>723.22</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>789.09</v>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
+        <v>788.27</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -841,37 +841,37 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2460.9</v>
+        <v>2529</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2221.19</v>
+        <v>2250.5</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2215.24</v>
+        <v>2227.55</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2398.64</v>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
+        <v>2399.93</v>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -885,37 +885,37 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>182.14</v>
+        <v>189.17</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>168.96</v>
+        <v>170.89</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>171.26</v>
+        <v>171.97</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>191.17</v>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
+        <v>191.15</v>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
@@ -929,37 +929,37 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1358.78</v>
+        <v>1361.27</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1368.89</v>
+        <v>1369.52</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.6</v>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
+        <v>1360.84</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -973,37 +973,37 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>973.7</v>
+        <v>963</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>968.12</v>
+        <v>967.63</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>991.45</v>
+        <v>990.34</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>997.46</v>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
+        <v>997.11</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1017,37 +1017,37 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1875.2</v>
+        <v>1891.7</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1826.13</v>
+        <v>1832.37</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1843.6</v>
+        <v>1845.49</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1877.03</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+        <v>1877.17</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1061,37 +1061,37 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1130.7</v>
+        <v>1168</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1063.32</v>
+        <v>1073.29</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1074.44</v>
+        <v>1078.11</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1192.25</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
+        <v>1192.01</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1105,37 +1105,37 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2907</v>
+        <v>2889</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2917.61</v>
+        <v>2914.88</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3041.54</v>
+        <v>3035.55</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3182.09</v>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="inlineStr">
+        <v>3179.17</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1149,37 +1149,37 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3661.9</v>
+        <v>3636</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3729.55</v>
+        <v>3720.64</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3833.29</v>
+        <v>3825.56</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3883.91</v>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
+        <v>3881.44</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -1193,37 +1193,37 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1236</v>
+        <v>1210</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1250.52</v>
+        <v>1246.66</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1251.48</v>
+        <v>1249.85</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1260.63</v>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
+        <v>1260.12</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -1237,37 +1237,37 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>174.04</v>
+        <v>172.45</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>178.41</v>
+        <v>177.84</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>182.64</v>
+        <v>182.24</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>185.93</v>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
+        <v>185.8</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -1281,37 +1281,37 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>320.2</v>
+        <v>312.35</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>323.52</v>
+        <v>322.46</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>318.55</v>
+        <v>318.31</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>293.33</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
+        <v>293.52</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1325,37 +1325,37 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1743</v>
+        <v>1745.1</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1794.2</v>
+        <v>1789.52</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1838.69</v>
+        <v>1835.02</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1814.99</v>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
+        <v>1814.3</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -1369,37 +1369,37 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>830</v>
+        <v>819.9</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>912.86</v>
+        <v>904</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>970.7</v>
+        <v>964.79</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1036.51</v>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
+        <v>1034.36</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
@@ -1413,37 +1413,37 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>442.3</v>
+        <v>437.8</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>430.69</v>
+        <v>431.37</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>417.96</v>
+        <v>418.74</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>405.66</v>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
+        <v>405.98</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -1457,37 +1457,37 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>317.72</v>
+        <v>316.32</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>326.41</v>
+        <v>325.49</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>342.51</v>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="inlineStr">
+        <v>342.12</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -1501,37 +1501,37 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>957.35</v>
+        <v>926</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>980.3099999999999</v>
+        <v>975.14</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1006.24</v>
+        <v>1003.1</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>988.26</v>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
+        <v>987.64</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1545,37 +1545,37 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>900.45</v>
+        <v>892.85</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>927.61</v>
+        <v>924.3</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>962.24</v>
+        <v>959.52</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>949.92</v>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="inlineStr">
+        <v>949.35</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1589,37 +1589,37 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2657.5</v>
+        <v>2594.5</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2778.66</v>
+        <v>2761.12</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2872.68</v>
+        <v>2861.78</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2724.12</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
+        <v>2722.83</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -1633,37 +1633,37 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>377.2</v>
+        <v>371.2</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>383.38</v>
+        <v>382.22</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>392.75</v>
+        <v>391.91</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>407.23</v>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
+        <v>406.87</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1677,37 +1677,37 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11475</v>
+        <v>11200</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>11689.18</v>
+        <v>11642.59</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12313.27</v>
+        <v>12269.61</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13293.82</v>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
+        <v>13272.99</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -1721,37 +1721,37 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>411.7</v>
+        <v>407.5</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>415.56</v>
+        <v>414.79</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>415.96</v>
+        <v>415.63</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.53</v>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
+        <v>413.47</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1765,37 +1765,37 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1766</v>
+        <v>1748.8</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1756.02</v>
+        <v>1755.34</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1747.22</v>
+        <v>1747.28</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1662.38</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
+        <v>1663.24</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -1809,37 +1809,37 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8133.27</v>
+        <v>8082.48</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8417.26</v>
+        <v>8385.209999999999</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8190.84</v>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J26" s="12" t="inlineStr">
+        <v>8184.96</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -1853,37 +1853,37 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>260.8</v>
+        <v>262</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>263.25</v>
+        <v>263.13</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>267.56</v>
+        <v>267.35</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>296.24</v>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="12" t="inlineStr">
+        <v>295.9</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1897,37 +1897,37 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>926.5</v>
+        <v>904.95</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>965.6</v>
+        <v>959.83</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1000.94</v>
+        <v>997.1799999999999</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>970.14</v>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
+        <v>969.49</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -1941,37 +1941,37 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1779.1</v>
+        <v>1834.7</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1588.44</v>
+        <v>1611.89</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1567.01</v>
+        <v>1577.51</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1511.23</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
+        <v>1514.45</v>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -1985,37 +1985,37 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4700</v>
+        <v>4641.5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4851.89</v>
+        <v>4831.85</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4949.13</v>
+        <v>4937.07</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5006.35</v>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J30" s="12" t="inlineStr">
+        <v>5002.72</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
@@ -2029,37 +2029,37 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1853.2</v>
+        <v>1850.2</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1889.87</v>
+        <v>1886.09</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1950.16</v>
+        <v>1946.24</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2126.93</v>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="inlineStr">
+        <v>2124.18</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2330.7</v>
+        <v>2319.4</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2386.64</v>
+        <v>2380.23</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2473.86</v>
+        <v>2467.81</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2533.72</v>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J32" s="12" t="inlineStr">
+        <v>2531.58</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -2117,37 +2117,37 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10650</v>
+        <v>10849</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10832.29</v>
+        <v>10833.88</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11058.4</v>
+        <v>11050.19</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11413.45</v>
+        <v>11407.83</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="12" t="inlineStr">
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2161,37 +2161,37 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>214</v>
+        <v>211.39</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>219.63</v>
+        <v>218.84</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>227.69</v>
+        <v>227.05</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>247.92</v>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H34" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="12" t="inlineStr">
+        <v>247.56</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
@@ -2205,37 +2205,37 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>278</v>
+        <v>275.7</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>288.02</v>
+        <v>286.84</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>302.63</v>
+        <v>301.57</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>358.69</v>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="inlineStr">
+        <v>357.87</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2249,37 +2249,37 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7349</v>
+        <v>7170.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7233.68</v>
+        <v>7227.66</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7407.05</v>
+        <v>7397.77</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7256.77</v>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H36" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J36" s="12" t="inlineStr">
+        <v>7255.91</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -2293,37 +2293,37 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4424.2</v>
+        <v>4380.9</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4573.44</v>
+        <v>4555.1</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4701.95</v>
+        <v>4689.36</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4437.35</v>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="inlineStr">
+        <v>4436.79</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2337,37 +2337,37 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2891.6</v>
+        <v>2822</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2854.63</v>
+        <v>2851.53</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2855.07</v>
+        <v>2853.78</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3115.55</v>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="12" t="inlineStr">
+        <v>3112.63</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2381,37 +2381,37 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>250.35</v>
+        <v>252.15</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>255.23</v>
+        <v>254.94</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>263.04</v>
+        <v>262.61</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>276.85</v>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J39" s="12" t="inlineStr">
+        <v>276.61</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2425,37 +2425,37 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2879</v>
+        <v>2889.1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>2987.97</v>
+        <v>2978.55</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3087.38</v>
+        <v>3079.6</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3014.54</v>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
+        <v>3013.29</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -2469,37 +2469,37 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>225</v>
+        <v>225.62</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>226.27</v>
+        <v>226.2</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>232.02</v>
+        <v>231.77</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>244.64</v>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
+        <v>244.45</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2513,37 +2513,37 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1379.9</v>
+        <v>1424.2</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1273.05</v>
+        <v>1287.45</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1260.18</v>
+        <v>1266.61</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1295.33</v>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
+        <v>1296.61</v>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I42" s="13" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J42" s="13" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -2557,37 +2557,37 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1242.7</v>
+        <v>1223.9</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1328.31</v>
+        <v>1318.37</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1373.07</v>
+        <v>1367.22</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1358.97</v>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
+        <v>1357.62</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2601,37 +2601,37 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1241.3</v>
+        <v>1222.9</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1226.87</v>
+        <v>1226.49</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1251.12</v>
+        <v>1250.01</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1228.75</v>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
+        <v>1228.69</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -2645,37 +2645,37 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>545.5</v>
+        <v>539.65</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>545.25</v>
+        <v>544.72</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>546.2</v>
+        <v>545.9400000000001</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>601.91</v>
-      </c>
-      <c r="G45" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
+        <v>601.29</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -2689,37 +2689,37 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10287</v>
+        <v>10072</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10516.46</v>
+        <v>10474.13</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10870.89</v>
+        <v>10839.56</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10288.9</v>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
+        <v>10286.74</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -2733,37 +2733,37 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1700</v>
+        <v>1690</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1763.84</v>
+        <v>1756.8</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1830.21</v>
+        <v>1824.71</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1881.74</v>
-      </c>
-      <c r="G47" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J47" s="12" t="inlineStr">
+        <v>1879.84</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2777,37 +2777,37 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1242.5</v>
+        <v>1244.5</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1211.75</v>
+        <v>1214.87</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1203.41</v>
+        <v>1205.02</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1228.77</v>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
+        <v>1228.93</v>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I48" s="13" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J48" s="12" t="inlineStr">
+      <c r="J48" s="13" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -2821,37 +2821,37 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1324.1</v>
+        <v>1314</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1341.88</v>
+        <v>1339.23</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1371.36</v>
+        <v>1369.11</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1392.87</v>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J49" s="12" t="inlineStr">
+        <v>1392.08</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -2865,37 +2865,37 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>966.5</v>
+        <v>970.65</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>977.23</v>
+        <v>976.61</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1007.69</v>
+        <v>1006.24</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1074.16</v>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
+        <v>1073.13</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2909,37 +2909,37 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>21-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1647.8</v>
+        <v>1661</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1696.22</v>
+        <v>1692.87</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1734</v>
+        <v>1731.14</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1821.09</v>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
+        <v>1819.5</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -152,13 +152,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 21-Oct-2026  15:48:27    |    Closing Price Date: 21-Oct-2026</t>
+          <t>Scan Run: 22-Oct-2026  15:46:09    |    Closing Price Date: 22-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>21-Oct-2026  15:48:27</t>
+          <t>22-Oct-2026  15:46:09</t>
         </is>
       </c>
     </row>
@@ -753,37 +753,37 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1209</v>
+        <v>1184.5</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1205.77</v>
+        <v>1203.75</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1239.49</v>
+        <v>1237.34</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1322.7</v>
+        <v>1321.39</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
@@ -797,37 +797,37 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>706.95</v>
+        <v>694.05</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>714.8200000000001</v>
+        <v>712.84</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>723.22</v>
+        <v>722.08</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>788.27</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
+        <v>787.6</v>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
@@ -841,37 +841,37 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2529</v>
+        <v>2506.9</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2250.5</v>
+        <v>2274.92</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2227.55</v>
+        <v>2238.5</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2399.93</v>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
+        <v>2402.21</v>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
@@ -885,37 +885,37 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>189.17</v>
+        <v>190.41</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>170.89</v>
+        <v>172.75</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>171.97</v>
+        <v>172.69</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>191.15</v>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
+        <v>191.27</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
@@ -929,37 +929,37 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1385</v>
+        <v>1398.5</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1361.27</v>
+        <v>1364.82</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1369.52</v>
+        <v>1370.66</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1360.84</v>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
+        <v>1361.54</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
@@ -973,37 +973,37 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>967.63</v>
+        <v>967.86</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>990.34</v>
+        <v>989.54</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>997.11</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+        <v>997.16</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>SBIN</t>
         </is>
@@ -1017,37 +1017,37 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1891.7</v>
+        <v>1895</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1832.37</v>
+        <v>1838.34</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1845.49</v>
+        <v>1847.43</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1877.17</v>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+        <v>1877.91</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
@@ -1061,37 +1061,37 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1168</v>
+        <v>1153.35</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1073.29</v>
+        <v>1080.92</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1078.11</v>
+        <v>1081.06</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1192.01</v>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+        <v>1192.26</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
@@ -1105,37 +1105,37 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2889</v>
+        <v>2864.1</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2914.88</v>
+        <v>2910.05</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3035.55</v>
+        <v>3028.83</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3179.17</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
+        <v>3177.58</v>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>M&amp;M</t>
         </is>
@@ -1149,37 +1149,37 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3636</v>
+        <v>3638.3</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3720.64</v>
+        <v>3712.8</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3825.56</v>
+        <v>3818.21</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3881.44</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
+        <v>3878.94</v>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
@@ -1193,37 +1193,37 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1246.66</v>
+        <v>1243.36</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1249.85</v>
+        <v>1248.37</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1260.12</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+        <v>1259.35</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>AXISBANK</t>
         </is>
@@ -1237,37 +1237,37 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>172.45</v>
+        <v>172.33</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>177.84</v>
+        <v>177.32</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>182.24</v>
+        <v>181.85</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>185.8</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+        <v>185.6</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
@@ -1281,37 +1281,37 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>312.35</v>
+        <v>304.45</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>322.46</v>
+        <v>320.74</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>318.31</v>
+        <v>317.76</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>293.52</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
+        <v>293.45</v>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>ETERNAL</t>
         </is>
@@ -1325,37 +1325,37 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1745.1</v>
+        <v>1758</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1789.52</v>
+        <v>1786.52</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1835.02</v>
+        <v>1832</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1814.3</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
+        <v>1815.64</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
@@ -1369,37 +1369,37 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>819.9</v>
+        <v>817</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>904</v>
+        <v>895.72</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>964.79</v>
+        <v>958.99</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1034.36</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
+        <v>1032.69</v>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>MAXHEALTH</t>
         </is>
@@ -1413,37 +1413,37 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>437.8</v>
+        <v>437</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>431.37</v>
+        <v>431.91</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>418.74</v>
+        <v>419.45</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>405.98</v>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
+        <v>406.16</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
@@ -1457,37 +1457,37 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>303</v>
+        <v>302.6</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>316.32</v>
+        <v>315.01</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>325.49</v>
+        <v>324.59</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>342.12</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
+        <v>341.72</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
@@ -1501,37 +1501,37 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>926</v>
+        <v>942.1</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>975.14</v>
+        <v>971.99</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1003.1</v>
+        <v>1000.7</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>987.64</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
+        <v>987.6</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
@@ -1545,37 +1545,37 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>892.85</v>
+        <v>885.6</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>924.3</v>
+        <v>920.61</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>959.52</v>
+        <v>956.62</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>949.35</v>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
+        <v>948.9</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>HINDALCO</t>
         </is>
@@ -1589,37 +1589,37 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2594.5</v>
+        <v>2550</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2761.12</v>
+        <v>2741.01</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2861.78</v>
+        <v>2849.55</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2722.83</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
+        <v>2721.83</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>ADANIENT</t>
         </is>
@@ -1633,37 +1633,37 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>371.2</v>
+        <v>364.5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>382.22</v>
+        <v>380.53</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>391.91</v>
+        <v>390.83</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>406.87</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
+        <v>406.52</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>BEL</t>
         </is>
@@ -1677,37 +1677,37 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11200</v>
+        <v>11170</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>11642.59</v>
+        <v>11597.58</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12269.61</v>
+        <v>12226.49</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13272.99</v>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
+        <v>13252.98</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
@@ -1721,37 +1721,37 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>407.5</v>
+        <v>402.55</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>414.79</v>
+        <v>413.63</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>415.63</v>
+        <v>415.11</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.47</v>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
+        <v>413.46</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
@@ -1765,37 +1765,37 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1748.8</v>
+        <v>1750</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1755.34</v>
+        <v>1754.83</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1747.28</v>
+        <v>1747.38</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1663.24</v>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
+        <v>1664.62</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
         </is>
@@ -1809,37 +1809,37 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7600</v>
+        <v>7604.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8082.48</v>
+        <v>8036.96</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8385.209999999999</v>
+        <v>8354.6</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8184.96</v>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
+        <v>8185.18</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
@@ -1853,37 +1853,37 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>262</v>
+        <v>258.9</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>263.13</v>
+        <v>262.73</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>267.35</v>
+        <v>267.01</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>295.9</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+        <v>295.64</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>ITC</t>
         </is>
@@ -1897,37 +1897,37 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>904.95</v>
+        <v>900.9</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>959.83</v>
+        <v>954.22</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>997.1799999999999</v>
+        <v>993.4</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>969.49</v>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
+        <v>969.4299999999999</v>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>SHRIRAMFIN</t>
         </is>
@@ -1941,37 +1941,37 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1834.7</v>
+        <v>1829.1</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1611.89</v>
+        <v>1632.58</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1577.51</v>
+        <v>1587.38</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1514.45</v>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
+        <v>1517.67</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
@@ -1985,37 +1985,37 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4641.5</v>
+        <v>4600</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4831.85</v>
+        <v>4809.77</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4937.07</v>
+        <v>4923.85</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5002.72</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+        <v>4998.29</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>INDIGO</t>
         </is>
@@ -2029,37 +2029,37 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1850.2</v>
+        <v>1828.3</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1886.09</v>
+        <v>1880.59</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1946.24</v>
+        <v>1941.62</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2124.18</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
+        <v>2121.67</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2319.4</v>
+        <v>2284.8</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2380.23</v>
+        <v>2371.14</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2467.81</v>
+        <v>2460.63</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2531.58</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
+        <v>2528.78</v>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
         </is>
@@ -2117,37 +2117,37 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10849</v>
+        <v>10958</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10833.88</v>
+        <v>10845.7</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11050.19</v>
+        <v>11046.57</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11407.83</v>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
+        <v>11402.77</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
         </is>
@@ -2161,37 +2161,37 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>211.39</v>
+        <v>210.8</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>218.84</v>
+        <v>218.08</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>227.05</v>
+        <v>226.41</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>247.56</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
+        <v>247.28</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>JIOFIN</t>
         </is>
@@ -2205,37 +2205,37 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>275.7</v>
+        <v>270</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>286.84</v>
+        <v>285.24</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>301.57</v>
+        <v>300.33</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>357.87</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
+        <v>357.41</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>TMPV</t>
         </is>
@@ -2249,37 +2249,37 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7170.5</v>
+        <v>7084.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7227.66</v>
+        <v>7214.03</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7397.77</v>
+        <v>7385.49</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7255.91</v>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
+        <v>7256.32</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>EICHERMOT</t>
         </is>
@@ -2293,37 +2293,37 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4380.9</v>
+        <v>4350</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4555.1</v>
+        <v>4535.57</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4689.36</v>
+        <v>4676.05</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4436.79</v>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
+        <v>4436.36</v>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>TITAN</t>
         </is>
@@ -2337,37 +2337,37 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2822</v>
+        <v>2775.8</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2851.53</v>
+        <v>2844.31</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2853.78</v>
+        <v>2850.72</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3112.63</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
+        <v>3112.51</v>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>TRENT</t>
         </is>
@@ -2381,37 +2381,37 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>252.15</v>
+        <v>248.4</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>254.94</v>
+        <v>254.32</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>262.61</v>
+        <v>262.06</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>276.61</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
+        <v>276.32</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
@@ -2425,37 +2425,37 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2889.1</v>
+        <v>2894.4</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>2978.55</v>
+        <v>2970.54</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3079.6</v>
+        <v>3072.34</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3013.29</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
+        <v>3011.86</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>GRASIM</t>
         </is>
@@ -2469,37 +2469,37 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>225.62</v>
+        <v>225</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>226.2</v>
+        <v>226.09</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>231.77</v>
+        <v>231.5</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>244.45</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
+        <v>244.24</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>ONGC</t>
         </is>
@@ -2513,37 +2513,37 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1424.2</v>
+        <v>1421.7</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1287.45</v>
+        <v>1300.23</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1266.61</v>
+        <v>1272.69</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1296.61</v>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
+        <v>1295.7</v>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I42" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J42" s="13" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
@@ -2557,37 +2557,37 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1223.9</v>
+        <v>1189.9</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1318.37</v>
+        <v>1306.13</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1367.22</v>
+        <v>1360.27</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1357.62</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
+        <v>1356.45</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>NESTLEIND</t>
         </is>
@@ -2601,37 +2601,37 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1222.9</v>
+        <v>1220</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1226.49</v>
+        <v>1225.87</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1250.01</v>
+        <v>1248.83</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1228.69</v>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
+        <v>1228.44</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
@@ -2645,37 +2645,37 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>539.65</v>
+        <v>528.35</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>544.72</v>
+        <v>543.16</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>545.9400000000001</v>
+        <v>545.25</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>601.29</v>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
+        <v>600.23</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>HDFCLIFE</t>
         </is>
@@ -2689,37 +2689,37 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10072</v>
+        <v>10155</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10474.13</v>
+        <v>10443.73</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10839.56</v>
+        <v>10812.72</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10286.74</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
+        <v>10294.87</v>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>BAJAJ-AUTO</t>
         </is>
@@ -2733,37 +2733,37 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1690</v>
+        <v>1678</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1756.8</v>
+        <v>1749.3</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1824.71</v>
+        <v>1818.96</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1879.84</v>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
+        <v>1879.24</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>BAJAJFINSV</t>
         </is>
@@ -2777,37 +2777,37 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1244.5</v>
+        <v>1239</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1214.87</v>
+        <v>1217.17</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1205.02</v>
+        <v>1206.35</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1228.93</v>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
+        <v>1229.47</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="I48" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J48" s="13" t="inlineStr">
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
@@ -2821,37 +2821,37 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1314</v>
+        <v>1330.9</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1339.23</v>
+        <v>1338.44</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1369.11</v>
+        <v>1367.61</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1392.08</v>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
+        <v>1391.76</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>CIPLA</t>
         </is>
@@ -2865,37 +2865,37 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>970.65</v>
+        <v>959.8</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>976.61</v>
+        <v>975</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1006.24</v>
+        <v>1004.41</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1073.13</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
+        <v>1072.42</v>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
@@ -2909,37 +2909,37 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>21-Oct-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1661</v>
+        <v>1642.9</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1692.87</v>
+        <v>1688.11</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1731.14</v>
+        <v>1727.68</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1819.5</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
+        <v>1816.61</v>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 22-Oct-2026  15:46:09    |    Closing Price Date: 22-Oct-2026</t>
+          <t>Scan Run: 23-Oct-2026  15:37:08    |    Closing Price Date: 23-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,11 +586,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>20</v>
@@ -603,7 +603,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>22-Oct-2026  15:46:09</t>
+          <t>23-Oct-2026  15:37:08</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 11 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1184.5</v>
+        <v>1190</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1203.75</v>
+        <v>1202.44</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1237.34</v>
+        <v>1235.48</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1321.39</v>
+        <v>1320.1</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>694.05</v>
+        <v>692.8</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>712.84</v>
+        <v>710.9299999999999</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>722.08</v>
+        <v>720.9299999999999</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>787.6</v>
+        <v>786.67</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2506.9</v>
+        <v>2530</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2274.92</v>
+        <v>2299.21</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2238.5</v>
+        <v>2249.93</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2402.21</v>
+        <v>2403.14</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>190.41</v>
+        <v>189.84</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>172.75</v>
+        <v>174.37</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>172.69</v>
+        <v>173.36</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>191.27</v>
+        <v>191.47</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1398.5</v>
+        <v>1394.2</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1364.82</v>
+        <v>1367.62</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1370.66</v>
+        <v>1371.58</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1361.54</v>
+        <v>1361.68</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -973,24 +973,24 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>970</v>
+        <v>958.6</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>967.86</v>
+        <v>966.98</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>989.54</v>
+        <v>988.33</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>997.16</v>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>997.42</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1895</v>
+        <v>1892.1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1838.34</v>
+        <v>1843.46</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1847.43</v>
+        <v>1849.18</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1877.91</v>
+        <v>1878.15</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1153.35</v>
+        <v>1153.8</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1080.92</v>
+        <v>1087.86</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1081.06</v>
+        <v>1083.91</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1192.26</v>
+        <v>1192.79</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2864.1</v>
+        <v>2861.2</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2910.05</v>
+        <v>2905.39</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3028.83</v>
+        <v>3022.26</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3177.58</v>
+        <v>3177.32</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3638.3</v>
+        <v>3647</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3712.8</v>
+        <v>3706.53</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3818.21</v>
+        <v>3811.5</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3878.94</v>
+        <v>3877.05</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1212</v>
+        <v>1217.5</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1243.36</v>
+        <v>1240.89</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1248.37</v>
+        <v>1247.16</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1259.35</v>
+        <v>1259.04</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>172.33</v>
+        <v>167.67</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>177.32</v>
+        <v>176.4</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>181.85</v>
+        <v>181.29</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>185.6</v>
+        <v>185.35</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>304.45</v>
+        <v>317.4</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>320.74</v>
+        <v>320.42</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>317.76</v>
+        <v>317.75</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>293.45</v>
+        <v>293.51</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1758</v>
+        <v>1748</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1786.52</v>
+        <v>1782.85</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1832</v>
+        <v>1828.71</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1815.64</v>
+        <v>1813.84</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>895.72</v>
+        <v>888.03</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>958.99</v>
+        <v>953.35</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1032.69</v>
+        <v>1030.74</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,24 +1413,24 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>437</v>
+        <v>430.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>431.91</v>
+        <v>431.77</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>419.45</v>
+        <v>419.88</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>406.16</v>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>406.32</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>302.6</v>
+        <v>298</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>315.01</v>
+        <v>313.39</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>324.59</v>
+        <v>323.55</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>341.72</v>
+        <v>341.31</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>942.1</v>
+        <v>928.95</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>971.99</v>
+        <v>967.89</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>1000.7</v>
+        <v>997.89</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>987.6</v>
+        <v>986.73</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>885.6</v>
+        <v>869.85</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>920.61</v>
+        <v>915.78</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>956.62</v>
+        <v>953.22</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>948.9</v>
+        <v>947.9400000000001</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2550</v>
+        <v>2477</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2741.01</v>
+        <v>2715.87</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2849.55</v>
+        <v>2834.94</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2721.83</v>
+        <v>2719.84</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>364.5</v>
+        <v>362</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>380.53</v>
+        <v>378.77</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>390.83</v>
+        <v>389.7</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>406.52</v>
+        <v>405.96</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11170</v>
+        <v>11230</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>11597.58</v>
+        <v>11562.58</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12226.49</v>
+        <v>12187.41</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13252.98</v>
+        <v>13234.03</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>402.55</v>
+        <v>397.45</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>413.63</v>
+        <v>412.09</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>415.11</v>
+        <v>414.42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.46</v>
+        <v>413.3</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,29 +1765,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1750</v>
+        <v>1702.7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1754.83</v>
+        <v>1749.86</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1747.38</v>
+        <v>1745.63</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1664.62</v>
+        <v>1665.49</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7604.5</v>
+        <v>7730</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8036.96</v>
+        <v>8007.73</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8354.6</v>
+        <v>8330.1</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8185.18</v>
+        <v>8180.31</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>258.9</v>
+        <v>257.9</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>262.73</v>
+        <v>262.27</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>267.01</v>
+        <v>266.66</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>295.64</v>
+        <v>295.37</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>900.9</v>
+        <v>865</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>954.22</v>
+        <v>945.72</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>993.4</v>
+        <v>988.37</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>969.4299999999999</v>
+        <v>967.71</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1829.1</v>
+        <v>1790</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1632.58</v>
+        <v>1635.46</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1587.38</v>
+        <v>1582.81</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1517.67</v>
+        <v>1509.25</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4600</v>
+        <v>4549</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4809.77</v>
+        <v>4784.94</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4923.85</v>
+        <v>4909.15</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4998.29</v>
+        <v>4994.65</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1828.3</v>
+        <v>1814.7</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1880.59</v>
+        <v>1874.31</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1941.62</v>
+        <v>1936.64</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2121.67</v>
+        <v>2118.22</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2284.8</v>
+        <v>2307</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2371.14</v>
+        <v>2365.03</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2460.63</v>
+        <v>2454.61</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2528.78</v>
+        <v>2527.3</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,29 +2117,29 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10958</v>
+        <v>11050</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10845.7</v>
+        <v>10865.16</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11046.57</v>
+        <v>11046.71</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11402.77</v>
+        <v>11397.21</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>210.8</v>
+        <v>205.03</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>218.08</v>
+        <v>216.84</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>226.41</v>
+        <v>225.57</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>247.28</v>
+        <v>246.79</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>270</v>
+        <v>264.6</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>285.24</v>
+        <v>283.27</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>300.33</v>
+        <v>298.93</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>357.41</v>
+        <v>356.26</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7084.5</v>
+        <v>7066</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7214.03</v>
+        <v>7199.93</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7385.49</v>
+        <v>7372.96</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7256.32</v>
+        <v>7255.91</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4350</v>
+        <v>4299.7</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4535.57</v>
+        <v>4513.1</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4676.05</v>
+        <v>4661.29</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4436.36</v>
+        <v>4435.1</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2775.8</v>
+        <v>2727.5</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2844.31</v>
+        <v>2833.19</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2850.72</v>
+        <v>2845.89</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3112.51</v>
+        <v>3108.33</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>248.4</v>
+        <v>247.4</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>254.32</v>
+        <v>253.66</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>262.06</v>
+        <v>261.48</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>276.32</v>
+        <v>275.99</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2894.4</v>
+        <v>2894</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>2970.54</v>
+        <v>2963.25</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3072.34</v>
+        <v>3065.34</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3011.86</v>
+        <v>3009.99</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,24 +2469,24 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>225</v>
+        <v>227.5</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>226.09</v>
+        <v>226.22</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>231.5</v>
+        <v>231.35</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>244.24</v>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>244.04</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1421.7</v>
+        <v>1422.2</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1300.23</v>
+        <v>1311.85</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1272.69</v>
+        <v>1278.55</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1295.7</v>
+        <v>1296.82</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1189.9</v>
+        <v>1175</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1306.13</v>
+        <v>1293.64</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1360.27</v>
+        <v>1353</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1356.45</v>
+        <v>1355.57</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1220</v>
+        <v>1185.5</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1225.87</v>
+        <v>1222.03</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1248.83</v>
+        <v>1246.35</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1228.44</v>
+        <v>1227.79</v>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>528.35</v>
+        <v>523.75</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>543.16</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>545.25</v>
+        <v>544.41</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>600.23</v>
+        <v>599.4299999999999</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10155</v>
+        <v>10072</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10443.73</v>
+        <v>10408.33</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10812.72</v>
+        <v>10783.67</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10294.87</v>
+        <v>10292.3</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1678</v>
+        <v>1655</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1749.3</v>
+        <v>1740.32</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1818.96</v>
+        <v>1812.53</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1879.24</v>
+        <v>1876.98</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1239</v>
+        <v>1229.5</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1217.17</v>
+        <v>1218.34</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1206.35</v>
+        <v>1207.26</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1229.47</v>
+        <v>1229.4</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1330.9</v>
+        <v>1338</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1338.44</v>
+        <v>1338.39</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1367.61</v>
+        <v>1366.45</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1391.76</v>
+        <v>1390.59</v>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>959.8</v>
+        <v>963.9</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>975</v>
+        <v>973.95</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1004.41</v>
+        <v>1002.83</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1072.42</v>
+        <v>1071.33</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>22-Oct-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1642.9</v>
+        <v>1640</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1688.11</v>
+        <v>1683.53</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1727.68</v>
+        <v>1724.24</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1816.61</v>
+        <v>1815.03</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 23-Oct-2026  15:37:08    |    Closing Price Date: 23-Oct-2026</t>
+          <t>Scan Run: 26-Oct-2026  17:06:30    |    Closing Price Date: 26-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>20</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>18</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>23-Oct-2026  15:37:08</t>
+          <t>26-Oct-2026  17:06:30</t>
         </is>
       </c>
     </row>
@@ -617,21 +617,21 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Medium-Term (50 EMA): STRONGLY BEARISH — 26.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 18.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,21 +645,21 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 15 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 13 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 9 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 10 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1190</v>
+        <v>1201.8</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1202.44</v>
+        <v>1202.38</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1235.48</v>
+        <v>1234.16</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1320.1</v>
+        <v>1316.46</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>692.8</v>
+        <v>688.05</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>710.9299999999999</v>
+        <v>708.75</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>720.9299999999999</v>
+        <v>719.64</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>786.67</v>
+        <v>785.79</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2530</v>
+        <v>2535</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2299.21</v>
+        <v>2321.67</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2249.93</v>
+        <v>2261.11</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2403.14</v>
+        <v>2401.36</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>189.84</v>
+        <v>189.2</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>174.37</v>
+        <v>175.79</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>173.36</v>
+        <v>173.98</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>191.47</v>
+        <v>191.35</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1394.2</v>
+        <v>1403</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1367.62</v>
+        <v>1370.99</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1371.58</v>
+        <v>1372.82</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1361.68</v>
+        <v>1363.79</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>958.6</v>
+        <v>960.8</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>966.98</v>
+        <v>966.39</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>988.33</v>
+        <v>987.25</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>997.42</v>
+        <v>996.74</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1892.1</v>
+        <v>1917.5</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1843.46</v>
+        <v>1850.51</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1849.18</v>
+        <v>1851.86</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1878.15</v>
+        <v>1878.06</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1153.8</v>
+        <v>1166</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1087.86</v>
+        <v>1095.3</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1083.91</v>
+        <v>1087.13</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1192.79</v>
+        <v>1191.55</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2861.2</v>
+        <v>2853.1</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2905.39</v>
+        <v>2900.41</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3022.26</v>
+        <v>3015.62</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3177.32</v>
+        <v>3176.26</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3647</v>
+        <v>3680</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3706.53</v>
+        <v>3704.01</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3811.5</v>
+        <v>3806.34</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3877.05</v>
+        <v>3875.07</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1217.5</v>
+        <v>1220</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1240.89</v>
+        <v>1238.9</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1247.16</v>
+        <v>1246.09</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1259.04</v>
+        <v>1255.68</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>167.67</v>
+        <v>169.94</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>176.4</v>
+        <v>175.78</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>181.29</v>
+        <v>180.85</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>185.35</v>
+        <v>185.44</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,29 +1281,29 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>317.4</v>
+        <v>325.55</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>320.42</v>
+        <v>320.91</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>317.75</v>
+        <v>318.05</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>293.51</v>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>294.24</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1748</v>
+        <v>1740</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1782.85</v>
+        <v>1778.77</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1828.71</v>
+        <v>1825.23</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1813.84</v>
+        <v>1812.74</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>888.03</v>
+        <v>882.98</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>953.35</v>
+        <v>948.71</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1030.74</v>
+        <v>1026.73</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,24 +1413,24 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>430.5</v>
+        <v>440.75</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>431.77</v>
+        <v>432.63</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>419.88</v>
+        <v>420.7</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>406.32</v>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>406.57</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>313.39</v>
+        <v>312.12</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>323.55</v>
+        <v>322.63</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>341.31</v>
+        <v>340.86</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>928.95</v>
+        <v>918.7</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>967.89</v>
+        <v>963.21</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>997.89</v>
+        <v>994.78</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>986.73</v>
+        <v>987.2</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>869.85</v>
+        <v>885.65</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>915.78</v>
+        <v>912.91</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>953.22</v>
+        <v>950.5700000000001</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>947.9400000000001</v>
+        <v>948</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2477</v>
+        <v>2508</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2715.87</v>
+        <v>2696.07</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2834.94</v>
+        <v>2822.12</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2719.84</v>
+        <v>2718.21</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>378.77</v>
+        <v>377.27</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>389.7</v>
+        <v>388.66</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>405.96</v>
+        <v>405.26</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11230</v>
+        <v>11220</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>11562.58</v>
+        <v>11529.95</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12187.41</v>
+        <v>12149.47</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13234.03</v>
+        <v>13207.28</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>397.45</v>
+        <v>405</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>412.09</v>
+        <v>411.41</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>414.42</v>
+        <v>414.05</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.3</v>
+        <v>413.23</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,29 +1765,29 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1702.7</v>
+        <v>1752.5</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1749.86</v>
+        <v>1750.11</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1745.63</v>
+        <v>1745.9</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1665.49</v>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1666.09</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7730</v>
+        <v>7844</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8007.73</v>
+        <v>7992.13</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8330.1</v>
+        <v>8311.040000000001</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8180.31</v>
+        <v>8172.72</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>257.9</v>
+        <v>260.5</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>262.27</v>
+        <v>262.1</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>266.66</v>
+        <v>266.42</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>295.37</v>
+        <v>294.84</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>865</v>
+        <v>825</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>945.72</v>
+        <v>934.22</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>988.37</v>
+        <v>981.96</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>967.71</v>
+        <v>965.75</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1790</v>
+        <v>1795</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1635.46</v>
+        <v>1650.65</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1582.81</v>
+        <v>1591.14</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1509.25</v>
+        <v>1509.45</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4549</v>
+        <v>4608</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4784.94</v>
+        <v>4768.09</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4909.15</v>
+        <v>4897.34</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4994.65</v>
+        <v>4987.77</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1814.7</v>
+        <v>1818.6</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1874.31</v>
+        <v>1869.01</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1936.64</v>
+        <v>1932.01</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2118.22</v>
+        <v>2112.99</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2307</v>
+        <v>2322</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2365.03</v>
+        <v>2360.94</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2454.61</v>
+        <v>2449.41</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2527.3</v>
+        <v>2523.75</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11050</v>
+        <v>11180</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10865.16</v>
+        <v>10895.14</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11046.71</v>
+        <v>11051.93</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11397.21</v>
+        <v>11400.3</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>205.03</v>
+        <v>205.23</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>216.84</v>
+        <v>215.73</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>225.57</v>
+        <v>224.77</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>246.79</v>
+        <v>246.28</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>264.6</v>
+        <v>263.7</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>283.27</v>
+        <v>281.41</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>298.93</v>
+        <v>297.55</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>356.26</v>
+        <v>355.7</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7066</v>
+        <v>7099.5</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7199.93</v>
+        <v>7190.36</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7372.96</v>
+        <v>7362.24</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7255.91</v>
+        <v>7251.42</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4299.7</v>
+        <v>4323</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4513.1</v>
+        <v>4495</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4661.29</v>
+        <v>4648.03</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4435.1</v>
+        <v>4434.67</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2727.5</v>
+        <v>2754</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2833.19</v>
+        <v>2825.65</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2845.89</v>
+        <v>2842.28</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3108.33</v>
+        <v>3104.53</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>247.4</v>
+        <v>247</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>253.66</v>
+        <v>253.02</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>261.48</v>
+        <v>260.91</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>275.99</v>
+        <v>275.7</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2894</v>
+        <v>2950</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>2963.25</v>
+        <v>2961.99</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3065.34</v>
+        <v>3060.82</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3009.99</v>
+        <v>3008.52</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>227.5</v>
+        <v>228.44</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>226.22</v>
+        <v>226.43</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>231.35</v>
+        <v>231.23</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>244.04</v>
+        <v>243.97</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1422.2</v>
+        <v>1417</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1311.85</v>
+        <v>1321.86</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1278.55</v>
+        <v>1283.98</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1296.82</v>
+        <v>1297.18</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1175</v>
+        <v>1173.5</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1293.64</v>
+        <v>1282.2</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1353</v>
+        <v>1345.96</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1355.57</v>
+        <v>1354.03</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,34 +2601,34 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1185.5</v>
+        <v>1260</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1222.03</v>
+        <v>1225.65</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1246.35</v>
+        <v>1246.89</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1227.79</v>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1228.32</v>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>523.75</v>
+        <v>519</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>541.3099999999999</v>
+        <v>539.1900000000001</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>544.41</v>
+        <v>543.41</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>599.4299999999999</v>
+        <v>598.48</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,20 +2689,20 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10072</v>
+        <v>10071</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10408.33</v>
+        <v>10376.2</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10783.67</v>
+        <v>10755.72</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10292.3</v>
+        <v>10295.93</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1655</v>
+        <v>1670.9</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1740.32</v>
+        <v>1733.71</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1812.53</v>
+        <v>1806.97</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1876.98</v>
+        <v>1875.72</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1229.5</v>
+        <v>1310.9</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1218.34</v>
+        <v>1227.16</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1207.26</v>
+        <v>1211.33</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1229.4</v>
+        <v>1230.21</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,24 +2821,24 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1338</v>
+        <v>1355</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1338.39</v>
+        <v>1339.98</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1366.45</v>
+        <v>1366</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1390.59</v>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1390.15</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -2865,20 +2865,20 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>963.9</v>
+        <v>936.5</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>973.95</v>
+        <v>970.38</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>1002.83</v>
+        <v>1000.22</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1071.33</v>
+        <v>1070.36</v>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>26-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1640</v>
+        <v>1643.7</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1683.53</v>
+        <v>1679.73</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1724.24</v>
+        <v>1721.08</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1815.03</v>
+        <v>1812.29</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 26-Oct-2026  17:06:30    |    Closing Price Date: 26-Oct-2026</t>
+          <t>Scan Run: 27-Oct-2026  16:09:43    |    Closing Price Date: 27-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -586,24 +586,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>26</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>26-Oct-2026  17:06:30</t>
+          <t>27-Oct-2026  16:09:43</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 34.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 20.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 22.0% stocks above EMA (market broadly declining)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 15 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 17 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 10 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 11 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>1201.8</v>
+        <v>1196.2</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1202.38</v>
+        <v>1201.79</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1234.16</v>
+        <v>1232.67</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1316.46</v>
+        <v>1315.26</v>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>688.05</v>
+        <v>680.2</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>708.75</v>
+        <v>706.03</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>719.64</v>
+        <v>718.09</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>785.79</v>
+        <v>784.74</v>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
@@ -841,20 +841,20 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2535</v>
+        <v>2496.9</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2321.67</v>
+        <v>2338.36</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>2261.11</v>
+        <v>2270.36</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>2401.36</v>
+        <v>2402.31</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -885,20 +885,20 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>189.2</v>
+        <v>187</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>175.79</v>
+        <v>176.85</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>173.98</v>
+        <v>174.49</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>191.35</v>
+        <v>191.31</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>1403</v>
+        <v>1386.9</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1370.99</v>
+        <v>1372.5</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1372.82</v>
+        <v>1373.37</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1363.79</v>
+        <v>1364.02</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -973,20 +973,20 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>960.8</v>
+        <v>945.1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>966.39</v>
+        <v>964.36</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>987.25</v>
+        <v>985.59</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>996.74</v>
+        <v>996.23</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -1017,20 +1017,20 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1917.5</v>
+        <v>1978.8</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>1850.51</v>
+        <v>1862.73</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1851.86</v>
+        <v>1856.84</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1878.06</v>
+        <v>1879.06</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1095.3</v>
+        <v>1101.75</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1087.13</v>
+        <v>1090.11</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1191.55</v>
+        <v>1191.27</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1105,20 +1105,20 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2853.1</v>
+        <v>2858.4</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2900.41</v>
+        <v>2896.41</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>3015.62</v>
+        <v>3009.46</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3176.26</v>
+        <v>3173.1</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1149,20 +1149,20 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3680</v>
+        <v>3665.1</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>3704.01</v>
+        <v>3700.3</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>3806.34</v>
+        <v>3800.8</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3875.07</v>
+        <v>3872.98</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1193,20 +1193,20 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1220</v>
+        <v>1205.7</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1238.9</v>
+        <v>1235.74</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1246.09</v>
+        <v>1244.51</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1255.68</v>
+        <v>1255.19</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
@@ -1237,20 +1237,20 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>169.94</v>
+        <v>171.42</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>175.78</v>
+        <v>175.37</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>180.85</v>
+        <v>180.48</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>185.44</v>
+        <v>185.3</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>325.55</v>
+        <v>331</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>320.91</v>
+        <v>321.87</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>318.05</v>
+        <v>318.56</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>294.24</v>
+        <v>294.61</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1325,20 +1325,20 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1740</v>
+        <v>1751.2</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>1778.77</v>
+        <v>1776.14</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>1825.23</v>
+        <v>1822.33</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1812.74</v>
+        <v>1812.12</v>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
@@ -1369,20 +1369,20 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>882.98</v>
+        <v>879.36</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>948.71</v>
+        <v>944.64</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1026.73</v>
+        <v>1024.92</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1413,20 +1413,20 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>440.75</v>
+        <v>442.5</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>432.63</v>
+        <v>433.57</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>420.7</v>
+        <v>421.56</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>406.57</v>
+        <v>406.93</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -1457,20 +1457,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>300</v>
+        <v>301.8</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>312.12</v>
+        <v>311.13</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>322.63</v>
+        <v>321.81</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>340.86</v>
+        <v>340.47</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>918.7</v>
+        <v>912</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>963.21</v>
+        <v>958.33</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>994.78</v>
+        <v>991.54</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>987.2</v>
+        <v>986.45</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>885.65</v>
+        <v>891.2</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>912.91</v>
+        <v>910.84</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>950.5700000000001</v>
+        <v>948.24</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>948</v>
+        <v>947.4400000000001</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1589,20 +1589,20 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>2508</v>
+        <v>2490</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2696.07</v>
+        <v>2676.45</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>2822.12</v>
+        <v>2809.09</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>2718.21</v>
+        <v>2715.94</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>363</v>
+        <v>367.95</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>377.27</v>
+        <v>376.38</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>388.66</v>
+        <v>387.84</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>405.26</v>
+        <v>404.89</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1677,20 +1677,20 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>11220</v>
+        <v>11450</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>11529.95</v>
+        <v>11522.34</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>12149.47</v>
+        <v>12122.04</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>13207.28</v>
+        <v>13189.79</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
@@ -1721,20 +1721,20 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>411.41</v>
+        <v>410.14</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>414.05</v>
+        <v>413.42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>413.23</v>
+        <v>413.08</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1752.5</v>
+        <v>1754.5</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>1750.11</v>
+        <v>1750.53</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>1745.9</v>
+        <v>1746.24</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>1666.09</v>
+        <v>1666.97</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -1809,20 +1809,20 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7844</v>
+        <v>7791.5</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>7992.13</v>
+        <v>7973.02</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>8311.040000000001</v>
+        <v>8290.66</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>8172.72</v>
+        <v>8168.92</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1853,20 +1853,20 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>260.5</v>
+        <v>260</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>262.1</v>
+        <v>261.9</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>266.42</v>
+        <v>266.16</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>294.84</v>
+        <v>294.49</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>825</v>
+        <v>823.6</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>934.22</v>
+        <v>923.6900000000001</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>981.96</v>
+        <v>975.75</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>965.75</v>
+        <v>964.34</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>1795</v>
+        <v>1811.4</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1650.65</v>
+        <v>1665.96</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>1591.14</v>
+        <v>1599.77</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1509.45</v>
+        <v>1512.46</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -1985,20 +1985,20 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>4608</v>
+        <v>4596.5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>4768.09</v>
+        <v>4751.75</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>4897.34</v>
+        <v>4885.54</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>4987.77</v>
+        <v>4983.87</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -2029,20 +2029,20 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1818.6</v>
+        <v>1818</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1869.01</v>
+        <v>1864.15</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>1932.01</v>
+        <v>1927.54</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>2112.99</v>
+        <v>2110.06</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2322</v>
+        <v>2277</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2360.94</v>
+        <v>2352.94</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>2449.41</v>
+        <v>2442.64</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>2523.75</v>
+        <v>2521.3</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2117,20 +2117,20 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>11180</v>
+        <v>11150</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>10895.14</v>
+        <v>10919.41</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>11051.93</v>
+        <v>11055.78</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>11400.3</v>
+        <v>11397.8</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>205.23</v>
+        <v>207.24</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>215.73</v>
+        <v>214.92</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>224.77</v>
+        <v>224.09</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>246.28</v>
+        <v>245.89</v>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
@@ -2205,20 +2205,20 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>263.7</v>
+        <v>261.2</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>281.41</v>
+        <v>279.49</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>297.55</v>
+        <v>296.13</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>355.7</v>
+        <v>354.76</v>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7099.5</v>
+        <v>7165</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7190.36</v>
+        <v>7187.95</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>7362.24</v>
+        <v>7354.5</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>7251.42</v>
+        <v>7250.56</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2293,20 +2293,20 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4323</v>
+        <v>4365.9</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>4495</v>
+        <v>4482.7</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>4648.03</v>
+        <v>4636.96</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>4434.67</v>
+        <v>4433.98</v>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
@@ -2337,20 +2337,20 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>2754</v>
+        <v>2820.6</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>2825.65</v>
+        <v>2825.17</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>2842.28</v>
+        <v>2841.43</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3104.53</v>
+        <v>3101.71</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2381,20 +2381,20 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>247</v>
+        <v>251.75</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>253.02</v>
+        <v>252.9</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>260.91</v>
+        <v>260.55</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>275.7</v>
+        <v>275.46</v>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
@@ -2425,20 +2425,20 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2950</v>
+        <v>2900.8</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>2961.99</v>
+        <v>2956.16</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>3060.82</v>
+        <v>3054.54</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3008.52</v>
+        <v>3007.45</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>228.44</v>
+        <v>229.85</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>226.43</v>
+        <v>226.76</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>231.23</v>
+        <v>231.18</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>243.97</v>
+        <v>243.83</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1321.86</v>
+        <v>1331.21</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>1283.98</v>
+        <v>1289.32</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1297.18</v>
+        <v>1298.4</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -2557,20 +2557,20 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>1173.5</v>
+        <v>1180.5</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1282.2</v>
+        <v>1272.52</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>1345.96</v>
+        <v>1339.47</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>1354.03</v>
+        <v>1352.31</v>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2601,20 +2601,20 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1260</v>
+        <v>1252.7</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1225.65</v>
+        <v>1228.22</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>1246.89</v>
+        <v>1247.11</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>1228.32</v>
+        <v>1228.56</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -2645,20 +2645,20 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>519</v>
+        <v>513.6</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>539.1900000000001</v>
+        <v>536.75</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>543.41</v>
+        <v>542.24</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>598.48</v>
+        <v>597.64</v>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
@@ -2689,24 +2689,24 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>10071</v>
+        <v>10390</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>10376.2</v>
+        <v>10377.52</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>10755.72</v>
+        <v>10741.38</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>10295.93</v>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>10296.86</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
@@ -2714,9 +2714,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
@@ -2733,20 +2733,20 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>1670.9</v>
+        <v>1677</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1733.71</v>
+        <v>1728.31</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>1806.97</v>
+        <v>1801.88</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1875.72</v>
+        <v>1873.75</v>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
@@ -2777,20 +2777,20 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1310.9</v>
+        <v>1310</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1227.16</v>
+        <v>1235.05</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1211.33</v>
+        <v>1215.2</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>1230.21</v>
+        <v>1231</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -2821,20 +2821,20 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1339.98</v>
+        <v>1340.93</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>1366</v>
+        <v>1365.37</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1390.15</v>
+        <v>1389.75</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -2865,24 +2865,24 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>936.5</v>
+        <v>1000</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>970.38</v>
+        <v>973.2</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>1000.22</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1070.36</v>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1069.66</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -2909,20 +2909,20 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>27-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>1643.7</v>
+        <v>1633</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1679.73</v>
+        <v>1675.28</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1721.08</v>
+        <v>1717.63</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>1812.29</v>
+        <v>1810.51</v>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 28-Oct-2026  16:57:00    |    Closing Price Date: 28-Oct-2026</t>
+          <t>Scan Run: 29-Oct-2026  17:17:15    |    Closing Price Date: 29-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>24</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>28-Oct-2026  16:57:00</t>
+          <t>29-Oct-2026  17:17:15</t>
         </is>
       </c>
     </row>
@@ -625,14 +625,14 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): MODERATELY BEARISH — 42.0% stocks above EMA</t>
+          <t>Short-Term  (20 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,14 +653,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 21 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 23 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 15 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1158</v>
+        <v>1167.4</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1197.62</v>
+        <v>1194.74</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1229.74</v>
+        <v>1227.3</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1313.7</v>
+        <v>1311.57</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>685.3</v>
+        <v>683.3</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>704.0599999999999</v>
+        <v>702.08</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>716.8099999999999</v>
+        <v>715.49</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>783.75</v>
+        <v>782.89</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2460</v>
+        <v>2478</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2349.94</v>
+        <v>2362.14</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2277.79</v>
+        <v>2285.65</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2402.88</v>
+        <v>2403.68</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>184.5</v>
+        <v>190.1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>177.58</v>
+        <v>178.77</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>174.89</v>
+        <v>175.48</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>191.24</v>
+        <v>191.2</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1377.6</v>
+        <v>1386.6</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1372.99</v>
+        <v>1374.28</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1373.53</v>
+        <v>1374.05</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1364.16</v>
+        <v>1364.71</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,24 +981,24 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>956.8</v>
+        <v>971.9</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>963.64</v>
+        <v>964.4299999999999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>984.46</v>
+        <v>983.97</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>995.83</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>995.21</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1948.1</v>
+        <v>1972.1</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1870.86</v>
+        <v>1880.5</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1860.42</v>
+        <v>1864.8</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1879.75</v>
+        <v>1880.57</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1123.15</v>
+        <v>1146.5</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1103.79</v>
+        <v>1107.85</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1091.4</v>
+        <v>1093.56</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1190.59</v>
+        <v>1189.6</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2869.9</v>
+        <v>2890</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2893.89</v>
+        <v>2893.52</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>3003.99</v>
+        <v>2999.52</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3170.08</v>
+        <v>3167.74</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3801.3</v>
+        <v>3837.1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3709.92</v>
+        <v>3722.03</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3800.82</v>
+        <v>3802.24</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3872.27</v>
+        <v>3870.3</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1234.24</v>
+        <v>1233.36</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1243.55</v>
+        <v>1242.82</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1254.84</v>
+        <v>1254.47</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>169.27</v>
+        <v>169.46</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>174.79</v>
+        <v>174.28</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>180.04</v>
+        <v>179.62</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>185.14</v>
+        <v>184.99</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>326</v>
+        <v>337.85</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>322.27</v>
+        <v>323.75</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>318.85</v>
+        <v>319.6</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>294.92</v>
+        <v>296.55</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1757.5</v>
+        <v>1761</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1774.37</v>
+        <v>1773.09</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1819.78</v>
+        <v>1817.48</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1811.58</v>
+        <v>1810.47</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>851.5</v>
+        <v>851.15</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>876.71</v>
+        <v>874.28</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>940.99</v>
+        <v>937.46</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1023.19</v>
+        <v>1021.51</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>434.18</v>
+        <v>436.54</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>422.28</v>
+        <v>423.72</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>407.25</v>
+        <v>407.73</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,24 +1465,24 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>303.75</v>
+        <v>310.5</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>310.43</v>
+        <v>310.44</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>321.1</v>
+        <v>320.69</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>339.78</v>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>917.25</v>
+        <v>938.9</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>954.42</v>
+        <v>952.9400000000001</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>988.62</v>
+        <v>986.67</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>985.77</v>
+        <v>985.47</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>893.75</v>
+        <v>886.3</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>909.21</v>
+        <v>907.03</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>946.11</v>
+        <v>943.76</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>946.91</v>
+        <v>946.61</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2479.8</v>
+        <v>2607.9</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2657.72</v>
+        <v>2652.97</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2796.18</v>
+        <v>2788.8</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2713.59</v>
+        <v>2711.18</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>363.35</v>
+        <v>370</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>375.14</v>
+        <v>374.65</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>386.88</v>
+        <v>386.22</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>404.48</v>
+        <v>404.27</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,24 +1685,24 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>11579</v>
+        <v>11426</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>11527.73</v>
+        <v>11518.04</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>12100.75</v>
+        <v>12074.29</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13173.77</v>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>13160.03</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>392</v>
+        <v>393.1</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>408.41</v>
+        <v>406.95</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>412.58</v>
+        <v>411.82</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>412.87</v>
+        <v>412.77</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1761.3</v>
+        <v>1872</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1751.56</v>
+        <v>1763.03</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1746.83</v>
+        <v>1751.74</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1667.91</v>
+        <v>1668.67</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,20 +1817,20 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8137</v>
+        <v>8200</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>7988.64</v>
+        <v>8008.77</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8284.639999999999</v>
+        <v>8281.32</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8168.6</v>
+        <v>8168.58</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
@@ -1842,9 +1842,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J26" s="13" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>259.5</v>
+        <v>265</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>261.67</v>
+        <v>261.99</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>265.9</v>
+        <v>265.87</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>294.14</v>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>293.68</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>832.55</v>
+        <v>841.1</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>915.01</v>
+        <v>901.5</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>970.14</v>
+        <v>957.8</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>963.02</v>
+        <v>953.72</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1776.6</v>
+        <v>1769.6</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1676.5</v>
+        <v>1685.37</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1606.71</v>
+        <v>1613.1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1515.08</v>
+        <v>1517.76</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4690</v>
+        <v>4675</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4745.86</v>
+        <v>4739.12</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4877.88</v>
+        <v>4869.92</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4980.95</v>
+        <v>4980.9</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -2037,20 +2037,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1815.8</v>
+        <v>1858.2</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>1859.55</v>
+        <v>1859.42</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>1923.16</v>
+        <v>1920.61</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2107.13</v>
+        <v>2105.28</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2284.6</v>
+        <v>2302</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2346.43</v>
+        <v>2342.2</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2436.45</v>
+        <v>2431.17</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2518.94</v>
+        <v>2516.35</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11104</v>
+        <v>11175</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>10936.99</v>
+        <v>10959.66</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11057.67</v>
+        <v>11062.27</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11394.88</v>
+        <v>11387.48</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>205.15</v>
+        <v>207</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>213.99</v>
+        <v>213.33</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>223.34</v>
+        <v>222.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>245.49</v>
+        <v>244.83</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>263.6</v>
+        <v>266</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>277.97</v>
+        <v>276.83</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>294.85</v>
+        <v>293.72</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>353.86</v>
+        <v>352.38</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7300</v>
+        <v>7238</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7198.62</v>
+        <v>7202.37</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7352.36</v>
+        <v>7347.88</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7251.05</v>
+        <v>7245.96</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2282,9 +2282,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="J36" s="13" t="inlineStr">
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4337.9</v>
+        <v>4434</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4468.91</v>
+        <v>4465.59</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4625.24</v>
+        <v>4617.74</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4433.03</v>
+        <v>4434.72</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2913.9</v>
+        <v>2861.7</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2833.62</v>
+        <v>2836.29</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2844.28</v>
+        <v>2844.96</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3099.84</v>
+        <v>3096.81</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,24 +2389,24 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>251.4</v>
+        <v>260</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>252.76</v>
+        <v>253.45</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>260.19</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>275.22</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>275.11</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -2433,20 +2433,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2900</v>
+        <v>2932.8</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>2950.81</v>
+        <v>2949.09</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3048.48</v>
+        <v>3043.95</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3006.38</v>
+        <v>3004.83</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>224.89</v>
+        <v>225.79</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>226.58</v>
+        <v>226.51</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>230.93</v>
+        <v>230.73</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>243.64</v>
+        <v>243.52</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1400.5</v>
+        <v>1403.9</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1337.81</v>
+        <v>1344.1</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1293.68</v>
+        <v>1298</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1299.42</v>
+        <v>1300.04</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1168</v>
+        <v>1188.6</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1262.56</v>
+        <v>1255.52</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1332.75</v>
+        <v>1327.1</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1350.47</v>
+        <v>1348.24</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,29 +2609,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1241.2</v>
+        <v>1255.4</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1229.46</v>
+        <v>1231.93</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1246.88</v>
+        <v>1247.22</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1228.69</v>
+        <v>1228.78</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>514.1</v>
+        <v>517</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>534.59</v>
+        <v>532.92</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>541.14</v>
+        <v>540.1900000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>596.8</v>
+        <v>596.48</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,24 +2697,24 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10485</v>
+        <v>10383</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10387.75</v>
+        <v>10387.3</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10731.32</v>
+        <v>10717.66</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10298.73</v>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>10293.51</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1652.4</v>
+        <v>1668</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1721.08</v>
+        <v>1716.02</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1796.01</v>
+        <v>1790.99</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1871.54</v>
+        <v>1868.91</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1335.4</v>
+        <v>1345</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1244.61</v>
+        <v>1254.17</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1219.91</v>
+        <v>1224.81</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1232.04</v>
+        <v>1232.35</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,29 +2829,29 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1365.6</v>
+        <v>1358</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1343.28</v>
+        <v>1344.68</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1365.38</v>
+        <v>1365.09</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1389.51</v>
+        <v>1388.79</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
@@ -2873,29 +2873,29 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1000.2</v>
+        <v>1021</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>975.77</v>
+        <v>980.08</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1000.22</v>
+        <v>1001.03</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1068.96</v>
+        <v>1068.25</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>28-Oct-2026</t>
+          <t>29-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1666.7</v>
+        <v>1652</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1674.46</v>
+        <v>1672.33</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1715.63</v>
+        <v>1713.13</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1809.08</v>
+        <v>1807.7</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>

--- a/Report/EMAReport/nifty_50_ema_breadth.xlsx
+++ b/Report/EMAReport/nifty_50_ema_breadth.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scan Run: 29-Oct-2026  17:17:15    |    Closing Price Date: 29-Oct-2026</t>
+          <t>Scan Run: 30-Oct-2026  16:55:34    |    Closing Price Date: 30-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -594,24 +594,24 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>29-Oct-2026  17:17:15</t>
+          <t>30-Oct-2026  16:55:34</t>
         </is>
       </c>
     </row>
@@ -625,21 +625,21 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Short-Term  (20 EMA): NEUTRAL — 46.0% stocks above EMA (mixed market)</t>
+          <t>Short-Term  (20 EMA): NEUTRAL — 52.0% stocks above EMA (mixed market)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 32.0% stocks above EMA</t>
+          <t>Medium-Term (50 EMA): MODERATELY BEARISH — 36.0% stocks above EMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Long-Term  (200 EMA): STRONGLY BEARISH — 24.0% stocks above EMA (market broadly declining)</t>
+          <t>Long-Term  (200 EMA): MODERATELY BEARISH — 30.0% stocks above EMA</t>
         </is>
       </c>
     </row>
@@ -653,21 +653,21 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 20 EMA : 23 of 50 stocks</t>
+          <t xml:space="preserve">  Above 20 EMA : 26 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 50 EMA : 16 of 50 stocks</t>
+          <t xml:space="preserve">  Above 50 EMA : 18 of 50 stocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Above 200 EMA: 12 of 50 stocks</t>
+          <t xml:space="preserve">  Above 200 EMA: 15 of 50 stocks</t>
         </is>
       </c>
     </row>
@@ -761,20 +761,20 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1167.4</v>
+        <v>1164.9</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1194.74</v>
+        <v>1191.9</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1227.3</v>
+        <v>1224.85</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1311.57</v>
+        <v>1310.61</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -805,20 +805,20 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>683.3</v>
+        <v>692.8</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>702.08</v>
+        <v>701.2</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>715.49</v>
+        <v>714.6</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>782.89</v>
+        <v>782.36</v>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
@@ -849,20 +849,20 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2478</v>
+        <v>2502.6</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>2362.14</v>
+        <v>2375.52</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>2285.65</v>
+        <v>2294.15</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2403.68</v>
+        <v>2405.47</v>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
@@ -893,20 +893,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>190.1</v>
+        <v>198.31</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>178.77</v>
+        <v>180.63</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>175.48</v>
+        <v>176.38</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>191.2</v>
+        <v>191.34</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -918,9 +918,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr">
@@ -937,20 +937,20 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1386.6</v>
+        <v>1398</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1374.28</v>
+        <v>1376.54</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1374.05</v>
+        <v>1374.99</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1364.71</v>
+        <v>1365.67</v>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
@@ -981,24 +981,24 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>971.9</v>
+        <v>961.85</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>964.4299999999999</v>
+        <v>964.1799999999999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>983.97</v>
+        <v>983.1</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>995.21</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>995.12</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -1025,20 +1025,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1972.1</v>
+        <v>1973.7</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>1880.5</v>
+        <v>1889.38</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1864.8</v>
+        <v>1869.07</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1880.57</v>
+        <v>1883.06</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -1069,20 +1069,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1146.5</v>
+        <v>1185</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1107.85</v>
+        <v>1115.2</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1093.56</v>
+        <v>1097.15</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1189.6</v>
+        <v>1189.7</v>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
@@ -1113,20 +1113,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2890</v>
+        <v>2840.3</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2893.52</v>
+        <v>2888.45</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>2999.52</v>
+        <v>2993.27</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3167.74</v>
+        <v>3164.98</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -1157,20 +1157,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3837.1</v>
+        <v>3871.7</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3722.03</v>
+        <v>3736.29</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3802.24</v>
+        <v>3804.97</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3870.3</v>
+        <v>3871.18</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1182,9 +1182,9 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr">
@@ -1201,20 +1201,20 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1225</v>
+        <v>1217</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1233.36</v>
+        <v>1231.8</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1242.82</v>
+        <v>1241.81</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1254.47</v>
+        <v>1254.39</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -1245,20 +1245,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>169.46</v>
+        <v>167.6</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>174.28</v>
+        <v>173.64</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>179.62</v>
+        <v>179.15</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>184.99</v>
+        <v>184.8</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -1289,20 +1289,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>337.85</v>
+        <v>343.65</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>323.75</v>
+        <v>325.65</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>319.6</v>
+        <v>320.54</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>296.55</v>
+        <v>297.12</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1761</v>
+        <v>1777.7</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1773.09</v>
+        <v>1773.53</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1817.48</v>
+        <v>1815.92</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1810.47</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>1810.33</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1377,20 +1377,20 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>851.15</v>
+        <v>860</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>874.28</v>
+        <v>872.92</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>937.46</v>
+        <v>934.4299999999999</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1021.51</v>
+        <v>1021.47</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>459</v>
+        <v>461.6</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>436.54</v>
+        <v>438.93</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>423.72</v>
+        <v>425.21</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>407.73</v>
+        <v>408.35</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1465,20 +1465,20 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>310.5</v>
+        <v>316.25</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>310.44</v>
+        <v>310.99</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>320.69</v>
+        <v>320.51</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>339.78</v>
+        <v>339.64</v>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
@@ -1509,20 +1509,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>938.9</v>
+        <v>939.1</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>952.9400000000001</v>
+        <v>951.62</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>986.67</v>
+        <v>984.8099999999999</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>985.47</v>
+        <v>985.6799999999999</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1553,20 +1553,20 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>886.3</v>
+        <v>884.7</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>907.03</v>
+        <v>904.91</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>943.76</v>
+        <v>941.4400000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>946.61</v>
+        <v>946.22</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2607.9</v>
+        <v>2579.4</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>2652.97</v>
+        <v>2645.97</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2788.8</v>
+        <v>2780.59</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2711.18</v>
+        <v>2711.01</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1641,20 +1641,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>370</v>
+        <v>369.9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>374.65</v>
+        <v>374.2</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>386.22</v>
+        <v>385.58</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>404.27</v>
+        <v>403.81</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1685,20 +1685,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>11426</v>
+        <v>11397</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>11518.04</v>
+        <v>11506.52</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>12074.29</v>
+        <v>12047.73</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>13160.03</v>
+        <v>13148.15</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C24" s="11" t="n">
-        <v>393.1</v>
+        <v>389</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>406.95</v>
+        <v>405.24</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>411.82</v>
+        <v>410.92</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>412.77</v>
+        <v>412.59</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1773,20 +1773,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1872</v>
+        <v>1850</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1763.03</v>
+        <v>1771.31</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1751.74</v>
+        <v>1755.59</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1668.67</v>
+        <v>1670.48</v>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
@@ -1817,29 +1817,29 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C26" s="11" t="n">
-        <v>8200</v>
+        <v>8448</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>8008.77</v>
+        <v>8050.6</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>8281.32</v>
+        <v>8287.860000000001</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8168.58</v>
+        <v>8176.78</v>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
@@ -1861,20 +1861,20 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>265</v>
+        <v>265.6</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>261.99</v>
+        <v>262.33</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>265.87</v>
+        <v>265.86</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>293.68</v>
+        <v>293.36</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
@@ -1905,20 +1905,20 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>841.1</v>
+        <v>823.15</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>901.5</v>
+        <v>894.04</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>957.8</v>
+        <v>952.52</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>953.72</v>
+        <v>953</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1949,20 +1949,20 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1769.6</v>
+        <v>1790.8</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>1685.37</v>
+        <v>1695.41</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1613.1</v>
+        <v>1620.06</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1517.76</v>
+        <v>1520.45</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
@@ -1993,29 +1993,29 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4675</v>
+        <v>4877.6</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4739.12</v>
+        <v>4752.3</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>4869.92</v>
+        <v>4870.22</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4980.9</v>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>4977.69</v>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -2037,24 +2037,24 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1858.2</v>
+        <v>1864.6</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>1859.42</v>
+        <v>1859.91</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>1920.61</v>
+        <v>1918.41</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2105.28</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>2101.65</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2302</v>
+        <v>2320</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>2342.2</v>
+        <v>2340.09</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2431.17</v>
+        <v>2426.81</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2516.35</v>
+        <v>2514.83</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -2125,29 +2125,29 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>11175</v>
+        <v>11045</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>10959.66</v>
+        <v>10967.79</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>11062.27</v>
+        <v>11061.59</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>11387.48</v>
+        <v>11380.73</v>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
@@ -2169,20 +2169,20 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>207</v>
+        <v>204.5</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>213.33</v>
+        <v>212.48</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>222.7</v>
+        <v>221.99</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>244.83</v>
+        <v>244.58</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -2213,20 +2213,20 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>266</v>
+        <v>265.4</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>276.83</v>
+        <v>275.74</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>293.72</v>
+        <v>292.61</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>352.38</v>
+        <v>352.23</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -2257,20 +2257,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7238</v>
+        <v>7220</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>7202.37</v>
+        <v>7204.05</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7347.88</v>
+        <v>7342.86</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7245.96</v>
+        <v>7245.79</v>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4434</v>
+        <v>4436.5</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>4465.59</v>
+        <v>4462.82</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>4617.74</v>
+        <v>4610.63</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4434.72</v>
+        <v>4434.7</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -2326,9 +2326,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr">
@@ -2345,20 +2345,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>2861.7</v>
+        <v>3017.3</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>2836.29</v>
+        <v>2853.53</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>2844.96</v>
+        <v>2851.72</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3096.81</v>
+        <v>3095.95</v>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
@@ -2389,29 +2389,29 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>253.45</v>
+        <v>254.55</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>260.19</v>
+        <v>260.38</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>275.11</v>
+        <v>275.07</v>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2932.8</v>
+        <v>2981.4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>2949.09</v>
+        <v>2952.17</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>3043.95</v>
+        <v>3041.49</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3004.83</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>3004.02</v>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -2477,20 +2477,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>225.79</v>
+        <v>225.39</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>226.51</v>
+        <v>226.4</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>230.73</v>
+        <v>230.52</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>243.52</v>
+        <v>243.3</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -2521,20 +2521,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1403.9</v>
+        <v>1428.1</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>1344.1</v>
+        <v>1352.1</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1298</v>
+        <v>1303.1</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1300.04</v>
+        <v>1301.71</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
@@ -2565,20 +2565,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1188.6</v>
+        <v>1167</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>1255.52</v>
+        <v>1247.09</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1327.1</v>
+        <v>1320.82</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1348.24</v>
+        <v>1346.63</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -2609,29 +2609,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1255.4</v>
+        <v>1246</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1231.93</v>
+        <v>1233.27</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1247.22</v>
+        <v>1247.17</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1228.78</v>
+        <v>1229.08</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>517</v>
+        <v>524.9</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>532.92</v>
+        <v>532.15</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>540.1900000000001</v>
+        <v>539.59</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>596.48</v>
+        <v>595.73</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>10383</v>
+        <v>10350</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>10387.3</v>
+        <v>10383.75</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>10717.66</v>
+        <v>10703.25</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>10293.51</v>
+        <v>10298.38</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -2741,20 +2741,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1668</v>
+        <v>1667.6</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1716.02</v>
+        <v>1711.41</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1790.99</v>
+        <v>1786.16</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1868.91</v>
+        <v>1867.8</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2785,20 +2785,20 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1254.17</v>
+        <v>1263.48</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1224.81</v>
+        <v>1229.8</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1232.35</v>
+        <v>1233.85</v>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
@@ -2829,29 +2829,29 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>1358</v>
+        <v>1378.9</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>1344.68</v>
+        <v>1347.94</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1365.09</v>
+        <v>1365.63</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1388.79</v>
+        <v>1389.08</v>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
@@ -2873,20 +2873,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1021</v>
+        <v>1025.9</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>980.08</v>
+        <v>984.4400000000001</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1001.03</v>
+        <v>1002.01</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1068.25</v>
+        <v>1066.89</v>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
@@ -2917,20 +2917,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>30-Oct-2026</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>1652</v>
+        <v>1658.6</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>1672.33</v>
+        <v>1671.02</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1713.13</v>
+        <v>1711</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1807.7</v>
+        <v>1806.24</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
